--- a/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20854F55-9118-484D-B676-F7790A4DBA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35E3197B-A132-4BF8-AA66-BF5A007CD8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,45 @@
     <sheet name="Daily Standup Guide" sheetId="2" r:id="rId2"/>
     <sheet name="Burndown" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="123">
   <si>
     <t>Epic</t>
   </si>
@@ -48,78 +81,18 @@
     <t>Blocker / Notes</t>
   </si>
   <si>
-    <t>Entry Flow</t>
-  </si>
-  <si>
-    <t>Definition of Done Met?</t>
-  </si>
-  <si>
     <t>Auth</t>
   </si>
   <si>
-    <t>1.1</t>
-  </si>
-  <si>
     <t>Splash screen</t>
   </si>
   <si>
-    <t>Implement splash UI + branding</t>
-  </si>
-  <si>
-    <t>Atish</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>Landing page</t>
-  </si>
-  <si>
-    <t>Landing UI with Rent/List/Explore</t>
-  </si>
-  <si>
     <t>Alekhya</t>
   </si>
   <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>SignIn nav</t>
-  </si>
-  <si>
-    <t>Landing → SignIn navigation</t>
-  </si>
-  <si>
-    <t>Rent/List</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
-    <t>Login</t>
-  </si>
-  <si>
-    <t>Email/Password form + validation</t>
-  </si>
-  <si>
-    <t>Redirect</t>
-  </si>
-  <si>
-    <t>Post-login redirect logic</t>
-  </si>
-  <si>
-    <t>You</t>
-  </si>
-  <si>
     <t>Daily Standup Checklist</t>
   </si>
   <si>
@@ -141,9 +114,6 @@
     <t>Day</t>
   </si>
   <si>
-    <t>Total Remaining Hours</t>
-  </si>
-  <si>
     <t>Day 1</t>
   </si>
   <si>
@@ -172,14 +142,679 @@
   </si>
   <si>
     <t>Day 10</t>
+  </si>
+  <si>
+    <t>ToDo</t>
+  </si>
+  <si>
+    <t>DoD Met?</t>
+  </si>
+  <si>
+    <t>T-Shirt Sizing</t>
+  </si>
+  <si>
+    <t>Handle button press → store entry intent (Rent/List)</t>
+  </si>
+  <si>
+    <t>Landing Screen</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pressing on the explore hyperlink should navigate the user to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ExploreMaps</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unlogged in users should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SignIn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen upon pressing any button</t>
+    </r>
+  </si>
+  <si>
+    <t>Task No.</t>
+  </si>
+  <si>
+    <t>Story Point</t>
+  </si>
+  <si>
+    <t>Preserve entry intent (Rent/List)</t>
+  </si>
+  <si>
+    <t>Create Sign In screen layout</t>
+  </si>
+  <si>
+    <t>Add Email input field</t>
+  </si>
+  <si>
+    <t>Add Password input field</t>
+  </si>
+  <si>
+    <t>Add Continue button</t>
+  </si>
+  <si>
+    <t>Handle navigation from Landing → Sign In</t>
+  </si>
+  <si>
+    <t>Sign in Screen</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Add </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SignUp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <t>Create login API service with FastAPI</t>
+  </si>
+  <si>
+    <t>Handle loading state</t>
+  </si>
+  <si>
+    <t>Handle successful login response</t>
+  </si>
+  <si>
+    <t>Handle invalid credentials error</t>
+  </si>
+  <si>
+    <t>Set correct bottom nav tab</t>
+  </si>
+  <si>
+    <t>Detect entry intent (Rent/List)</t>
+  </si>
+  <si>
+    <t>Detect user role (Owner/Renter)</t>
+  </si>
+  <si>
+    <t>Show personalized welcome note</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerE-BikeListing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerExistingE-BikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>Detect logged-in user state</t>
+  </si>
+  <si>
+    <t>Handle Rent button press → RenterE-BikeBookingFilter screen</t>
+  </si>
+  <si>
+    <t>Handle List button press → First time Listing? → OwnerE-BikeListing screen</t>
+  </si>
+  <si>
+    <t>Handle List button press → Existing lister? → OwnerExistingE-BikesList screen</t>
+  </si>
+  <si>
+    <t>Skip Sign In screen</t>
+  </si>
+  <si>
+    <t>Preserve bottom navigation state:
+Owner: My Bikes
+Renter: my Rides</t>
+  </si>
+  <si>
+    <t>Persist Explore tab selection</t>
+  </si>
+  <si>
+    <t>Create Explore screen shell</t>
+  </si>
+  <si>
+    <t>Handle Explore link from Landing</t>
+  </si>
+  <si>
+    <t>Handle Explore bottom nav selection</t>
+  </si>
+  <si>
+    <t>Allow guest access</t>
+  </si>
+  <si>
+    <t>Block navigation for Profile</t>
+  </si>
+  <si>
+    <t>Detect auth state on tab press</t>
+  </si>
+  <si>
+    <t>Block navigation for My Rides</t>
+  </si>
+  <si>
+    <t>Block navigation for My Bikes</t>
+  </si>
+  <si>
+    <t>Redirect to Sign In screen</t>
+  </si>
+  <si>
+    <t>Preserve target tab intent</t>
+  </si>
+  <si>
+    <t>After login → redirect to intended tab</t>
+  </si>
+  <si>
+    <t>Explore-guest</t>
+  </si>
+  <si>
+    <t>Show inline errors</t>
+  </si>
+  <si>
+    <t>Sign Up Screen</t>
+  </si>
+  <si>
+    <t>Create T&amp;C screen</t>
+  </si>
+  <si>
+    <t>Render scrollable content</t>
+  </si>
+  <si>
+    <t>Implement “OK” button</t>
+  </si>
+  <si>
+    <t>Navigate back to Sign Up screen upon pressing OK button</t>
+  </si>
+  <si>
+    <t>SignUp-T&amp;C</t>
+  </si>
+  <si>
+    <t>Add ID upload button</t>
+  </si>
+  <si>
+    <t>Integrate camera/gallery picker</t>
+  </si>
+  <si>
+    <t>Preview uploaded ID</t>
+  </si>
+  <si>
+    <t>Validate file type</t>
+  </si>
+  <si>
+    <t>Handle upload failure</t>
+  </si>
+  <si>
+    <t>SignUp-ID Upload</t>
+  </si>
+  <si>
+    <t>Add selfie capture button</t>
+  </si>
+  <si>
+    <t>Open camera</t>
+  </si>
+  <si>
+    <t>Capture selfie image</t>
+  </si>
+  <si>
+    <t>Preview selfie</t>
+  </si>
+  <si>
+    <t>Retake option</t>
+  </si>
+  <si>
+    <t>SignUp-Selfie</t>
+  </si>
+  <si>
+    <t>Create registration API service with FastAPI</t>
+  </si>
+  <si>
+    <t>Submit form data</t>
+  </si>
+  <si>
+    <t>Submit ID image</t>
+  </si>
+  <si>
+    <t>Submit selfie image</t>
+  </si>
+  <si>
+    <t>Show loading state</t>
+  </si>
+  <si>
+    <t>SignUp-Backend</t>
+  </si>
+  <si>
+    <t>Display field entry errors</t>
+  </si>
+  <si>
+    <t>Handle backend validation errors (existing email)</t>
+  </si>
+  <si>
+    <t>Auto-login user upon successful sign up</t>
+  </si>
+  <si>
+    <t>1. Create splash screen component in react native
+2. Add logo app name, tagline text
+3. Add brand values text</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>1. Implement 3-second timer
+2. Loading the required app resources within that span
+3. Navigate to Landing screen after timer</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Create landing screen layout
+2. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rent a Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button
+3. Add</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> List a Bike</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> primary button
+4. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <t>Sayan</t>
+  </si>
+  <si>
+    <t>Anirban</t>
+  </si>
+  <si>
+    <t>Create reusable fonts library</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Create reusable UI elements package</t>
+  </si>
+  <si>
+    <t>Remaining Story Points</t>
+  </si>
+  <si>
+    <t>Create reusable color palate</t>
+  </si>
+  <si>
+    <t>XS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Logged in renter should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+2. Logged in owner with zero listed e-bikes should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerE-BikeListing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+3. Logged in owner with existing listed e-bikes should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerExistingE-BikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Client-side email match with database entry
+2. Client-side password match with database entry
+3. Disable Continue button on invalid input
+4. Show inline validation errors</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Renter should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+2. Owner with zero listed e-bikes should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerE-BikeListing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+3. Owner with existing listed e-bikes should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerExistingE-BikesList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Create Sign Up screen layout
+2. Full Name input
+3. Birth date picker
+4. Email input
+5. Terms &amp; Conditions checkbox
+6. Disable Continue button until checkbox checked</t>
+  </si>
+  <si>
+    <t>Client-side validations:
+1. Age &gt; 16 years
+2. Prevent using same email to signup twice
+3. Name should match Govt. ID name</t>
+  </si>
+  <si>
+    <t>1. Validate image against ID ~ 80%
+2. Validate image is without hats or glasses
+3. Validate image clarity (no blur or shake)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -195,7 +830,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -203,12 +838,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,197 +1179,2669 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="65.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E2" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H2" s="4" cm="1">
+        <f t="array" ref="H2">_xlfn.SWITCH(G2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H3" s="4" cm="1">
+        <f t="array" ref="H3">_xlfn.SWITCH(G3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" s="4" cm="1">
+        <f t="array" ref="H4">_xlfn.SWITCH(G4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H5" s="4" cm="1">
+        <f t="array" ref="H5">_xlfn.SWITCH(G5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H6" s="4" cm="1">
+        <f t="array" ref="H6">_xlfn.SWITCH(G6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="4" cm="1">
+        <f t="array" ref="H7">_xlfn.SWITCH(G7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="4" cm="1">
+        <f t="array" ref="H8">_xlfn.SWITCH(G8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" s="4" cm="1">
+        <f t="array" ref="H9">_xlfn.SWITCH(G9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <v>14</v>
       </c>
-      <c r="F2">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="4" cm="1">
+        <f t="array" ref="H10">_xlfn.SWITCH(G10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="B11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" s="4" cm="1">
+        <f t="array" ref="H11">_xlfn.SWITCH(G11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H12" s="4" cm="1">
+        <f t="array" ref="H12">_xlfn.SWITCH(G12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="4" cm="1">
+        <f t="array" ref="H13">_xlfn.SWITCH(G13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H14" s="4" cm="1">
+        <f t="array" ref="H14">_xlfn.SWITCH(G14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <v>19</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="4" cm="1">
+        <f t="array" ref="H15">_xlfn.SWITCH(G15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H16" s="4" cm="1">
+        <f t="array" ref="H16">_xlfn.SWITCH(G16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
         <v>21</v>
       </c>
-      <c r="F3">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="4" cm="1">
+        <f t="array" ref="H17">_xlfn.SWITCH(G17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="4" cm="1">
+        <f t="array" ref="H18">_xlfn.SWITCH(G18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
         <v>23</v>
       </c>
-      <c r="D4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H19" s="4" cm="1">
+        <f t="array" ref="H19">_xlfn.SWITCH(G19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="4" cm="1">
+        <f t="array" ref="H20">_xlfn.SWITCH(G20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
         <v>28</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="B21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" s="4" cm="1">
+        <f t="array" ref="H21">_xlfn.SWITCH(G21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>29</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H22" s="4" cm="1">
+        <f t="array" ref="H22">_xlfn.SWITCH(G22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
         <v>30</v>
       </c>
-      <c r="E6" t="s">
+      <c r="B23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="4" cm="1">
+        <f t="array" ref="H23">_xlfn.SWITCH(G23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
         <v>31</v>
       </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" t="s">
-        <v>17</v>
-      </c>
+      <c r="B24" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" s="4" cm="1">
+        <f t="array" ref="H24">_xlfn.SWITCH(G24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>32</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" s="4" cm="1">
+        <f t="array" ref="H25">_xlfn.SWITCH(G25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <v>33</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" s="4" cm="1">
+        <f t="array" ref="H26">_xlfn.SWITCH(G26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>34</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H27" s="4" cm="1">
+        <f t="array" ref="H27">_xlfn.SWITCH(G27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
+        <v>35</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H28" s="4" cm="1">
+        <f t="array" ref="H28">_xlfn.SWITCH(G28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>36</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" s="4" cm="1">
+        <f t="array" ref="H29">_xlfn.SWITCH(G29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
+        <v>37</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="4" cm="1">
+        <f t="array" ref="H30">_xlfn.SWITCH(G30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>38</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H31" s="4" cm="1">
+        <f t="array" ref="H31">_xlfn.SWITCH(G31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="4">
+        <v>39</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H32" s="4" cm="1">
+        <f t="array" ref="H32">_xlfn.SWITCH(G32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>40</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H33" s="4" cm="1">
+        <f t="array" ref="H33">_xlfn.SWITCH(G33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
+        <v>41</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H34" s="4" cm="1">
+        <f t="array" ref="H34">_xlfn.SWITCH(G34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>42</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H35" s="4" cm="1">
+        <f t="array" ref="H35">_xlfn.SWITCH(G35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>43</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H36" s="4" cm="1">
+        <f t="array" ref="H36">_xlfn.SWITCH(G36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>44</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H37" s="4" cm="1">
+        <f t="array" ref="H37">_xlfn.SWITCH(G37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
+        <v>45</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H38" s="4" cm="1">
+        <f t="array" ref="H38">_xlfn.SWITCH(G38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>46</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H39" s="4" cm="1">
+        <f t="array" ref="H39">_xlfn.SWITCH(G39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>47</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H40" s="4" cm="1">
+        <f t="array" ref="H40">_xlfn.SWITCH(G40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>48</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H41" s="4" cm="1">
+        <f t="array" ref="H41">_xlfn.SWITCH(G41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="4">
+        <v>49</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H42" s="4" cm="1">
+        <f t="array" ref="H42">_xlfn.SWITCH(G42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="4">
+        <v>50</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H43" s="4" cm="1">
+        <f t="array" ref="H43">_xlfn.SWITCH(G43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="4">
+        <v>51</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H44" s="4" cm="1">
+        <f t="array" ref="H44">_xlfn.SWITCH(G44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
+        <v>52</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H45" s="4" cm="1">
+        <f t="array" ref="H45">_xlfn.SWITCH(G45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="4">
+        <v>53</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H46" s="4" cm="1">
+        <f t="array" ref="H46">_xlfn.SWITCH(G46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="4">
+        <v>54</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H47" s="4" cm="1">
+        <f t="array" ref="H47">_xlfn.SWITCH(G47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="4">
+        <v>55</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H48" s="4" cm="1">
+        <f t="array" ref="H48">_xlfn.SWITCH(G48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="4">
+        <v>61</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H49" s="4" cm="1">
+        <f t="array" ref="H49">_xlfn.SWITCH(G49,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="4">
+        <v>62</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H50" s="4" cm="1">
+        <f t="array" ref="H50">_xlfn.SWITCH(G50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="4">
+        <v>63</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H51" s="4" cm="1">
+        <f t="array" ref="H51">_xlfn.SWITCH(G51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="4">
+        <v>64</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H52" s="4" cm="1">
+        <f t="array" ref="H52">_xlfn.SWITCH(G52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="4">
+        <v>65</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H53" s="4" cm="1">
+        <f t="array" ref="H53">_xlfn.SWITCH(G53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="4">
+        <v>66</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H54" s="4" cm="1">
+        <f t="array" ref="H54">_xlfn.SWITCH(G54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="4">
+        <v>67</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H55" s="4" cm="1">
+        <f t="array" ref="H55">_xlfn.SWITCH(G55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="4">
+        <v>68</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H56" s="4" cm="1">
+        <f t="array" ref="H56">_xlfn.SWITCH(G56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="4">
+        <v>69</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H57" s="4" cm="1">
+        <f t="array" ref="H57">_xlfn.SWITCH(G57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="4">
+        <v>70</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H58" s="4" cm="1">
+        <f t="array" ref="H58">_xlfn.SWITCH(G58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="4">
+        <v>71</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H59" s="4" cm="1">
+        <f t="array" ref="H59">_xlfn.SWITCH(G59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="4">
+        <v>72</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H60" s="4" cm="1">
+        <f t="array" ref="H60">_xlfn.SWITCH(G60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="4">
+        <v>73</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H61" s="4" cm="1">
+        <f t="array" ref="H61">_xlfn.SWITCH(G61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="4">
+        <v>74</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H62" s="4" cm="1">
+        <f t="array" ref="H62">_xlfn.SWITCH(G62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="4">
+        <v>75</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H63" s="4" cm="1">
+        <f t="array" ref="H63">_xlfn.SWITCH(G63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="4">
+        <v>76</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H64" s="4" cm="1">
+        <f t="array" ref="H64">_xlfn.SWITCH(G64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="4">
+        <v>77</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H65" s="4" cm="1">
+        <f t="array" ref="H65">_xlfn.SWITCH(G65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="4">
+        <v>80</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H66" s="4" cm="1">
+        <f t="array" ref="H66">_xlfn.SWITCH(G66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="4">
+        <v>81</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H67" s="4" cm="1">
+        <f t="array" ref="H67">_xlfn.SWITCH(G67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="4">
+        <v>82</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G68" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H68" s="4" cm="1">
+        <f t="array" ref="H68">_xlfn.SWITCH(G68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="4">
+        <v>83</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G69" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H69" s="4" cm="1">
+        <f t="array" ref="H69">_xlfn.SWITCH(G69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="4">
+        <v>84</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H70" s="4" cm="1">
+        <f t="array" ref="H70">_xlfn.SWITCH(G70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="4">
+        <v>85</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H71" s="4" cm="1">
+        <f t="array" ref="H71">_xlfn.SWITCH(G71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="4">
+        <v>86</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H72" s="4" cm="1">
+        <f t="array" ref="H72">_xlfn.SWITCH(G72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="4">
+        <v>87</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="4"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H73" s="4" cm="1">
+        <f t="array" ref="H73">_xlfn.SWITCH(G73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="4">
+        <v>88</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="4"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H74" s="4" cm="1">
+        <f t="array" ref="H74">_xlfn.SWITCH(G74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A75" s="4">
+        <v>89</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H75" s="4" cm="1">
+        <f t="array" ref="H75">_xlfn.SWITCH(G75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="4">
+        <v>90</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H76" s="4" cm="1">
+        <f t="array" ref="H76">_xlfn.SWITCH(G76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="4">
+        <v>91</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4" t="str" cm="1">
+        <f t="array" ref="H77">_xlfn.SWITCH(G77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="4">
+        <v>92</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4" t="str" cm="1">
+        <f t="array" ref="H78">_xlfn.SWITCH(G78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="4">
+        <v>93</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4" t="str" cm="1">
+        <f t="array" ref="H79">_xlfn.SWITCH(G79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="4">
+        <v>94</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" s="4"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="4"/>
+      <c r="H80" s="4" t="str" cm="1">
+        <f t="array" ref="H80">_xlfn.SWITCH(G80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="4">
+        <v>95</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4" t="str" cm="1">
+        <f t="array" ref="H81">_xlfn.SWITCH(G81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="4">
+        <v>96</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4" t="str" cm="1">
+        <f t="array" ref="H82">_xlfn.SWITCH(G82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="4">
+        <v>97</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4" t="str" cm="1">
+        <f t="array" ref="H83">_xlfn.SWITCH(G83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="4">
+        <v>98</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4" t="str" cm="1">
+        <f t="array" ref="H84">_xlfn.SWITCH(G84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="4">
+        <v>99</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4" t="str" cm="1">
+        <f t="array" ref="H85">_xlfn.SWITCH(G85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -715,32 +3855,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -751,64 +3891,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="13.44140625" style="1"/>
+    <col min="3" max="16384" width="13.44140625" style="6"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" t="s">
-        <v>39</v>
+    <row r="1" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>40</v>
+      <c r="A2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>41</v>
+      <c r="A3" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>42</v>
+      <c r="A4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>43</v>
+      <c r="A5" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>44</v>
+      <c r="A6" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>45</v>
+      <c r="A7" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>46</v>
+      <c r="A8" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>47</v>
+      <c r="A9" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>48</v>
+      <c r="A10" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>49</v>
+      <c r="A11" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C4A82F-C5B4-4A8D-BAC9-BE1322566F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5521A2C-7725-4591-B2AC-C7880A1D5B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="158">
   <si>
     <t>Epic</t>
   </si>
@@ -218,9 +218,6 @@
   </si>
   <si>
     <t>Sign in Screen</t>
-  </si>
-  <si>
-    <t>Create login API service with FastAPI</t>
   </si>
   <si>
     <t>Handle loading state</t>
@@ -369,12 +366,6 @@
   </si>
   <si>
     <t>XS</t>
-  </si>
-  <si>
-    <t>1. Client-side email match with database entry
-2. Client-side password match with database entry
-3. Disable Continue button on invalid input
-4. Show inline validation errors</t>
   </si>
   <si>
     <t>Client-side validations:
@@ -788,78 +779,6 @@
   </si>
   <si>
     <t>Landing screen renders</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign In</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout
-2. Add Email input field
-3. Add Password input field
-4. Add </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Continue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button
-5. Add </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SignUp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink</t>
-    </r>
   </si>
   <si>
     <r>
@@ -956,22 +875,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Add entryResolve logic for separating renter, lister(owner) based on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>entryIntent</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Pressing </t>
     </r>
     <r>
@@ -1668,6 +1571,384 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen layout</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Add entryResolve logic for separating renter, lister(owner) based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>entryIntent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> context</t>
+    </r>
+  </si>
+  <si>
+    <t>Sign In</t>
+  </si>
+  <si>
+    <t>Sign In screen renders without crashing</t>
+  </si>
+  <si>
+    <t>Pressing Sign In calls Signin() with email and password</t>
+  </si>
+  <si>
+    <t>Manage local form state (email, password)</t>
+  </si>
+  <si>
+    <t>1. Handle successful login response
+2. Handle failed login response (error message)</t>
+  </si>
+  <si>
+    <t>1. Prevent multiple submissions
+2. Implement loading state while login is underway</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. On successful sign in, update authStatus = AUTHENTICATED
+2. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">EntryResolver </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>if sign in was successful</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Disable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Sign In button when both or any one inputs (Email, Password)are empty</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Handle </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button press with onPress
+2. Call Signin() method</t>
+    </r>
+  </si>
+  <si>
+    <t>Add testIDs to inputs and buttons:
+1. Email Input- testID = "emailTextInput"
+2. Passwordl Input- testID = "passwordTextInput"
+1. Button- testID = "SignInButton"</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reset local form state on unmount (navigating away anywhere from Sign in):
+1. Email: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>const [email, setEmail] = useState('');</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Password: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>const [password, setPassword] = useState('');</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Email input is visible
+2. Password input is visible
+3. Sign In button is visible
+4. Sign Up hyperlink is visible</t>
+  </si>
+  <si>
+    <t>1. Sign In button is disabled when email is empty
+2. Sign In button is disabled when password is empty
+3. Sign In button is enabled when both fields are filled</t>
+  </si>
+  <si>
+    <t>1. Multiple rapid presses do not trigger multiple signin calls
+2. Loading indicator is shown during login attempt</t>
+  </si>
+  <si>
+    <t>1. Successful login updates authStatus to AUTHENTICATED
+2. Successful login navigates to EntryResolver
+3. entryIntent is preserved after login</t>
+  </si>
+  <si>
+    <t>1. Failed login shows error message
+2. Failed login does NOT update authStatus
+3. Failed login does NOT navigate</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink navigates to Sign Up screen layout</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout
+2. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> input field
+3. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Password</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> input field
+4. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Continue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button
+5. Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SignUp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Handle </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink click → navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab (public access)</t>
     </r>
   </si>
 </sst>
@@ -1675,7 +1956,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1723,8 +2004,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1764,6 +2052,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1808,7 +2120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1862,6 +2174,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2165,7 +2501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2186,7 +2522,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -2198,7 +2534,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>3</v>
@@ -2226,98 +2562,98 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="12">
+      <c r="A2" s="20">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" s="12" cm="1">
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="20" cm="1">
         <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12" t="s">
+      <c r="J2" s="20"/>
+      <c r="K2" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
+      <c r="A3" s="20">
         <v>2</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="12" cm="1">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" s="20" cm="1">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12" t="s">
+      <c r="J3" s="20"/>
+      <c r="K3" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
+      <c r="A4" s="20">
         <v>3</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="12" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I4" s="12" cm="1">
+      <c r="G4" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="20" cm="1">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12" t="s">
+      <c r="J4" s="20"/>
+      <c r="K4" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2329,16 +2665,16 @@
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I5" s="12" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2361,16 +2697,16 @@
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I6" s="12" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2393,16 +2729,16 @@
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>112</v>
-      </c>
       <c r="G7" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I7" s="12" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2423,16 +2759,16 @@
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I8" s="12" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2453,16 +2789,16 @@
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I9" s="12" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2478,96 +2814,96 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+      <c r="A10" s="22">
         <v>7</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="I10" s="12" cm="1">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" s="22" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12" t="s">
+      <c r="J10" s="22"/>
+      <c r="K10" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="H11" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="12" cm="1">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="22" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12" t="s">
+      <c r="J11" s="22"/>
+      <c r="K11" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
-        <v>8</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" s="12" t="s">
+      <c r="A12" s="22">
+        <v>8</v>
+      </c>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="G12" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="12" cm="1">
+      <c r="H12" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="22" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12" t="s">
+      <c r="J12" s="22"/>
+      <c r="K12" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2585,16 +2921,16 @@
         <v>9</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I13" s="7" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2623,16 +2959,16 @@
         <v>9</v>
       </c>
       <c r="E14" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>97</v>
-      </c>
       <c r="G14" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I14" s="7" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2661,16 +2997,16 @@
         <v>9</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I15" s="7" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2699,16 +3035,16 @@
         <v>9</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F16" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>102</v>
-      </c>
       <c r="H16" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I16" s="7" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2737,16 +3073,16 @@
         <v>9</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I17" s="7" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2771,16 +3107,16 @@
         <v>9</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I18" s="7" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2805,16 +3141,16 @@
         <v>9</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>11</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I19" s="10" cm="1">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2843,16 +3179,16 @@
         <v>9</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I20" s="10" cm="1">
         <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2872,21 +3208,23 @@
         <v>17</v>
       </c>
       <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="C21" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D21" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I21" s="14" cm="1">
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2906,21 +3244,23 @@
         <v>18</v>
       </c>
       <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
+      <c r="C22" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D22" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I22" s="14" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2940,21 +3280,23 @@
         <v>19</v>
       </c>
       <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="C23" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D23" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I23" s="14" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2974,21 +3316,23 @@
         <v>20</v>
       </c>
       <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="C24" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D24" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I24" s="14" cm="1">
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3008,21 +3352,23 @@
         <v>21</v>
       </c>
       <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="C25" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D25" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I25" s="14" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3040,21 +3386,23 @@
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
+      <c r="C26" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D26" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I26" s="14" cm="1">
         <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3072,21 +3420,23 @@
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="14"/>
       <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
+      <c r="C27" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D27" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I27" s="14" cm="1">
         <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3104,21 +3454,23 @@
     <row r="28" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
+      <c r="C28" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D28" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I28" s="14" cm="1">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3136,21 +3488,23 @@
     <row r="29" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="14"/>
       <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
+      <c r="C29" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D29" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I29" s="14" cm="1">
         <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3168,21 +3522,23 @@
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="14"/>
       <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
+      <c r="C30" s="14">
+        <v>1.2</v>
+      </c>
       <c r="D30" s="14" t="s">
         <v>32</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I30" s="14" cm="1">
         <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3211,16 +3567,16 @@
         <v>32</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G31" s="15" t="s">
         <v>11</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I31" s="15" cm="1">
         <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3249,16 +3605,16 @@
         <v>32</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G32" s="15" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I32" s="15" cm="1">
         <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3280,693 +3636,707 @@
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="15"/>
+      <c r="C33" s="15">
+        <v>1.2</v>
+      </c>
       <c r="D33" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G33" s="15" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I33" s="15" cm="1">
         <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
+      <c r="K33" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
+      <c r="M33" s="15" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>25</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="2">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="15">
         <v>1.2</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="15" cm="1">
+        <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="24">
+        <v>1.3</v>
+      </c>
+      <c r="D35" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I34" s="2" cm="1">
-        <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>26</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I35" s="2" cm="1">
+      <c r="E35" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="G35" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="I35" s="24" cm="1">
         <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>27</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I36" s="2" cm="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="24"/>
+      <c r="B36" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="24">
+        <v>1.3</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F36" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="G36" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="I36" s="24" cm="1">
         <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>28</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="24">
         <v>1.3</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I37" s="2" cm="1">
+      <c r="D37" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="G37" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="24" cm="1">
         <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2" t="s">
+      <c r="J37" s="24"/>
+      <c r="K37" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>33</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="2">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="24">
         <v>1.3</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I38" s="2" cm="1">
+      <c r="D38" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="I38" s="24" cm="1">
         <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
-        <v>34</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="J38" s="24"/>
+      <c r="K38" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="24">
         <v>1.3</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I39" s="2" cm="1">
+      <c r="D39" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H39" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="24" cm="1">
         <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>35</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="2">
+      <c r="J39" s="24"/>
+      <c r="K39" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="24">
         <v>1.3</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I40" s="2" cm="1">
+      <c r="D40" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="G40" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H40" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="I40" s="24" cm="1">
         <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>36</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="2">
+        <v>3</v>
+      </c>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="24">
         <v>1.3</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I41" s="2" cm="1">
+      <c r="D41" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F41" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G41" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H41" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="I41" s="24" cm="1">
         <f t="array" ref="I41">_xlfn.SWITCH(H41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>37</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="2">
+      <c r="A42" s="24"/>
+      <c r="B42" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="24">
         <v>1.3</v>
       </c>
-      <c r="D42" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I42" s="2" cm="1">
+      <c r="D42" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="G42" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H42" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="I42" s="24" cm="1">
         <f t="array" ref="I42">_xlfn.SWITCH(H42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>38</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="2">
+        <v>2</v>
+      </c>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A43" s="26"/>
+      <c r="B43" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="26">
         <v>1.3</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I43" s="2" cm="1">
+      <c r="D43" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F43" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="G43" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="I43" s="26" cm="1">
         <f t="array" ref="I43">_xlfn.SWITCH(H43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>39</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="2">
+      <c r="A44" s="26"/>
+      <c r="B44" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="26">
         <v>1.3</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I44" s="2" cm="1">
+      <c r="D44" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="G44" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I44" s="26" cm="1">
         <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
-        <v>40</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="2">
+        <v>2</v>
+      </c>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="26"/>
+      <c r="B45" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="26">
         <v>1.3</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I45" s="2" cm="1">
+      <c r="D45" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E45" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="G45" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I45" s="26" cm="1">
         <f t="array" ref="I45">_xlfn.SWITCH(H45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
-        <v>41</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="2">
+        <v>2</v>
+      </c>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="26"/>
+      <c r="B46" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="26">
         <v>1.3</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I46" s="2" cm="1">
+      <c r="D46" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F46" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="G46" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="I46" s="26" cm="1">
         <f t="array" ref="I46">_xlfn.SWITCH(H46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
-        <v>42</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="26"/>
+      <c r="B47" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="26">
         <v>1.3</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I47" s="2" cm="1">
+      <c r="D47" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="G47" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I47" s="26" cm="1">
         <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>43</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="2">
+      <c r="J47" s="26"/>
+      <c r="K47" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L47" s="26"/>
+      <c r="M47" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="26"/>
+      <c r="B48" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="26">
         <v>1.3</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I48" s="2" cm="1">
+      <c r="D48" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I48" s="26" cm="1">
         <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
-        <v>44</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="2">
+      <c r="J48" s="26"/>
+      <c r="K48" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L48" s="26"/>
+      <c r="M48" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="26"/>
+      <c r="B49" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="26">
         <v>1.3</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G49" s="2" t="s">
+      <c r="D49" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F49" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="G49" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="H49" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I49" s="2" cm="1">
+      <c r="H49" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I49" s="26" cm="1">
         <f t="array" ref="I49">_xlfn.SWITCH(H49,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J49" s="26"/>
+      <c r="K49" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L49" s="26"/>
+      <c r="M49" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="26"/>
+      <c r="B50" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="D50" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F50" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="G50" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="I50" s="26" cm="1">
+        <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
-        <v>45</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="2">
+      <c r="J50" s="26"/>
+      <c r="K50" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L50" s="26"/>
+      <c r="M50" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="26"/>
+      <c r="B51" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="26">
         <v>1.3</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I50" s="2" cm="1">
-        <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
-        <v>46</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I51" s="2" cm="1">
+      <c r="D51" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F51" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="G51" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="I51" s="26" cm="1">
         <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="J51" s="26"/>
+      <c r="K51" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L51" s="26"/>
+      <c r="M51" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="C52" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E52" s="2"/>
       <c r="F52" s="3" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I52" s="2" cm="1">
         <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3981,28 +4351,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="C53" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E53" s="2"/>
       <c r="F53" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I53" s="2" cm="1">
         <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -4015,26 +4389,30 @@
     </row>
     <row r="54" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="C54" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E54" s="2"/>
       <c r="F54" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I54" s="2" cm="1">
         <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
@@ -4047,26 +4425,30 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
+      <c r="C55" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E55" s="2"/>
       <c r="F55" s="3" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I55" s="2" cm="1">
         <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
@@ -4077,28 +4459,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
+      <c r="C56" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E56" s="2"/>
       <c r="F56" s="3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I56" s="2" cm="1">
         <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
@@ -4111,28 +4497,30 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C57" s="2"/>
+      <c r="C57" s="2">
+        <v>1.3</v>
+      </c>
       <c r="D57" s="2" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="3" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I57" s="2" cm="1">
         <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
@@ -4145,22 +4533,26 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="C58" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E58" s="2"/>
       <c r="F58" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I58" s="2" cm="1">
         <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4177,22 +4569,26 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
+      <c r="C59" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E59" s="2"/>
       <c r="F59" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I59" s="2" cm="1">
         <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4209,22 +4605,26 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
+      <c r="C60" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E60" s="2"/>
       <c r="F60" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I60" s="2" cm="1">
         <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4241,22 +4641,26 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
+      <c r="C61" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E61" s="2"/>
       <c r="F61" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I61" s="2" cm="1">
         <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4273,26 +4677,30 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="C62" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E62" s="2"/>
       <c r="F62" s="3" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I62" s="2" cm="1">
         <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
@@ -4305,26 +4713,30 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
+      <c r="C63" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E63" s="2"/>
       <c r="F63" s="3" t="s">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I63" s="2" cm="1">
         <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
@@ -4337,26 +4749,30 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
+      <c r="C64" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E64" s="2"/>
       <c r="F64" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I64" s="2" cm="1">
         <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
@@ -4369,22 +4785,26 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
+      <c r="C65" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E65" s="2"/>
       <c r="F65" s="3" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I65" s="2" cm="1">
         <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4401,7 +4821,7 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>8</v>
@@ -4410,13 +4830,13 @@
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="3" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I66" s="2" cm="1">
         <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4433,7 +4853,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>8</v>
@@ -4442,13 +4862,13 @@
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="3" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I67" s="2" cm="1">
         <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4465,7 +4885,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>8</v>
@@ -4474,13 +4894,13 @@
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="3" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I68" s="2" cm="1">
         <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4495,30 +4915,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="2" t="s">
-        <v>119</v>
-      </c>
+      <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I69" s="2" cm="1">
         <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
@@ -4529,30 +4947,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="2"/>
-      <c r="D70" s="2" t="s">
-        <v>121</v>
-      </c>
+      <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="3" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I70" s="2" cm="1">
         <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
@@ -4563,30 +4979,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="2"/>
-      <c r="D71" s="2" t="s">
-        <v>120</v>
-      </c>
+      <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="3" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I71" s="2" cm="1">
         <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
@@ -4597,30 +5011,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>123</v>
+        <v>64</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" s="3" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I72" s="2" cm="1">
         <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
@@ -4631,30 +5045,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="2"/>
-      <c r="D73" s="2" t="s">
-        <v>124</v>
-      </c>
+      <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="3" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I73" s="2" cm="1">
         <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
@@ -4667,28 +5079,26 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="2"/>
-      <c r="D74" s="2" t="s">
-        <v>125</v>
-      </c>
+      <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="3" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I74" s="2" cm="1">
         <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
@@ -4701,7 +5111,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>8</v>
@@ -4710,13 +5120,13 @@
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I75" s="2" cm="1">
         <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4733,7 +5143,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>8</v>
@@ -4742,13 +5152,13 @@
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="3" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I76" s="2" cm="1">
         <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4765,7 +5175,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>8</v>
@@ -4774,13 +5184,13 @@
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I77" s="2" cm="1">
         <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4797,7 +5207,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>8</v>
@@ -4806,13 +5216,13 @@
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I78" s="2" cm="1">
         <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4827,30 +5237,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="2"/>
-      <c r="D79" s="2" t="s">
-        <v>126</v>
-      </c>
+      <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="3" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>81</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I79" s="2" cm="1">
         <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
@@ -4861,26 +5269,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="2"/>
-      <c r="D80" s="2" t="s">
-        <v>73</v>
-      </c>
+      <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="3" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I80" s="2" cm="1">
         <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4897,7 +5303,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>8</v>
@@ -4906,17 +5312,17 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="I81" s="2" cm="1">
         <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J81" s="2"/>
       <c r="K81" s="2" t="s">
@@ -4929,7 +5335,7 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>8</v>
@@ -4938,17 +5344,17 @@
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="3" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I82" s="2" cm="1">
         <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
@@ -4961,7 +5367,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>8</v>
@@ -4970,17 +5376,17 @@
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
       <c r="F83" s="3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I83" s="2" cm="1">
         <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J83" s="2"/>
       <c r="K83" s="2" t="s">
@@ -4991,24 +5397,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
+      <c r="D84" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="E84" s="2"/>
       <c r="F84" s="3" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I84" s="2" cm="1">
         <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5023,28 +5431,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
+      <c r="D85" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="E85" s="2"/>
       <c r="F85" s="3" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I85" s="2" cm="1">
         <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -5055,28 +5465,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
+      <c r="D86" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="E86" s="2"/>
       <c r="F86" s="3" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I86" s="2" cm="1">
         <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
@@ -5087,28 +5499,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
+      <c r="D87" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="E87" s="2"/>
       <c r="F87" s="3" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I87" s="2" cm="1">
         <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
@@ -5119,53 +5533,77 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
+      <c r="D88" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2" t="str" cm="1">
+      <c r="F88" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I88" s="2" cm="1">
         <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
+      <c r="K88" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
+      <c r="M88" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
+      <c r="D89" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2" t="str" cm="1">
+      <c r="F89" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I89" s="2" cm="1">
         <f t="array" ref="I89">_xlfn.SWITCH(H89,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
+      <c r="K89" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
+      <c r="M89" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>8</v>
@@ -5173,21 +5611,31 @@
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2" t="str" cm="1">
+      <c r="F90" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I90" s="2" cm="1">
         <f t="array" ref="I90">_xlfn.SWITCH(H90,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
+      <c r="K90" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
+      <c r="M90" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>8</v>
@@ -5195,21 +5643,31 @@
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2" t="str" cm="1">
+      <c r="F91" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I91" s="2" cm="1">
         <f t="array" ref="I91">_xlfn.SWITCH(H91,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
+      <c r="K91" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
+      <c r="M91" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>8</v>
@@ -5217,21 +5675,31 @@
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2" t="str" cm="1">
+      <c r="F92" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I92" s="2" cm="1">
         <f t="array" ref="I92">_xlfn.SWITCH(H92,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
+      <c r="K92" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
+      <c r="M92" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>8</v>
@@ -5239,65 +5707,99 @@
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2" t="str" cm="1">
+      <c r="F93" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I93" s="2" cm="1">
         <f t="array" ref="I93">_xlfn.SWITCH(H93,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
+      <c r="K93" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M93" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
+      <c r="D94" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2" t="str" cm="1">
+      <c r="F94" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I94" s="2" cm="1">
         <f t="array" ref="I94">_xlfn.SWITCH(H94,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>8</v>
       </c>
       <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
+      <c r="K94" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M94" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
+      <c r="D95" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2" t="str" cm="1">
+      <c r="F95" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I95" s="2" cm="1">
         <f t="array" ref="I95">_xlfn.SWITCH(H95,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
+      <c r="K95" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
+      <c r="M95" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>8</v>
@@ -5305,17 +5807,417 @@
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2" t="str" cm="1">
+      <c r="F96" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I96" s="2" cm="1">
         <f t="array" ref="I96">_xlfn.SWITCH(H96,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>87</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I97" s="2" cm="1">
+        <f t="array" ref="I97">_xlfn.SWITCH(H97,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L97" s="2"/>
+      <c r="M97" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>88</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I98" s="2" cm="1">
+        <f t="array" ref="I98">_xlfn.SWITCH(H98,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>89</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I99" s="2" cm="1">
+        <f t="array" ref="I99">_xlfn.SWITCH(H99,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>90</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I100" s="2" cm="1">
+        <f t="array" ref="I100">_xlfn.SWITCH(H100,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>91</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I101" s="2" cm="1">
+        <f t="array" ref="I101">_xlfn.SWITCH(H101,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>92</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I102" s="2" cm="1">
+        <f t="array" ref="I102">_xlfn.SWITCH(H102,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>93</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2" t="str" cm="1">
+        <f t="array" ref="I103">_xlfn.SWITCH(H103,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+      <c r="M103" s="2"/>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>94</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2" t="str" cm="1">
+        <f t="array" ref="I104">_xlfn.SWITCH(H104,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+      <c r="M104" s="2"/>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>95</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="2"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2" t="str" cm="1">
+        <f t="array" ref="I105">_xlfn.SWITCH(H105,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+      <c r="M105" s="2"/>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>96</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2" t="str" cm="1">
+        <f t="array" ref="I106">_xlfn.SWITCH(H106,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+      <c r="M106" s="2"/>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>97</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2" t="str" cm="1">
+        <f t="array" ref="I107">_xlfn.SWITCH(H107,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+      <c r="M107" s="2"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>98</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2" t="str" cm="1">
+        <f t="array" ref="I108">_xlfn.SWITCH(H108,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2"/>
+      <c r="M108" s="2"/>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>99</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2" t="str" cm="1">
+        <f t="array" ref="I109">_xlfn.SWITCH(H109,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J109" s="2"/>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+      <c r="M109" s="2"/>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>100</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2" t="str" cm="1">
+        <f t="array" ref="I110">_xlfn.SWITCH(H110,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>101</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2" t="str" cm="1">
+        <f t="array" ref="I111">_xlfn.SWITCH(H111,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
+      <c r="M111" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5376,7 +6278,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">

--- a/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5521A2C-7725-4591-B2AC-C7880A1D5B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01843D33-B61D-4A5C-884C-3CD6DA76C25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="159">
   <si>
     <t>Epic</t>
   </si>
@@ -1951,12 +1951,53 @@
       <t xml:space="preserve"> bottomNavTab (public access)</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HOW TO DECIDE WHO IS OWNER AND WHO IS RENTER?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="3"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1. entryIntent stored from Rent a Bike, List a Bike button press on Landing screen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="9" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2. Explicitly ask user whether he wants to micro2move as an owner or a renter (Primarily)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="7" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3. Can a renter be an owner later on, if we take number 2 as our approach?</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2010,6 +2051,38 @@
       <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="7" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -2080,7 +2153,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -2116,11 +2189,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2198,6 +2308,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2501,7 +2620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -4315,45 +4434,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
-        <v>25</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I52" s="2" cm="1">
-        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="52" spans="1:13" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="30"/>
     </row>
     <row r="53" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>8</v>
@@ -4366,17 +4466,17 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="3" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I53" s="2" cm="1">
         <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
@@ -4389,7 +4489,7 @@
     </row>
     <row r="54" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>8</v>
@@ -4402,7 +4502,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>81</v>
@@ -4423,25 +4523,25 @@
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="2">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>76</v>
@@ -4461,7 +4561,7 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>8</v>
@@ -4474,7 +4574,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>80</v>
@@ -4497,7 +4597,7 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>8</v>
@@ -4510,17 +4610,17 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I57" s="2" cm="1">
         <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
@@ -4533,7 +4633,7 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>8</v>
@@ -4546,7 +4646,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>81</v>
@@ -4569,7 +4669,7 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>8</v>
@@ -4582,7 +4682,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>81</v>
@@ -4605,7 +4705,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>8</v>
@@ -4618,7 +4718,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>81</v>
@@ -4641,7 +4741,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>8</v>
@@ -4654,7 +4754,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>81</v>
@@ -4677,7 +4777,7 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>8</v>
@@ -4690,17 +4790,17 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="3" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>81</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I62" s="2" cm="1">
         <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
@@ -4713,7 +4813,7 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>8</v>
@@ -4726,7 +4826,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>81</v>
@@ -4749,7 +4849,7 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>8</v>
@@ -4762,17 +4862,17 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="3" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I64" s="2" cm="1">
         <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
@@ -4785,7 +4885,7 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>8</v>
@@ -4798,17 +4898,17 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I65" s="2" cm="1">
         <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
@@ -4821,16 +4921,20 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
+      <c r="C66" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="E66" s="2"/>
       <c r="F66" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>81</v>
@@ -4853,7 +4957,7 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>8</v>
@@ -4862,7 +4966,7 @@
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>81</v>
@@ -4885,7 +4989,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>8</v>
@@ -4894,7 +4998,7 @@
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>81</v>
@@ -4915,9 +5019,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>8</v>
@@ -4926,7 +5030,7 @@
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>81</v>
@@ -4947,9 +5051,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>8</v>
@@ -4958,7 +5062,7 @@
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>81</v>
@@ -4979,9 +5083,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>8</v>
@@ -4990,7 +5094,7 @@
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>81</v>
@@ -5011,30 +5115,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="2"/>
-      <c r="D72" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I72" s="2" cm="1">
         <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
@@ -5047,26 +5149,28 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
+      <c r="D73" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="E73" s="2"/>
       <c r="F73" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I73" s="2" cm="1">
         <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
@@ -5079,7 +5183,7 @@
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>8</v>
@@ -5088,7 +5192,7 @@
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>81</v>
@@ -5111,7 +5215,7 @@
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>8</v>
@@ -5120,7 +5224,7 @@
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>81</v>
@@ -5143,7 +5247,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>8</v>
@@ -5152,7 +5256,7 @@
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>81</v>
@@ -5175,7 +5279,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>8</v>
@@ -5184,7 +5288,7 @@
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>81</v>
@@ -5207,7 +5311,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>8</v>
@@ -5216,7 +5320,7 @@
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>81</v>
@@ -5239,7 +5343,7 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>8</v>
@@ -5248,7 +5352,7 @@
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>81</v>
@@ -5271,7 +5375,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>8</v>
@@ -5280,7 +5384,7 @@
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>81</v>
@@ -5303,7 +5407,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>8</v>
@@ -5312,7 +5416,7 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>81</v>
@@ -5335,7 +5439,7 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>8</v>
@@ -5344,7 +5448,7 @@
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>81</v>
@@ -5367,7 +5471,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>8</v>
@@ -5376,7 +5480,7 @@
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
       <c r="F83" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>81</v>
@@ -5397,30 +5501,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="2"/>
-      <c r="D84" s="2" t="s">
-        <v>116</v>
-      </c>
+      <c r="D84" s="2"/>
       <c r="E84" s="2"/>
       <c r="F84" s="3" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I84" s="2" cm="1">
         <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J84" s="2"/>
       <c r="K84" s="2" t="s">
@@ -5431,30 +5533,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" s="3" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I85" s="2" cm="1">
         <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J85" s="2"/>
       <c r="K85" s="2" t="s">
@@ -5465,30 +5567,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="3" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I86" s="2" cm="1">
         <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2" t="s">
@@ -5499,30 +5601,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" s="3" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I87" s="2" cm="1">
         <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J87" s="2"/>
       <c r="K87" s="2" t="s">
@@ -5533,30 +5635,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I88" s="2" cm="1">
         <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
@@ -5567,30 +5669,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="3" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I89" s="2" cm="1">
         <f t="array" ref="I89">_xlfn.SWITCH(H89,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
@@ -5603,26 +5705,28 @@
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
+      <c r="D90" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="E90" s="2"/>
       <c r="F90" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I90" s="2" cm="1">
         <f t="array" ref="I90">_xlfn.SWITCH(H90,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2" t="s">
@@ -5635,7 +5739,7 @@
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>8</v>
@@ -5644,7 +5748,7 @@
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>81</v>
@@ -5667,7 +5771,7 @@
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>8</v>
@@ -5676,7 +5780,7 @@
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>81</v>
@@ -5699,7 +5803,7 @@
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>8</v>
@@ -5708,7 +5812,7 @@
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>81</v>
@@ -5729,30 +5833,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="2"/>
-      <c r="D94" s="2" t="s">
-        <v>123</v>
-      </c>
+      <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="3" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I94" s="2" cm="1">
         <f t="array" ref="I94">_xlfn.SWITCH(H94,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
@@ -5765,28 +5867,28 @@
     </row>
     <row r="95" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" s="3" t="s">
-        <v>124</v>
+        <v>88</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I95" s="2" cm="1">
         <f t="array" ref="I95">_xlfn.SWITCH(H95,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
@@ -5797,28 +5899,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
+      <c r="D96" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="E96" s="2"/>
       <c r="F96" s="3" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I96" s="2" cm="1">
         <f t="array" ref="I96">_xlfn.SWITCH(H96,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
@@ -5831,7 +5935,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>8</v>
@@ -5840,17 +5944,17 @@
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
       <c r="F97" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I97" s="2" cm="1">
         <f t="array" ref="I97">_xlfn.SWITCH(H97,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J97" s="2"/>
       <c r="K97" s="2" t="s">
@@ -5863,7 +5967,7 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>8</v>
@@ -5872,7 +5976,7 @@
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
       <c r="F98" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>11</v>
@@ -5895,7 +5999,7 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>8</v>
@@ -5904,7 +6008,7 @@
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>11</v>
@@ -5927,7 +6031,7 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>8</v>
@@ -5936,7 +6040,7 @@
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
       <c r="F100" s="3" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>11</v>
@@ -5957,9 +6061,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>8</v>
@@ -5968,17 +6072,17 @@
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
       <c r="F101" s="3" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I101" s="2" cm="1">
         <f t="array" ref="I101">_xlfn.SWITCH(H101,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J101" s="2"/>
       <c r="K101" s="2" t="s">
@@ -5989,9 +6093,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>8</v>
@@ -6000,17 +6104,17 @@
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="3" t="s">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I102" s="2" cm="1">
         <f t="array" ref="I102">_xlfn.SWITCH(H102,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J102" s="2"/>
       <c r="K102" s="2" t="s">
@@ -6023,7 +6127,7 @@
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>8</v>
@@ -6031,21 +6135,31 @@
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2" t="str" cm="1">
+      <c r="F103" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I103" s="2" cm="1">
         <f t="array" ref="I103">_xlfn.SWITCH(H103,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
+      <c r="K103" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="L103" s="2"/>
-      <c r="M103" s="2"/>
+      <c r="M103" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>8</v>
@@ -6067,7 +6181,7 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>8</v>
@@ -6089,7 +6203,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>8</v>
@@ -6111,7 +6225,7 @@
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>8</v>
@@ -6133,7 +6247,7 @@
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>8</v>
@@ -6155,7 +6269,7 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>8</v>
@@ -6177,7 +6291,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>8</v>
@@ -6199,7 +6313,7 @@
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>8</v>
@@ -6219,7 +6333,32 @@
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
     </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>101</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2" t="str" cm="1">
+        <f t="array" ref="I112">_xlfn.SWITCH(H112,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="2"/>
+      <c r="M112" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A52:M52"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01843D33-B61D-4A5C-884C-3CD6DA76C25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267BC00F-ED1C-46B1-B9B4-3B1096F610EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="141">
   <si>
     <t>Epic</t>
   </si>
@@ -156,148 +156,13 @@
     <t>Landing Screen</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Pressing on the explore hyperlink should navigate the user to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ExploreMaps</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Unlogged in users should be navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">SignIn </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screen upon pressing any button</t>
-    </r>
-  </si>
-  <si>
     <t>Story Point</t>
   </si>
   <si>
-    <t>Preserve entry intent (Rent/List)</t>
-  </si>
-  <si>
-    <t>Handle navigation from Landing → Sign In</t>
-  </si>
-  <si>
-    <t>Sign in Screen</t>
-  </si>
-  <si>
-    <t>Handle loading state</t>
-  </si>
-  <si>
-    <t>Handle successful login response</t>
-  </si>
-  <si>
-    <t>Handle invalid credentials error</t>
-  </si>
-  <si>
-    <t>Set correct bottom nav tab</t>
-  </si>
-  <si>
     <t>Detect entry intent (Rent/List)</t>
   </si>
   <si>
-    <t>Detect user role (Owner/Renter)</t>
-  </si>
-  <si>
     <t>Show personalized welcome note</t>
-  </si>
-  <si>
-    <t>Detect logged-in user state</t>
-  </si>
-  <si>
-    <t>Handle Rent button press → RenterE-BikeBookingFilter screen</t>
-  </si>
-  <si>
-    <t>Handle List button press → First time Listing? → OwnerE-BikeListing screen</t>
-  </si>
-  <si>
-    <t>Handle List button press → Existing lister? → OwnerExistingE-BikesList screen</t>
-  </si>
-  <si>
-    <t>Skip Sign In screen</t>
-  </si>
-  <si>
-    <t>Preserve bottom navigation state:
-Owner: My Bikes
-Renter: my Rides</t>
-  </si>
-  <si>
-    <t>Persist Explore tab selection</t>
-  </si>
-  <si>
-    <t>Create Explore screen shell</t>
-  </si>
-  <si>
-    <t>Handle Explore link from Landing</t>
-  </si>
-  <si>
-    <t>Handle Explore bottom nav selection</t>
-  </si>
-  <si>
-    <t>Allow guest access</t>
-  </si>
-  <si>
-    <t>Block navigation for Profile</t>
-  </si>
-  <si>
-    <t>Detect auth state on tab press</t>
-  </si>
-  <si>
-    <t>Block navigation for My Rides</t>
-  </si>
-  <si>
-    <t>Block navigation for My Bikes</t>
-  </si>
-  <si>
-    <t>Redirect to Sign In screen</t>
-  </si>
-  <si>
-    <t>Preserve target tab intent</t>
-  </si>
-  <si>
-    <t>After login → redirect to intended tab</t>
-  </si>
-  <si>
-    <t>Explore-guest</t>
   </si>
   <si>
     <t>Show inline errors</t>
@@ -471,32 +336,6 @@
   </si>
   <si>
     <t>Brand values text is displayed on splash screen: "Affordable Reliable Safe"</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Landing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen after splash timeout</t>
-    </r>
   </si>
   <si>
     <t>Atish</t>
@@ -875,223 +714,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Pressing </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Rent a Bike </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>button stores entryIntent = RENT</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Pressing </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List a Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button stores entryIntent = LIST</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Guest user is navigated to SignIn upon pressing </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rent a Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List a Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Signed-in user is navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EntryResolver</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> upon pressing </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Rent a Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>List a Bike</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button</t>
-    </r>
-  </si>
-  <si>
-    <t>Create navigation stack</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Pressing on </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Create reusable UI elements package: </t>
     </r>
     <r>
@@ -1502,79 +1124,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerE-BikeListing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerExistingE-BikesList</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Add entryResolve logic for separating renter, lister(owner) based on </t>
     </r>
     <r>
@@ -1604,9 +1153,6 @@
   </si>
   <si>
     <t>Sign In screen renders without crashing</t>
-  </si>
-  <si>
-    <t>Pressing Sign In calls Signin() with email and password</t>
   </si>
   <si>
     <t>Manage local form state (email, password)</t>
@@ -1618,33 +1164,6 @@
   <si>
     <t>1. Prevent multiple submissions
 2. Implement loading state while login is underway</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. On successful sign in, update authStatus = AUTHENTICATED
-2. Navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">EntryResolver </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>if sign in was successful</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1703,43 +1222,6 @@
 1. Button- testID = "SignInButton"</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Reset local form state on unmount (navigating away anywhere from Sign in):
-1. Email: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>const [email, setEmail] = useState('');</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. Password: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>const [password, setPassword] = useState('');</t>
-    </r>
-  </si>
-  <si>
     <t>1. Email input is visible
 2. Password input is visible
 3. Sign In button is visible
@@ -1751,46 +1233,6 @@
 3. Sign In button is enabled when both fields are filled</t>
   </si>
   <si>
-    <t>1. Multiple rapid presses do not trigger multiple signin calls
-2. Loading indicator is shown during login attempt</t>
-  </si>
-  <si>
-    <t>1. Successful login updates authStatus to AUTHENTICATED
-2. Successful login navigates to EntryResolver
-3. entryIntent is preserved after login</t>
-  </si>
-  <si>
-    <t>1. Failed login shows error message
-2. Failed login does NOT update authStatus
-3. Failed login does NOT navigate</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Pressing </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink navigates to Sign Up screen layout</t>
-    </r>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">1. Create </t>
     </r>
@@ -1905,6 +1347,400 @@
     </r>
   </si>
   <si>
+    <t>On successful sign in, update authStatus = AUTHENTICATED</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Reset local form state on unmount (after navigating away anywhere from Sign in):
+1. Email: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>const [email, setEmail] = useState('');</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Password: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>const [password, setPassword] = useState('');</t>
+    </r>
+  </si>
+  <si>
+    <t>Post-landing Navigation</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Rent a Bike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>button calls a mockFunction()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">List a Bike </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>button calls a mockFunction()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hyperlink calls a mockFunction()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button calls a mockFunction()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Login attempt with invalid credentials show error message:
+1. For wrong email: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Email does not exist
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>For wrong password:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Incorrect password, Try again.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Landing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen after splash timeout (MANUAL/e2e TESTING)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink:
+1. Calls a mockFunction()
+2. navigates to Sign Up screen layout (MANUAL/e2e TESTING)</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Multiple rapid presses do not trigger multiple signin calls (MANUAL/e2e TESTING)
+2. Loading indicator is shown during login attempt (MANUAL/e2e TESTING)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = UNAUTHENTICATED and entryIntent = LIST/RENT/NULL
+1. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">SignIn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = UNAUTHENTICATED, pressing Rent a Bike or List a Bike button navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SignIn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> page</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Pressing </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink
+1. Navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ExploreMaps</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout (MANUAL/e2e TESTING)
+2. Activates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab (MANUAL/e2e TESTING)</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Handle </t>
     </r>
@@ -1927,13 +1763,90 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> hyperlink click → navigate to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve"> hyperlink press with onPress</t>
+    </r>
+  </si>
+  <si>
+    <t>Explore</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create navigation stack with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>expo-router</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (file-based routing):
+app/
+ |-- _layout.tsx
+ |-- splash.tsx
+ |-- landing.tsx
+ |-- (auth)/
+ │   |-- signin.tsx
+ │   |-- signup.tsx
+ |-- (tabs)/
+ │   |-- _layout.tsx
+ │
+ │   |-- explore.tsx
+ │
+ │   |-- my-rides/
+ │   │   |-- _layout.tsx
+ │   │   |-- index.tsx
+ │   │   └─ filter.tsx
+ │
+ │   |-- my-bikes/
+ │   │   |-- _layout.tsx
+ │   │   |-- index.tsx
+ │   │   └─ list.tsx
+ │
+ │   |-- profile.tsx</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED or UNAUTHENTICATED:
+1. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ExploreMaps</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout
+2. Activate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1943,53 +1856,706 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab (public access)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">HOW TO DECIDE WHO IS OWNER AND WHO IS RENTER?
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab (guest access)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, tapping on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tabs should navigate the user to the respective screens</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = UNAUTHENTICATED, if user presses any other tab
+1. Block navigation for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Profile
 </t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="3"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1. entryIntent stored from Rent a Bike, List a Bike button press on Landing screen
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2. Store tab pressing intent of user in context </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tabIntent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = RIDES, BIKES, PROFILE and share globally
+3. navigate the user to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SignIn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>After successful login (if user's authStatus = UNAUTHENTICATED) redirect to the intended tab, based on tabIntent</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen render
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bottomNavTabs render with Explore tab active (MANUAL/e2e TESTING)</t>
+    </r>
+  </si>
+  <si>
+    <t>All tab icons press call mockFunction()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If user's authStatus = UNAUTHENTICATED
 </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="16"/>
-        <color theme="9" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">2. Explicitly ask user whether he wants to micro2move as an owner or a renter (Primarily)
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tabs are not pressable (MANUAL/e2e TESTING)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED and entryIntent = RENT:
+1. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeFilter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen
+2. Show "Welcome Username" as heading of the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+3. Activate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED and entryIntent = LIST:
+1. Navigate to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OwnerE-BikeBooking </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen
+2. Show "Welcome Username" as heading of the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerE-BikeListing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+3. Activate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, pressing Rent a Bike button:
+1. Navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeFilter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen
+2. Activates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, pressing List a Bike button:
+1. Navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OwnerE-BikeListing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen
+2. Activates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Routing logic works with tabs mapped to correct screens:
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - RenterE-BikeFilter
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -  OwnerE-BikeListing
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - ExploreMaps</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="7" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3. Can a renter be an owner later on, if we take number 2 as our approach?</t>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Profile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Profile</t>
     </r>
   </si>
 </sst>
@@ -1997,7 +2563,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2053,39 +2619,27 @@
       <family val="3"/>
     </font>
     <font>
-      <b/>
-      <sz val="26"/>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="3"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color theme="9" tint="-0.499984740745262"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="7" tint="-0.499984740745262"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2152,8 +2706,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2189,48 +2767,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2309,14 +2850,32 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2620,15 +3179,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="82" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -2641,7 +3200,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -2653,7 +3212,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>3</v>
@@ -2665,7 +3224,7 @@
         <v>31</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>5</v>
@@ -2688,16 +3247,16 @@
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="20" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="I2" s="20" cm="1">
         <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2720,16 +3279,16 @@
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="I3" s="20" cm="1">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2752,16 +3311,16 @@
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
       <c r="E4" s="20" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I4" s="20" cm="1">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2784,16 +3343,16 @@
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="I5" s="12" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2816,16 +3375,16 @@
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I6" s="12" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2848,16 +3407,16 @@
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I7" s="12" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2873,21 +3432,23 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
+      <c r="A8" s="12">
+        <v>7</v>
+      </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I8" s="12" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2903,21 +3464,23 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
+      <c r="A9" s="12">
+        <v>8</v>
+      </c>
       <c r="B9" s="12"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="12" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="I9" s="12" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2932,24 +3495,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A10" s="22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10" s="22"/>
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="I10" s="22" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -2964,26 +3527,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
+    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="22">
+        <v>9</v>
+      </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="I11" s="22" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J11" s="22"/>
       <c r="K11" s="22" t="s">
@@ -2996,22 +3561,22 @@
     </row>
     <row r="12" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" s="22">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B12" s="22"/>
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="I12" s="22" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3028,7 +3593,7 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>8</v>
@@ -3040,16 +3605,16 @@
         <v>9</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I13" s="7" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3066,7 +3631,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>8</v>
@@ -3078,16 +3643,16 @@
         <v>9</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I14" s="7" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3104,7 +3669,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>8</v>
@@ -3116,16 +3681,16 @@
         <v>9</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I15" s="7" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3142,7 +3707,7 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>8</v>
@@ -3154,16 +3719,16 @@
         <v>9</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I16" s="7" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3180,7 +3745,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>8</v>
@@ -3192,16 +3757,16 @@
         <v>9</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I17" s="7" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3214,7 +3779,7 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>8</v>
@@ -3226,16 +3791,16 @@
         <v>9</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I18" s="7" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3248,7 +3813,7 @@
     </row>
     <row r="19" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>8</v>
@@ -3260,16 +3825,16 @@
         <v>9</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>11</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I19" s="10" cm="1">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3286,7 +3851,7 @@
     </row>
     <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>8</v>
@@ -3298,16 +3863,16 @@
         <v>9</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>11</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I20" s="10" cm="1">
         <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3324,7 +3889,7 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14">
@@ -3334,16 +3899,16 @@
         <v>32</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I21" s="14" cm="1">
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3360,7 +3925,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14">
@@ -3370,16 +3935,16 @@
         <v>32</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I22" s="14" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3396,7 +3961,7 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14">
@@ -3406,16 +3971,16 @@
         <v>32</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I23" s="14" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3432,7 +3997,7 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B24" s="14"/>
       <c r="C24" s="14">
@@ -3442,16 +4007,16 @@
         <v>32</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I24" s="14" cm="1">
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3468,7 +4033,7 @@
     </row>
     <row r="25" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B25" s="14"/>
       <c r="C25" s="14">
@@ -3478,16 +4043,16 @@
         <v>32</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I25" s="14" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3503,7 +4068,9 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
+      <c r="A26" s="14">
+        <v>25</v>
+      </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14">
         <v>1.2</v>
@@ -3512,16 +4079,16 @@
         <v>32</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I26" s="14" cm="1">
         <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3537,7 +4104,9 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
+      <c r="A27" s="14">
+        <v>26</v>
+      </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14">
         <v>1.2</v>
@@ -3546,16 +4115,16 @@
         <v>32</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I27" s="14" cm="1">
         <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3570,8 +4139,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="14">
+        <v>29</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14">
         <v>1.2</v>
@@ -3580,16 +4151,16 @@
         <v>32</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I28" s="14" cm="1">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3604,77 +4175,85 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14">
+    <row r="29" spans="1:13" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A29" s="15">
+        <v>30</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="15">
         <v>1.2</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="I29" s="14" cm="1">
+      <c r="E29" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" s="15" cm="1">
         <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14" t="s">
+      <c r="J29" s="15"/>
+      <c r="K29" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14">
+      <c r="A30" s="15">
+        <v>31</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="15">
         <v>1.2</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="H30" s="14" t="s">
+      <c r="E30" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I30" s="14" cm="1">
+      <c r="G30" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="15" cm="1">
         <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="J30" s="15"/>
+      <c r="K30" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="15">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>8</v>
@@ -3686,20 +4265,20 @@
         <v>32</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="G31" s="15" t="s">
         <v>11</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="I31" s="15" cm="1">
         <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="15"/>
       <c r="K31" s="15" t="s">
@@ -3712,7 +4291,7 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="15">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>8</v>
@@ -3724,16 +4303,16 @@
         <v>32</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="G32" s="15" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I32" s="15" cm="1">
         <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3748,82 +4327,86 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="15">
-        <v>24</v>
-      </c>
-      <c r="B33" s="15" t="s">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="24">
+        <v>34</v>
+      </c>
+      <c r="B33" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="15">
-        <v>1.2</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="15" t="s">
+      <c r="C33" s="24">
+        <v>1.3</v>
+      </c>
+      <c r="D33" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="F33" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="I33" s="15" cm="1">
+      <c r="E33" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="I33" s="24" cm="1">
         <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="24">
+        <v>35</v>
+      </c>
+      <c r="B34" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="15">
-        <v>1.2</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" s="15" t="s">
+      <c r="C34" s="24">
+        <v>1.3</v>
+      </c>
+      <c r="D34" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="G34" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I34" s="15" cm="1">
+      <c r="E34" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G34" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" s="24" cm="1">
         <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="24"/>
+        <v>1</v>
+      </c>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="24">
+        <v>36</v>
+      </c>
       <c r="B35" s="24" t="s">
         <v>8</v>
       </c>
@@ -3831,23 +4414,23 @@
         <v>1.3</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="I35" s="24" cm="1">
         <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="24"/>
       <c r="K35" s="24" t="s">
@@ -3858,8 +4441,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="24"/>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="24">
+        <v>37</v>
+      </c>
       <c r="B36" s="24" t="s">
         <v>8</v>
       </c>
@@ -3867,23 +4452,23 @@
         <v>1.3</v>
       </c>
       <c r="D36" s="24" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="G36" s="24" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H36" s="24" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="I36" s="24" cm="1">
         <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="24"/>
       <c r="K36" s="24" t="s">
@@ -3895,7 +4480,9 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="24"/>
+      <c r="A37" s="24">
+        <v>38</v>
+      </c>
       <c r="B37" s="24" t="s">
         <v>8</v>
       </c>
@@ -3903,19 +4490,19 @@
         <v>1.3</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I37" s="24" cm="1">
         <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3930,8 +4517,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="24"/>
+    <row r="38" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="24">
+        <v>40</v>
+      </c>
       <c r="B38" s="24" t="s">
         <v>8</v>
       </c>
@@ -3939,23 +4528,23 @@
         <v>1.3</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="I38" s="24" cm="1">
         <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" s="24"/>
       <c r="K38" s="24" t="s">
@@ -3966,8 +4555,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="24"/>
+    <row r="39" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="24">
+        <v>41</v>
+      </c>
       <c r="B39" s="24" t="s">
         <v>8</v>
       </c>
@@ -3975,19 +4566,19 @@
         <v>1.3</v>
       </c>
       <c r="D39" s="24" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="G39" s="24" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I39" s="24" cm="1">
         <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4002,116 +4593,124 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24" t="s">
+    <row r="40" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A40" s="26">
+        <v>42</v>
+      </c>
+      <c r="B40" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="26">
         <v>1.3</v>
       </c>
-      <c r="D40" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E40" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="F40" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="G40" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="H40" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="I40" s="24" cm="1">
+      <c r="D40" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="G40" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I40" s="26" cm="1">
         <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J40" s="24"/>
-      <c r="K40" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="26">
+        <v>43</v>
+      </c>
+      <c r="B41" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="26">
         <v>1.3</v>
       </c>
-      <c r="D41" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E41" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="G41" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="H41" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="I41" s="24" cm="1">
+      <c r="D41" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F41" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I41" s="26" cm="1">
         <f t="array" ref="I41">_xlfn.SWITCH(H41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="L41" s="24"/>
-      <c r="M41" s="24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="24"/>
-      <c r="B42" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="26">
+        <v>44</v>
+      </c>
+      <c r="B42" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="24">
+      <c r="C42" s="26">
         <v>1.3</v>
       </c>
-      <c r="D42" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="E42" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="F42" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="G42" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="H42" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="I42" s="24" cm="1">
+      <c r="D42" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E42" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G42" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I42" s="26" cm="1">
         <f t="array" ref="I42">_xlfn.SWITCH(H42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J42" s="24"/>
-      <c r="K42" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="L42" s="24"/>
-      <c r="M42" s="24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A43" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="26">
+        <v>45</v>
+      </c>
       <c r="B43" s="26" t="s">
         <v>8</v>
       </c>
@@ -4119,19 +4718,19 @@
         <v>1.3</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>11</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="I43" s="26" cm="1">
         <f t="array" ref="I43">_xlfn.SWITCH(H43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4146,8 +4745,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="26"/>
+    <row r="44" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A44" s="26">
+        <v>46</v>
+      </c>
       <c r="B44" s="26" t="s">
         <v>8</v>
       </c>
@@ -4155,19 +4756,19 @@
         <v>1.3</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>11</v>
       </c>
       <c r="H44" s="26" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I44" s="26" cm="1">
         <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4183,7 +4784,9 @@
       </c>
     </row>
     <row r="45" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A45" s="26"/>
+      <c r="A45" s="26">
+        <v>47</v>
+      </c>
       <c r="B45" s="26" t="s">
         <v>8</v>
       </c>
@@ -4191,19 +4794,19 @@
         <v>1.3</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>11</v>
       </c>
       <c r="H45" s="26" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I45" s="26" cm="1">
         <f t="array" ref="I45">_xlfn.SWITCH(H45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4218,8 +4821,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="26"/>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="26">
+        <v>48</v>
+      </c>
       <c r="B46" s="26" t="s">
         <v>8</v>
       </c>
@@ -4227,23 +4832,23 @@
         <v>1.3</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>11</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="I46" s="26" cm="1">
         <f t="array" ref="I46">_xlfn.SWITCH(H46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" s="26"/>
       <c r="K46" s="26" t="s">
@@ -4254,8 +4859,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="26"/>
+    <row r="47" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="26">
+        <v>49</v>
+      </c>
       <c r="B47" s="26" t="s">
         <v>8</v>
       </c>
@@ -4263,23 +4870,23 @@
         <v>1.3</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="G47" s="26" t="s">
         <v>11</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="I47" s="26" cm="1">
         <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J47" s="26"/>
       <c r="K47" s="26" t="s">
@@ -4290,8 +4897,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="26"/>
+    <row r="48" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="26">
+        <v>50</v>
+      </c>
       <c r="B48" s="26" t="s">
         <v>8</v>
       </c>
@@ -4299,19 +4908,19 @@
         <v>1.3</v>
       </c>
       <c r="D48" s="26" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F48" s="27" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>11</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I48" s="26" cm="1">
         <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4326,549 +4935,552 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="26"/>
-      <c r="B49" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D49" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E49" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="F49" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="G49" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H49" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="I49" s="26" cm="1">
+    <row r="49" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="28"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28">
+        <v>1.4</v>
+      </c>
+      <c r="D49" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F49" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="G49" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H49" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I49" s="28" cm="1">
         <f t="array" ref="I49">_xlfn.SWITCH(H49,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="L49" s="26"/>
-      <c r="M49" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="26"/>
-      <c r="B50" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D50" s="26" t="s">
+      <c r="J49" s="28"/>
+      <c r="K49" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="28"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28">
+        <v>1.4</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F50" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="F50" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="G50" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H50" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="I50" s="26" cm="1">
+      <c r="G50" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H50" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I50" s="28" cm="1">
         <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="L50" s="26"/>
-      <c r="M50" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="26"/>
-      <c r="B51" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D51" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="F51" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="G51" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H51" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="I51" s="26" cm="1">
+        <v>2</v>
+      </c>
+      <c r="J50" s="28"/>
+      <c r="K50" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="28"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28">
+        <v>1.4</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="G51" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H51" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I51" s="28" cm="1">
         <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="99.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="30"/>
-    </row>
-    <row r="53" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
-        <v>25</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C53" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G53" s="2" t="s">
+      <c r="J51" s="28"/>
+      <c r="K51" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28">
+        <v>1.4</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="G52" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="H52" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I52" s="28" cm="1">
+        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30">
+        <v>1.4</v>
+      </c>
+      <c r="D53" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="G53" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I53" s="2" cm="1">
+      <c r="H53" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="I53" s="30" cm="1">
         <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
-        <v>26</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C54" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I54" s="2" cm="1">
+        <v>2</v>
+      </c>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="L53" s="30"/>
+      <c r="M53" s="30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30">
+        <v>1.4</v>
+      </c>
+      <c r="D54" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E54" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="G54" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="I54" s="30" cm="1">
         <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2" t="s">
+      <c r="J54" s="30"/>
+      <c r="K54" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="L54" s="30"/>
+      <c r="M54" s="30" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
-        <v>27</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I55" s="2" cm="1">
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30">
+        <v>1.4</v>
+      </c>
+      <c r="D55" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="G55" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H55" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="I55" s="30" cm="1">
         <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
-        <v>33</v>
-      </c>
-      <c r="B56" s="2" t="s">
+      <c r="J55" s="30"/>
+      <c r="K55" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="30">
+        <v>52</v>
+      </c>
+      <c r="B56" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C56" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I56" s="2" cm="1">
+      <c r="C56" s="30">
+        <v>1.4</v>
+      </c>
+      <c r="D56" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="G56" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="I56" s="30" cm="1">
         <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
-        <v>34</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I57" s="2" cm="1">
+      <c r="J56" s="30"/>
+      <c r="K56" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="L56" s="30"/>
+      <c r="M56" s="30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="35"/>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="D57" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E57" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="F57" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G57" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="H57" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="I57" s="35" cm="1">
         <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
-        <v>37</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I58" s="2" cm="1">
+      <c r="A58" s="35"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E58" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="F58" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="G58" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="H58" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="I58" s="35" cm="1">
         <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A59" s="2">
-        <v>38</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I59" s="2" cm="1">
+        <v>1</v>
+      </c>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="L58" s="35"/>
+      <c r="M58" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="35"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="D59" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E59" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="F59" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="G59" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="H59" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I59" s="35" cm="1">
         <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A60" s="2">
-        <v>39</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I60" s="2" cm="1">
+      <c r="J59" s="35"/>
+      <c r="K59" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="L59" s="35"/>
+      <c r="M59" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A60" s="35"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="E60" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="F60" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="G60" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="H60" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="I60" s="35" cm="1">
         <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L60" s="2"/>
-      <c r="M60" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A61" s="2">
-        <v>40</v>
-      </c>
-      <c r="B61" s="2" t="s">
+      <c r="J60" s="35"/>
+      <c r="K60" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="L60" s="35"/>
+      <c r="M60" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A61" s="33">
+        <v>58</v>
+      </c>
+      <c r="B61" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C61" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I61" s="2" cm="1">
+      <c r="C61" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E61" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="F61" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="I61" s="33" cm="1">
         <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L61" s="2"/>
-      <c r="M61" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A62" s="2">
-        <v>41</v>
-      </c>
-      <c r="B62" s="2" t="s">
+      <c r="J61" s="33"/>
+      <c r="K61" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="L61" s="33"/>
+      <c r="M61" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="33">
+        <v>63</v>
+      </c>
+      <c r="B62" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C62" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I62" s="2" cm="1">
+      <c r="C62" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="F62" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="G62" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="I62" s="33" cm="1">
         <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A63" s="2">
-        <v>42</v>
-      </c>
-      <c r="B63" s="2" t="s">
+      <c r="J62" s="33"/>
+      <c r="K62" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="L62" s="33"/>
+      <c r="M62" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="33">
+        <v>61</v>
+      </c>
+      <c r="B63" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C63" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I63" s="2" cm="1">
+      <c r="C63" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="D63" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E63" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="F63" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="G63" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="I63" s="33" cm="1">
         <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J63" s="33"/>
+      <c r="K63" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C64" s="2">
-        <v>1.3</v>
-      </c>
+      <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="3" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="I64" s="2" cm="1">
         <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4883,32 +5495,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="2">
-        <v>1.3</v>
-      </c>
+      <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="I65" s="2" cm="1">
         <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
@@ -4921,30 +5531,28 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C66" s="2">
-        <v>1.3</v>
-      </c>
+      <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="I66" s="2" cm="1">
         <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
@@ -4955,24 +5563,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
+      <c r="D67" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="E67" s="2"/>
       <c r="F67" s="3" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I67" s="2" cm="1">
         <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4987,28 +5597,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
+      <c r="D68" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="E68" s="2"/>
       <c r="F68" s="3" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="I68" s="2" cm="1">
         <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
@@ -5021,26 +5633,28 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
+      <c r="D69" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="E69" s="2"/>
       <c r="F69" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="I69" s="2" cm="1">
         <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
@@ -5051,9 +5665,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>8</v>
@@ -5062,13 +5676,13 @@
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="I70" s="2" cm="1">
         <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5085,7 +5699,7 @@
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>8</v>
@@ -5094,13 +5708,13 @@
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I71" s="2" cm="1">
         <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5115,9 +5729,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>8</v>
@@ -5126,13 +5740,13 @@
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I72" s="2" cm="1">
         <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5149,28 +5763,26 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="2"/>
-      <c r="D73" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="3" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="I73" s="2" cm="1">
         <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
@@ -5181,28 +5793,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
+      <c r="D74" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="E74" s="2"/>
       <c r="F74" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="I74" s="2" cm="1">
         <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
@@ -5213,24 +5827,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
+      <c r="D75" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E75" s="2"/>
       <c r="F75" s="3" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I75" s="2" cm="1">
         <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5247,7 +5863,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>8</v>
@@ -5256,17 +5872,17 @@
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="I76" s="2" cm="1">
         <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
@@ -5279,7 +5895,7 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>8</v>
@@ -5288,17 +5904,17 @@
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
       <c r="F77" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I77" s="2" cm="1">
         <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
@@ -5311,7 +5927,7 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>8</v>
@@ -5320,17 +5936,17 @@
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I78" s="2" cm="1">
         <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
@@ -5343,7 +5959,7 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>8</v>
@@ -5352,17 +5968,17 @@
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
       <c r="F79" s="3" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I79" s="2" cm="1">
         <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J79" s="2"/>
       <c r="K79" s="2" t="s">
@@ -5375,7 +5991,7 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>8</v>
@@ -5384,17 +6000,17 @@
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
       <c r="F80" s="3" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I80" s="2" cm="1">
         <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80" s="2"/>
       <c r="K80" s="2" t="s">
@@ -5405,9 +6021,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>8</v>
@@ -5416,13 +6032,13 @@
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
       <c r="F81" s="3" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="I81" s="2" cm="1">
         <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5439,7 +6055,7 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>8</v>
@@ -5448,17 +6064,17 @@
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
       <c r="F82" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I82" s="2" cm="1">
         <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2" t="s">
@@ -5471,7 +6087,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>8</v>
@@ -5479,31 +6095,21 @@
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I83" s="2" cm="1">
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2" t="str" cm="1">
         <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="J83" s="2"/>
-      <c r="K83" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="K83" s="2"/>
       <c r="L83" s="2"/>
-      <c r="M83" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="M83" s="2"/>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>8</v>
@@ -5511,235 +6117,153 @@
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I84" s="2" cm="1">
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2" t="str" cm="1">
         <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="J84" s="2"/>
-      <c r="K84" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="K84" s="2"/>
       <c r="L84" s="2"/>
-      <c r="M84" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="M84" s="2"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="2"/>
-      <c r="D85" s="2" t="s">
-        <v>116</v>
-      </c>
+      <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I85" s="2" cm="1">
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2" t="str" cm="1">
         <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="J85" s="2"/>
-      <c r="K85" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="K85" s="2"/>
       <c r="L85" s="2"/>
-      <c r="M85" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="M85" s="2"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="2"/>
-      <c r="D86" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I86" s="2" cm="1">
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2" t="str" cm="1">
         <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="J86" s="2"/>
-      <c r="K86" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="K86" s="2"/>
       <c r="L86" s="2"/>
-      <c r="M86" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="M86" s="2"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="2"/>
-      <c r="D87" s="2" t="s">
-        <v>117</v>
-      </c>
+      <c r="D87" s="2"/>
       <c r="E87" s="2"/>
-      <c r="F87" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I87" s="2" cm="1">
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2" t="str" cm="1">
         <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J87" s="2"/>
-      <c r="K87" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="K87" s="2"/>
       <c r="L87" s="2"/>
-      <c r="M87" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="M87" s="2"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="2"/>
-      <c r="D88" s="2" t="s">
-        <v>120</v>
-      </c>
+      <c r="D88" s="2"/>
       <c r="E88" s="2"/>
-      <c r="F88" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I88" s="2" cm="1">
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2" t="str" cm="1">
         <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="J88" s="2"/>
-      <c r="K88" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="K88" s="2"/>
       <c r="L88" s="2"/>
-      <c r="M88" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="M88" s="2"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="2"/>
-      <c r="D89" s="2" t="s">
-        <v>121</v>
-      </c>
+      <c r="D89" s="2"/>
       <c r="E89" s="2"/>
-      <c r="F89" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I89" s="2" cm="1">
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2" t="str" cm="1">
         <f t="array" ref="I89">_xlfn.SWITCH(H89,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="J89" s="2"/>
-      <c r="K89" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="K89" s="2"/>
       <c r="L89" s="2"/>
-      <c r="M89" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="M89" s="2"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="2"/>
-      <c r="D90" s="2" t="s">
-        <v>122</v>
-      </c>
+      <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I90" s="2" cm="1">
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2" t="str" cm="1">
         <f t="array" ref="I90">_xlfn.SWITCH(H90,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J90" s="2"/>
-      <c r="K90" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="K90" s="2"/>
       <c r="L90" s="2"/>
-      <c r="M90" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="M90" s="2"/>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>8</v>
@@ -5747,619 +6271,21 @@
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I91" s="2" cm="1">
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2" t="str" cm="1">
         <f t="array" ref="I91">_xlfn.SWITCH(H91,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="J91" s="2"/>
-      <c r="K91" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="K91" s="2"/>
       <c r="L91" s="2"/>
-      <c r="M91" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>78</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I92" s="2" cm="1">
-        <f t="array" ref="I92">_xlfn.SWITCH(H92,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <v>79</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I93" s="2" cm="1">
-        <f t="array" ref="I93">_xlfn.SWITCH(H93,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
-        <v>80</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I94" s="2" cm="1">
-        <f t="array" ref="I94">_xlfn.SWITCH(H94,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
-        <v>81</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I95" s="2" cm="1">
-        <f t="array" ref="I95">_xlfn.SWITCH(H95,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
-        <v>83</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H96" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I96" s="2" cm="1">
-        <f t="array" ref="I96">_xlfn.SWITCH(H96,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A97" s="2">
-        <v>86</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I97" s="2" cm="1">
-        <f t="array" ref="I97">_xlfn.SWITCH(H97,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L97" s="2"/>
-      <c r="M97" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
-        <v>87</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I98" s="2" cm="1">
-        <f t="array" ref="I98">_xlfn.SWITCH(H98,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L98" s="2"/>
-      <c r="M98" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
-        <v>88</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I99" s="2" cm="1">
-        <f t="array" ref="I99">_xlfn.SWITCH(H99,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L99" s="2"/>
-      <c r="M99" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A100" s="2">
-        <v>89</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I100" s="2" cm="1">
-        <f t="array" ref="I100">_xlfn.SWITCH(H100,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L100" s="2"/>
-      <c r="M100" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A101" s="2">
-        <v>90</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I101" s="2" cm="1">
-        <f t="array" ref="I101">_xlfn.SWITCH(H101,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L101" s="2"/>
-      <c r="M101" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A102" s="2">
-        <v>91</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I102" s="2" cm="1">
-        <f t="array" ref="I102">_xlfn.SWITCH(H102,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L102" s="2"/>
-      <c r="M102" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A103" s="2">
-        <v>92</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I103" s="2" cm="1">
-        <f t="array" ref="I103">_xlfn.SWITCH(H103,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L103" s="2"/>
-      <c r="M103" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A104" s="2">
-        <v>93</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2" t="str" cm="1">
-        <f t="array" ref="I104">_xlfn.SWITCH(H104,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
-      <c r="M104" s="2"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A105" s="2">
-        <v>94</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2" t="str" cm="1">
-        <f t="array" ref="I105">_xlfn.SWITCH(H105,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
-      <c r="L105" s="2"/>
-      <c r="M105" s="2"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A106" s="2">
-        <v>95</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2" t="str" cm="1">
-        <f t="array" ref="I106">_xlfn.SWITCH(H106,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
-      <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A107" s="2">
-        <v>96</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2" t="str" cm="1">
-        <f t="array" ref="I107">_xlfn.SWITCH(H107,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
-      <c r="L107" s="2"/>
-      <c r="M107" s="2"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A108" s="2">
-        <v>97</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2" t="str" cm="1">
-        <f t="array" ref="I108">_xlfn.SWITCH(H108,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
-      <c r="L108" s="2"/>
-      <c r="M108" s="2"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A109" s="2">
-        <v>98</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2" t="str" cm="1">
-        <f t="array" ref="I109">_xlfn.SWITCH(H109,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J109" s="2"/>
-      <c r="K109" s="2"/>
-      <c r="L109" s="2"/>
-      <c r="M109" s="2"/>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A110" s="2">
-        <v>99</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2" t="str" cm="1">
-        <f t="array" ref="I110">_xlfn.SWITCH(H110,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J110" s="2"/>
-      <c r="K110" s="2"/>
-      <c r="L110" s="2"/>
-      <c r="M110" s="2"/>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A111" s="2">
-        <v>100</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2" t="str" cm="1">
-        <f t="array" ref="I111">_xlfn.SWITCH(H111,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J111" s="2"/>
-      <c r="K111" s="2"/>
-      <c r="L111" s="2"/>
-      <c r="M111" s="2"/>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A112" s="2">
-        <v>101</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2" t="str" cm="1">
-        <f t="array" ref="I112">_xlfn.SWITCH(H112,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J112" s="2"/>
-      <c r="K112" s="2"/>
-      <c r="L112" s="2"/>
-      <c r="M112" s="2"/>
+      <c r="M91" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A52:M52"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6417,7 +6343,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">

--- a/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267BC00F-ED1C-46B1-B9B4-3B1096F610EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D708069-B7B6-43BA-8783-538925E43EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="135">
   <si>
     <t>Epic</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Assigned To</t>
   </si>
   <si>
-    <t>Estimate (hrs)</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -159,40 +156,10 @@
     <t>Story Point</t>
   </si>
   <si>
-    <t>Detect entry intent (Rent/List)</t>
-  </si>
-  <si>
-    <t>Show personalized welcome note</t>
-  </si>
-  <si>
     <t>Show inline errors</t>
   </si>
   <si>
-    <t>Add selfie capture button</t>
-  </si>
-  <si>
-    <t>Open camera</t>
-  </si>
-  <si>
-    <t>Capture selfie image</t>
-  </si>
-  <si>
-    <t>Preview selfie</t>
-  </si>
-  <si>
-    <t>Retake option</t>
-  </si>
-  <si>
-    <t>Show loading state</t>
-  </si>
-  <si>
     <t>SignUp-Backend</t>
-  </si>
-  <si>
-    <t>Display field entry errors</t>
-  </si>
-  <si>
-    <t>Handle backend validation errors (existing email)</t>
   </si>
   <si>
     <t>Auto-login user upon successful sign up</t>
@@ -233,17 +200,6 @@
     <t>XS</t>
   </si>
   <si>
-    <t>Client-side validations:
-1. Age &gt; 16 years
-2. Prevent using same email to signup twice
-3. Name should match Govt. ID name</t>
-  </si>
-  <si>
-    <t>1. Validate image against ID ~ 80%
-2. Validate image is without hats or glasses
-3. Validate image clarity (no blur or shake)</t>
-  </si>
-  <si>
     <t>Scope</t>
   </si>
   <si>
@@ -387,29 +343,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> button is visible on Landing screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> link is visible on Landing screen</t>
     </r>
   </si>
   <si>
@@ -486,12 +419,6 @@
     </r>
   </si>
   <si>
-    <t>Handle button press with onPress</t>
-  </si>
-  <si>
-    <t>Create user table in database</t>
-  </si>
-  <si>
     <t>Backend Dev</t>
   </si>
   <si>
@@ -614,72 +541,9 @@
     <t>Connect database with FastAPI using SQLAlchemy</t>
   </si>
   <si>
-    <t>Micro2Move logo + text: "Shining the light on micro-mobility" is visible on Landing screen</t>
-  </si>
-  <si>
     <t>Landing screen renders</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout
-2. Full Name input
-3. Birth date picker
-4. Email input
-5. Terms &amp; Conditions checkbox
-6. Disable Continue button until checkbox checked</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Create T&amp;C screen layout
-2. Render scrollable content
-3. Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button
-4. Navigate back to Sign Up screen upon pressing OK button</t>
-    </r>
-  </si>
-  <si>
     <t>Sign Up</t>
   </si>
   <si>
@@ -687,13 +551,6 @@
   </si>
   <si>
     <t>Sign Up-validations</t>
-  </si>
-  <si>
-    <t>1. Add ID upload button
-2. Integrate camera/gallery picker
-3. Preview uploaded ID
-4. Validate file type
-5. Handle upload failure</t>
   </si>
   <si>
     <t>Sign Up-T&amp;C</t>
@@ -1072,54 +929,6 @@
       </rPr>
       <t xml:space="preserve"> until authStatus is resolved
 7. Expose authStatus globally</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Renter should be navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout
-2. Owner should be navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerE-BikeListing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout</t>
     </r>
   </si>
   <si>
@@ -1738,32 +1547,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> bottomNavTab (MANUAL/e2e TESTING)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Handle </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Explore</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hyperlink press with onPress</t>
     </r>
   </si>
   <si>
@@ -2045,9 +1828,6 @@
     </r>
   </si>
   <si>
-    <t>After successful login (if user's authStatus = UNAUTHENTICATED) redirect to the intended tab, based on tabIntent</t>
-  </si>
-  <si>
     <r>
       <t>1.</t>
     </r>
@@ -2153,13 +1933,36 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">If user's authStatus = UNAUTHENTICATED
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
+      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, pressing Rent a Bike button:
+1. Navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">RenterE-BikeFilter </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen
+2. Activates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2169,16 +1972,46 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, pressing List a Bike button:
+1. Navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">OwnerE-BikeListing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">screen
+2. Activates </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2188,31 +2021,45 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Profile </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>tabs are not pressable (MANUAL/e2e TESTING)</t>
-    </r>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Create user table in database </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Explore</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink is visible on Landing screen</t>
+    </r>
+  </si>
+  <si>
+    <t>Micro2Move logo + text: "Shining the light on micro-mobility" is visible on Landing screen (might be MANUAL)</t>
+  </si>
+  <si>
+    <t>Handle button, hyperlink press with onPress</t>
   </si>
   <si>
     <r>
@@ -2261,6 +2108,7 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen
+3. Show "Book an E-Bike" sub-heading under heading
 3. Activate </t>
     </r>
     <r>
@@ -2332,7 +2180,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen
-3. Activate </t>
+3. Show "Your E-Bikes" as subheading under heading
+4. Activate </t>
     </r>
     <r>
       <rPr>
@@ -2358,36 +2207,13 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, pressing Rent a Bike button:
-1. Navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">RenterE-BikeFilter </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">screen
-2. Activates </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
+      <t xml:space="preserve">If user's authStatus = UNAUTHENTICATED
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2397,46 +2223,16 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Given user's authStatus = AUTHENTICATED, pressing List a Bike button:
-1. Navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">OwnerE-BikeListing </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">screen
-2. Activates </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2446,17 +2242,56 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Routing logic works with tabs mapped to correct screens:
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Profile </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">tabs are not pressable (MANUAL/e2e TESTING)
+2. user is navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SignIn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen (MANUAL/e2e TESTING)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If user's authStatus = UNAUTHENTICATED
+Routing logic works with tabs mapped to correct screens:
 1. </t>
     </r>
     <r>
@@ -2555,7 +2390,337 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> - Profile</t>
+      <t xml:space="preserve"> - Profile
+(MANUAL/e2e TESTING)</t>
+    </r>
+  </si>
+  <si>
+    <t>After successful login (if user's authStatus = AUTHENTICATED) redirect to the intended tab, based on tabIntent</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout
+2. Full Name input
+3. Birth date picker - calendar control
+4. Email input
+5. Terms &amp; Conditions checkbox
+6. Disable Continue button until checkbox checked</t>
+    </r>
+  </si>
+  <si>
+    <t>Client-side validations:
+1. Age &gt; 16 years
+2. Prevent using same email to signup twice</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Create T&amp;C screen layout
+2. Render scrollable content
+3. Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button
+4. Navigate back to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen upon pressing OK button</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Add ID upload button
+2. Integrate camera
+3. Preview uploaded ID
+4. Handle upload failure</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Add selfie capture button
+2. Open camera
+3. Capture selfie image
+4. Preview selfie
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retake</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> buttons
+6.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button closes the camera and navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retake</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button reopens the camera</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Validate image against ID ~ 80%</t>
+  </si>
+  <si>
+    <t>1. Validate image is without hats or glasses
+2. Validate image clarity (no blur or shake)</t>
+  </si>
+  <si>
+    <t>AI verification</t>
+  </si>
+  <si>
+    <t>1. Show loading state
+2. Handle backend validation errors (existing email)
+3. Display field entry errors</t>
+  </si>
+  <si>
+    <t>1. Detect entryIntent (RENT/LIST)
+2. Detect tabIntent (RIDES/BIKES/PROFILE)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Renter should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout
+2. Show "Welcome Username" as heading of the RenterE-BikeFilter screen
+3. Show "Book an E-Bike" sub-heading under heading
+4. Activate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Lister/Owner should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerE-BikeBooking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+2. Show "Welcome Username" as heading of the OwnerE-BikeListing screen
+3. Show "Your E-Bikes" as subheading under heading
+4. Activate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
     </r>
   </si>
 </sst>
@@ -2639,7 +2804,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2730,8 +2895,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2767,11 +2938,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2876,6 +3071,66 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3179,20 +3434,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="82" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="88.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="8.88671875" style="1"/>
@@ -3200,7 +3455,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>0</v>
@@ -3212,7 +3467,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>3</v>
@@ -3221,22 +3476,23 @@
         <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="6">
+        <f>SUM(J2:J76)</f>
+        <v>156</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="M1" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -3247,28 +3503,31 @@
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="20" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="I2" s="20" cm="1">
         <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J2" s="20"/>
+        <v>8</v>
+      </c>
+      <c r="J2" s="20">
+        <f>I2</f>
+        <v>8</v>
+      </c>
       <c r="K2" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L2" s="20"/>
       <c r="M2" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -3279,28 +3538,31 @@
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="20" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="I3" s="20" cm="1">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J3" s="20"/>
+      <c r="J3" s="20">
+        <f t="shared" ref="J3:J65" si="0">I3</f>
+        <v>5</v>
+      </c>
       <c r="K3" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L3" s="20"/>
       <c r="M3" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -3311,28 +3573,31 @@
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
       <c r="E4" s="20" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I4" s="20" cm="1">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J4" s="20"/>
+      <c r="J4" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="K4" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L4" s="20"/>
       <c r="M4" s="20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -3343,28 +3608,31 @@
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I5" s="12" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J5" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="J5" s="20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="K5" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -3375,28 +3643,31 @@
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I6" s="12" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J6" s="12"/>
+      <c r="J6" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="K6" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -3407,28 +3678,31 @@
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I7" s="12" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J7" s="12"/>
+      <c r="J7" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="K7" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -3439,31 +3713,34 @@
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
       <c r="E8" s="12" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I8" s="12" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J8" s="12"/>
+      <c r="J8" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="K8" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>8</v>
       </c>
@@ -3471,28 +3748,33 @@
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="12" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="I9" s="12" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J9" s="12"/>
+      <c r="J9" s="20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="K9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="12"/>
+        <v>28</v>
+      </c>
+      <c r="L9" s="12">
+        <v>32</v>
+      </c>
       <c r="M9" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="374.4" x14ac:dyDescent="0.3">
@@ -3503,28 +3785,31 @@
       <c r="C10" s="22"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I10" s="22" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J10" s="22"/>
+        <v>5</v>
+      </c>
+      <c r="J10" s="20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="K10" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L10" s="22"/>
       <c r="M10" s="22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -3535,31 +3820,34 @@
       <c r="C11" s="22"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I11" s="22" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J11" s="22"/>
+        <v>5</v>
+      </c>
+      <c r="J11" s="20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="K11" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L11" s="22"/>
       <c r="M11" s="22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="22">
         <v>11</v>
       </c>
@@ -3567,28 +3855,31 @@
       <c r="C12" s="22"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="I12" s="22" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J12" s="22"/>
+      <c r="J12" s="20">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
       <c r="K12" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L12" s="22"/>
       <c r="M12" s="22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
@@ -3596,37 +3887,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I13" s="7" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J13" s="7"/>
+      <c r="J13" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K13" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L13" s="7"/>
       <c r="M13" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
@@ -3634,37 +3928,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I14" s="7" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J14" s="7"/>
+      <c r="J14" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K14" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L14" s="7"/>
       <c r="M14" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -3672,37 +3969,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I15" s="7" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J15" s="7"/>
+      <c r="J15" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K15" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L15" s="7"/>
       <c r="M15" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -3710,37 +4010,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I16" s="7" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J16" s="7"/>
+      <c r="J16" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K16" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L16" s="7"/>
       <c r="M16" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -3748,32 +4051,37 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I17" s="7" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="J17" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
@@ -3782,32 +4090,37 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="7">
         <v>1.1000000000000001</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I18" s="7" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="J18" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
@@ -3816,37 +4129,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="10">
         <v>1.1000000000000001</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I19" s="10" cm="1">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J19" s="10"/>
+      <c r="J19" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K19" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L19" s="10"/>
       <c r="M19" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -3854,37 +4170,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="10">
         <v>1.1000000000000001</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I20" s="10" cm="1">
         <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J20" s="10"/>
+      <c r="J20" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="K20" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L20" s="10"/>
       <c r="M20" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -3896,31 +4215,34 @@
         <v>1.2</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I21" s="14" cm="1">
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J21" s="14"/>
+      <c r="J21" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K21" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L21" s="14"/>
       <c r="M21" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -3932,31 +4254,34 @@
         <v>1.2</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I22" s="14" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J22" s="14"/>
+      <c r="J22" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K22" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L22" s="14"/>
       <c r="M22" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -3968,31 +4293,34 @@
         <v>1.2</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I23" s="14" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J23" s="14"/>
+      <c r="J23" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K23" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L23" s="14"/>
       <c r="M23" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -4004,34 +4332,37 @@
         <v>1.2</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I24" s="14" cm="1">
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J24" s="14"/>
+      <c r="J24" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K24" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L24" s="14"/>
       <c r="M24" s="14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
         <v>24</v>
       </c>
@@ -4040,31 +4371,34 @@
         <v>1.2</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I25" s="14" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J25" s="14"/>
+      <c r="J25" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K25" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L25" s="14"/>
       <c r="M25" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -4076,31 +4410,34 @@
         <v>1.2</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I26" s="14" cm="1">
         <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J26" s="14"/>
+      <c r="J26" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="K26" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L26" s="14"/>
       <c r="M26" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
@@ -4112,31 +4449,34 @@
         <v>1.2</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I27" s="14" cm="1">
         <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J27" s="14"/>
+      <c r="J27" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="K27" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L27" s="14"/>
       <c r="M27" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -4148,31 +4488,34 @@
         <v>1.2</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I28" s="14" cm="1">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J28" s="14"/>
+      <c r="J28" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="K28" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L28" s="14"/>
       <c r="M28" s="14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.3">
@@ -4180,37 +4523,40 @@
         <v>30</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="15">
         <v>1.2</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I29" s="15" cm="1">
         <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J29" s="15"/>
+      <c r="J29" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="K29" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L29" s="15"/>
       <c r="M29" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -4218,265 +4564,282 @@
         <v>31</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="15">
         <v>1.2</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H30" s="15" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I30" s="15" cm="1">
         <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J30" s="15"/>
+      <c r="J30" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="K30" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L30" s="15"/>
       <c r="M30" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="15">
         <v>32</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="15">
         <v>1.2</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I31" s="15" cm="1">
         <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J31" s="15"/>
+      <c r="J31" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="K31" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="15">
+      <c r="A32" s="24">
         <v>33</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="15">
-        <v>1.2</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="G32" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I32" s="15" cm="1">
+      <c r="B32" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="24">
+        <v>1.3</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" s="24" cm="1">
         <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J32" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K32" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A33" s="24">
         <v>34</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="24">
         <v>1.3</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F33" s="25" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="G33" s="24" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I33" s="24" cm="1">
         <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J33" s="24"/>
+      <c r="J33" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K33" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L33" s="24"/>
       <c r="M33" s="24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="39" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="37">
         <v>35</v>
       </c>
-      <c r="B34" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="24">
+      <c r="B34" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="37">
         <v>1.3</v>
       </c>
-      <c r="D34" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="F34" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="G34" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="H34" s="24" t="s">
+      <c r="D34" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="I34" s="24" cm="1">
+      <c r="H34" s="37"/>
+      <c r="I34" s="37" t="str" cm="1">
         <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v/>
+      </c>
+      <c r="J34" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K34" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="24">
         <v>36</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="24">
         <v>1.3</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F35" s="25" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="G35" s="24" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I35" s="24" cm="1">
         <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J35" s="24"/>
+      <c r="J35" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="K35" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L35" s="24"/>
       <c r="M35" s="24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="24">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="39" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="37">
         <v>37</v>
       </c>
-      <c r="B36" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="24">
+      <c r="B36" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="37">
         <v>1.3</v>
       </c>
-      <c r="D36" s="24" t="s">
+      <c r="D36" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="G36" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="H36" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="I36" s="24" cm="1">
+      <c r="G36" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37" t="str" cm="1">
         <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24" t="s">
-        <v>10</v>
+        <v/>
+      </c>
+      <c r="J36" s="37" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K36" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" s="37"/>
+      <c r="M36" s="37" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -4484,905 +4847,832 @@
         <v>38</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" s="24">
         <v>1.3</v>
       </c>
       <c r="D37" s="24" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G37" s="24" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I37" s="24" cm="1">
         <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J37" s="24"/>
+        <v>1</v>
+      </c>
+      <c r="J37" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K37" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L37" s="24"/>
       <c r="M37" s="24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="24">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="24">
         <v>1.3</v>
       </c>
       <c r="D38" s="24" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="G38" s="24" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H38" s="24" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I38" s="24" cm="1">
         <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J38" s="24"/>
+        <v>2</v>
+      </c>
+      <c r="J38" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="K38" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L38" s="24"/>
       <c r="M38" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A39" s="26">
+        <v>40</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="26">
+        <v>1.3</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="G39" s="40" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="24">
+      <c r="H39" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="40" cm="1">
+        <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J39" s="43">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="K39" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="26">
         <v>41</v>
       </c>
-      <c r="B39" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="24">
-        <v>1.3</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="F39" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="G39" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="H39" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="I39" s="24" cm="1">
-        <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J39" s="24"/>
-      <c r="K39" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A40" s="26">
-        <v>42</v>
-      </c>
       <c r="B40" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="26">
         <v>1.3</v>
       </c>
       <c r="D40" s="26" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F40" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H40" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="I40" s="26" cm="1">
-        <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J40" s="26"/>
+        <v>82</v>
+      </c>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="44"/>
       <c r="K40" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L40" s="26"/>
       <c r="M40" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="26">
-        <v>43</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" s="39" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="37">
+        <v>42</v>
+      </c>
+      <c r="B41" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="37">
         <v>1.3</v>
       </c>
-      <c r="D41" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F41" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H41" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="I41" s="26" cm="1">
-        <f t="array" ref="I41">_xlfn.SWITCH(H41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26" t="s">
-        <v>10</v>
+      <c r="D41" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41" s="37"/>
+      <c r="M41" s="37" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="26">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="26">
         <v>1.3</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F42" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H42" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="I42" s="26" cm="1">
-        <f t="array" ref="I42">_xlfn.SWITCH(H42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J42" s="26"/>
+        <v>86</v>
+      </c>
+      <c r="G42" s="41"/>
+      <c r="H42" s="41"/>
+      <c r="I42" s="41"/>
+      <c r="J42" s="44"/>
       <c r="K42" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L42" s="26"/>
       <c r="M42" s="26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="26">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" s="26">
         <v>1.3</v>
       </c>
       <c r="D43" s="26" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F43" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="G43" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H43" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="I43" s="26" cm="1">
-        <f t="array" ref="I43">_xlfn.SWITCH(H43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J43" s="26"/>
+        <v>83</v>
+      </c>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="41"/>
+      <c r="J43" s="44"/>
       <c r="K43" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L43" s="26"/>
       <c r="M43" s="26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A44" s="26">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" s="26">
         <v>1.3</v>
       </c>
       <c r="D44" s="26" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F44" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="G44" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H44" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="I44" s="26" cm="1">
-        <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J44" s="26"/>
+        <v>84</v>
+      </c>
+      <c r="G44" s="41"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="41"/>
+      <c r="J44" s="44"/>
       <c r="K44" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L44" s="26"/>
       <c r="M44" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="26">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="26">
         <v>1.3</v>
       </c>
       <c r="D45" s="26" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F45" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="G45" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H45" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="I45" s="26" cm="1">
-        <f t="array" ref="I45">_xlfn.SWITCH(H45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J45" s="26"/>
+        <v>91</v>
+      </c>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="44"/>
       <c r="K45" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L45" s="26"/>
       <c r="M45" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="26">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46" s="26">
         <v>1.3</v>
       </c>
       <c r="D46" s="26" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F46" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G46" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H46" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="I46" s="26" cm="1">
-        <f t="array" ref="I46">_xlfn.SWITCH(H46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J46" s="26"/>
+        <v>87</v>
+      </c>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="44"/>
       <c r="K46" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L46" s="26"/>
       <c r="M46" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="26">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C47" s="26">
         <v>1.3</v>
       </c>
       <c r="D47" s="26" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F47" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G47" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H47" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="I47" s="26" cm="1">
-        <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J47" s="26"/>
+        <v>92</v>
+      </c>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="45"/>
       <c r="K47" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L47" s="26"/>
       <c r="M47" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="26">
-        <v>50</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D48" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E48" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="F48" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="G48" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H48" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="I48" s="26" cm="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="28">
+        <v>49</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28">
+        <v>1.4</v>
+      </c>
+      <c r="D48" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="G48" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="H48" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" s="46" cm="1">
         <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="L48" s="26"/>
-      <c r="M48" s="26" t="s">
-        <v>10</v>
+      <c r="J48" s="43">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K48" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="28"/>
+      <c r="A49" s="28">
+        <v>50</v>
+      </c>
       <c r="B49" s="28"/>
       <c r="C49" s="28">
         <v>1.4</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E49" s="28" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="G49" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="H49" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="I49" s="28" cm="1">
-        <f t="array" ref="I49">_xlfn.SWITCH(H49,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J49" s="28"/>
+        <v>113</v>
+      </c>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="44"/>
       <c r="K49" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L49" s="28"/>
       <c r="M49" s="28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="28"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="28">
+        <v>51</v>
+      </c>
       <c r="B50" s="28"/>
       <c r="C50" s="28">
         <v>1.4</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="G50" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="H50" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="I50" s="28" cm="1">
-        <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J50" s="28"/>
+        <v>103</v>
+      </c>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="48"/>
+      <c r="J50" s="44"/>
       <c r="K50" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L50" s="28"/>
       <c r="M50" s="28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A51" s="28"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="28">
+        <v>52</v>
+      </c>
       <c r="B51" s="28"/>
       <c r="C51" s="28">
         <v>1.4</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="G51" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="H51" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="I51" s="28" cm="1">
-        <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J51" s="28"/>
+        <v>104</v>
+      </c>
+      <c r="G51" s="47"/>
+      <c r="H51" s="47"/>
+      <c r="I51" s="47"/>
+      <c r="J51" s="45"/>
       <c r="K51" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L51" s="28"/>
       <c r="M51" s="28" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A52" s="30">
+        <v>53</v>
+      </c>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30">
+        <v>1.4</v>
+      </c>
+      <c r="D52" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G52" s="49" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="28"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28">
-        <v>1.4</v>
-      </c>
-      <c r="D52" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="E52" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="F52" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="G52" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="H52" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="I52" s="28" cm="1">
+      <c r="H52" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="I52" s="49" cm="1">
         <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="30"/>
+        <v>3</v>
+      </c>
+      <c r="J52" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K52" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A53" s="30">
+        <v>54</v>
+      </c>
       <c r="B53" s="30"/>
       <c r="C53" s="30">
         <v>1.4</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E53" s="30" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F53" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="G53" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="H53" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="I53" s="30" cm="1">
-        <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J53" s="30"/>
+        <v>119</v>
+      </c>
+      <c r="G53" s="50"/>
+      <c r="H53" s="50"/>
+      <c r="I53" s="50"/>
+      <c r="J53" s="44"/>
       <c r="K53" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L53" s="30"/>
       <c r="M53" s="30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="30"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="30">
+        <v>55</v>
+      </c>
       <c r="B54" s="30"/>
       <c r="C54" s="30">
         <v>1.4</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E54" s="30" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="G54" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="H54" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="I54" s="30" cm="1">
-        <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J54" s="30"/>
+        <v>102</v>
+      </c>
+      <c r="G54" s="50"/>
+      <c r="H54" s="50"/>
+      <c r="I54" s="50"/>
+      <c r="J54" s="44"/>
       <c r="K54" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L54" s="30"/>
       <c r="M54" s="30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="30">
+        <v>56</v>
+      </c>
+      <c r="B55" s="30" t="s">
+        <v>7</v>
+      </c>
       <c r="C55" s="30">
         <v>1.4</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E55" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="F55" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G55" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="H55" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="I55" s="30" cm="1">
-        <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J55" s="30"/>
+        <v>58</v>
+      </c>
+      <c r="F55" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="G55" s="51"/>
+      <c r="H55" s="51"/>
+      <c r="I55" s="51"/>
+      <c r="J55" s="45"/>
       <c r="K55" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L55" s="30"/>
       <c r="M55" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="30">
-        <v>52</v>
-      </c>
-      <c r="B56" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="30">
-        <v>1.4</v>
-      </c>
-      <c r="D56" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="E56" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="F56" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G56" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="H56" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="I56" s="30" cm="1">
+      <c r="A56" s="35">
+        <v>57</v>
+      </c>
+      <c r="B56" s="35"/>
+      <c r="C56" s="35">
+        <v>1.5</v>
+      </c>
+      <c r="D56" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="E56" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="F56" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="G56" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="H56" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="I56" s="52" cm="1">
         <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J56" s="30"/>
-      <c r="K56" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="L56" s="30"/>
-      <c r="M56" s="30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="35"/>
+        <v>3</v>
+      </c>
+      <c r="J56" s="43">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K56" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="L56" s="35"/>
+      <c r="M56" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A57" s="35">
+        <v>58</v>
+      </c>
       <c r="B57" s="35"/>
       <c r="C57" s="35">
         <v>1.5</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E57" s="35" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G57" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="H57" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="I57" s="35" cm="1">
-        <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J57" s="35"/>
+        <v>111</v>
+      </c>
+      <c r="G57" s="53"/>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="44"/>
       <c r="K57" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L57" s="35"/>
       <c r="M57" s="35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A58" s="35"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="35">
+        <v>59</v>
+      </c>
       <c r="B58" s="35"/>
       <c r="C58" s="35">
         <v>1.5</v>
       </c>
       <c r="D58" s="35" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E58" s="35" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="G58" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="H58" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="I58" s="35" cm="1">
-        <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J58" s="35"/>
+        <v>120</v>
+      </c>
+      <c r="G58" s="53"/>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="44"/>
       <c r="K58" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L58" s="35"/>
       <c r="M58" s="35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="35"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="35">
+        <v>60</v>
+      </c>
       <c r="B59" s="35"/>
       <c r="C59" s="35">
         <v>1.5</v>
       </c>
       <c r="D59" s="35" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E59" s="35" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="G59" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="H59" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="I59" s="35" cm="1">
-        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J59" s="35"/>
+        <v>121</v>
+      </c>
+      <c r="G59" s="54"/>
+      <c r="H59" s="54"/>
+      <c r="I59" s="54"/>
+      <c r="J59" s="45"/>
       <c r="K59" s="35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L59" s="35"/>
       <c r="M59" s="35" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A60" s="33">
+        <v>61</v>
+      </c>
+      <c r="B60" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="E60" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="F60" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="G60" s="33" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A60" s="35"/>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="D60" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="E60" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="F60" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="G60" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="H60" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="I60" s="35" cm="1">
+      <c r="H60" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="I60" s="33" cm="1">
         <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J60" s="35"/>
-      <c r="K60" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="L60" s="35"/>
-      <c r="M60" s="35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="J60" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K60" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L60" s="33"/>
+      <c r="M60" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="33">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C61" s="33">
         <v>1.5</v>
       </c>
       <c r="D61" s="33" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F61" s="34" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G61" s="33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H61" s="33" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I61" s="33" cm="1">
         <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J61" s="33"/>
+      <c r="J61" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="K61" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L61" s="33"/>
       <c r="M61" s="33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -5390,707 +5680,702 @@
         <v>63</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C62" s="33">
         <v>1.5</v>
       </c>
       <c r="D62" s="33" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F62" s="34" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="G62" s="33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H62" s="33" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I62" s="33" cm="1">
         <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J62" s="33"/>
+        <v>2</v>
+      </c>
+      <c r="J62" s="20">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
       <c r="K62" s="33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L62" s="33"/>
       <c r="M62" s="33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>64</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A63" s="33">
-        <v>61</v>
-      </c>
-      <c r="B63" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C63" s="33">
-        <v>1.5</v>
-      </c>
-      <c r="D63" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E63" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="F63" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="G63" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="H63" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="I63" s="33" cm="1">
+      <c r="H63" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I63" s="2" cm="1">
         <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="L63" s="33"/>
-      <c r="M63" s="33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="J63" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" s="3" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="I64" s="2" cm="1">
         <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J64" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="J64" s="20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
       <c r="K64" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I65" s="2" cm="1">
         <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J65" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="J65" s="20">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K65" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="I66" s="2" cm="1">
         <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J66" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="J66" s="20">
+        <f t="shared" ref="J66:J85" si="1">I66</f>
+        <v>2</v>
+      </c>
       <c r="K66" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" s="3" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I67" s="2" cm="1">
         <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J67" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="J67" s="20">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
       <c r="K67" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" s="3" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="I68" s="2" cm="1">
         <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J68" s="2"/>
+      <c r="J68" s="20">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
       <c r="K68" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C69" s="2"/>
-      <c r="D69" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E69" s="2"/>
+      <c r="D69" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="E69" s="55" t="s">
+        <v>130</v>
+      </c>
       <c r="F69" s="3" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="I69" s="2" cm="1">
         <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J69" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="J69" s="20">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
       <c r="K69" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A70" s="2">
-        <v>77</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
+      <c r="D70" s="56"/>
+      <c r="E70" s="56"/>
       <c r="F70" s="3" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I70" s="2" cm="1">
         <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J70" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="J70" s="20">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
       <c r="K70" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
+      <c r="D71" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E71" s="2"/>
       <c r="F71" s="3" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I71" s="2" cm="1">
         <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J71" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="J71" s="20">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
       <c r="K71" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="3" t="s">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I72" s="2" cm="1">
         <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J72" s="2"/>
+      <c r="J72" s="20">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
       <c r="K72" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I73" s="2" cm="1">
         <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J73" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="J73" s="20">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="K73" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C74" s="2"/>
-      <c r="D74" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="D74" s="2"/>
       <c r="E74" s="2"/>
       <c r="F74" s="3" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I74" s="2" cm="1">
         <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J74" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="J74" s="20">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
       <c r="K74" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C75" s="2"/>
-      <c r="D75" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="3" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I75" s="2" cm="1">
         <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J75" s="2"/>
+      <c r="J75" s="20">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
       <c r="K75" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
       <c r="F76" s="3" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="I76" s="2" cm="1">
         <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J76" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="J76" s="20">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
       <c r="K76" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
-      <c r="F77" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I77" s="2" cm="1">
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2" t="str" cm="1">
         <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J77" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K77" s="2"/>
       <c r="L77" s="2"/>
-      <c r="M77" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="M77" s="2"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
-      <c r="F78" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I78" s="2" cm="1">
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2" t="str" cm="1">
         <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J78" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K78" s="2"/>
       <c r="L78" s="2"/>
-      <c r="M78" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="M78" s="2"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
-      <c r="F79" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I79" s="2" cm="1">
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2" t="str" cm="1">
         <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J79" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K79" s="2"/>
       <c r="L79" s="2"/>
-      <c r="M79" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="M79" s="2"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
-      <c r="F80" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I80" s="2" cm="1">
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2" t="str" cm="1">
         <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J80" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K80" s="2"/>
       <c r="L80" s="2"/>
-      <c r="M80" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
-      <c r="F81" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I81" s="2" cm="1">
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2" t="str" cm="1">
         <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J81" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K81" s="2"/>
       <c r="L81" s="2"/>
-      <c r="M81" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="M81" s="2"/>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
-      <c r="F82" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I82" s="2" cm="1">
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2" t="str" cm="1">
         <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J82" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K82" s="2"/>
       <c r="L82" s="2"/>
-      <c r="M82" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="M82" s="2"/>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -6102,17 +6387,20 @@
         <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J83" s="2"/>
+      <c r="J83" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -6124,17 +6412,20 @@
         <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J84" s="2"/>
+      <c r="J84" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -6146,144 +6437,35 @@
         <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J85" s="2"/>
+      <c r="J85" s="20" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
-        <v>96</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2" t="str" cm="1">
-        <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
-      <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
-        <v>97</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2" t="str" cm="1">
-        <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
-        <v>98</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2" t="str" cm="1">
-        <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
-        <v>99</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2" t="str" cm="1">
-        <f t="array" ref="I89">_xlfn.SWITCH(H89,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
-        <v>100</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2" t="str" cm="1">
-        <f t="array" ref="I90">_xlfn.SWITCH(H90,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
-        <v>101</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2" t="str" cm="1">
-        <f t="array" ref="I91">_xlfn.SWITCH(H91,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
-    </row>
   </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="G52:G55"/>
+    <mergeCell ref="H52:H55"/>
+    <mergeCell ref="I52:I55"/>
+    <mergeCell ref="J52:J55"/>
+    <mergeCell ref="G56:G59"/>
+    <mergeCell ref="H56:H59"/>
+    <mergeCell ref="I56:I59"/>
+    <mergeCell ref="J56:J59"/>
+    <mergeCell ref="H48:H51"/>
+    <mergeCell ref="I48:I51"/>
+    <mergeCell ref="G48:G51"/>
+    <mergeCell ref="J48:J51"/>
+    <mergeCell ref="G39:G47"/>
+    <mergeCell ref="H39:H47"/>
+    <mergeCell ref="I39:I47"/>
+    <mergeCell ref="J39:J47"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -6296,32 +6478,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -6340,60 +6522,60 @@
   <sheetData>
     <row r="1" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D708069-B7B6-43BA-8783-538925E43EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8173FFF-3AAF-4444-9860-6EA7DE17E68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="130">
   <si>
     <t>Epic</t>
   </si>
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t>Show inline errors</t>
-  </si>
-  <si>
-    <t>SignUp-Backend</t>
   </si>
   <si>
     <t>Auto-login user upon successful sign up</t>
@@ -547,24 +544,6 @@
     <t>Sign Up</t>
   </si>
   <si>
-    <t>Sign Up-Errors</t>
-  </si>
-  <si>
-    <t>Sign Up-validations</t>
-  </si>
-  <si>
-    <t>Sign Up-T&amp;C</t>
-  </si>
-  <si>
-    <t>Sign Up-ID Upload</t>
-  </si>
-  <si>
-    <t>Sign Up-Selfie</t>
-  </si>
-  <si>
-    <t>Sign Up-ID Verification</t>
-  </si>
-  <si>
     <t>1. Submit form data
 2. Submit ID image
 3. Submit selfie image</t>
@@ -959,9 +938,6 @@
   </si>
   <si>
     <t>Sign In</t>
-  </si>
-  <si>
-    <t>Sign In screen renders without crashing</t>
   </si>
   <si>
     <t>Manage local form state (email, password)</t>
@@ -1029,12 +1005,6 @@
 1. Email Input- testID = "emailTextInput"
 2. Passwordl Input- testID = "passwordTextInput"
 1. Button- testID = "SignInButton"</t>
-  </si>
-  <si>
-    <t>1. Email input is visible
-2. Password input is visible
-3. Sign In button is visible
-4. Sign Up hyperlink is visible</t>
   </si>
   <si>
     <t>1. Sign In button is disabled when email is empty
@@ -2484,10 +2454,444 @@
     </r>
   </si>
   <si>
-    <t>1. Add ID upload button
+    <t>1. Validate image against ID ~ 80%</t>
+  </si>
+  <si>
+    <t>1. Validate image is without hats or glasses
+2. Validate image clarity (no blur or shake)</t>
+  </si>
+  <si>
+    <t>1. Show loading state
+2. Handle backend validation errors (existing email)
+3. Display field entry errors</t>
+  </si>
+  <si>
+    <t>1. Detect entryIntent (RENT/LIST)
+2. Detect tabIntent (RIDES/BIKES/PROFILE)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Renter should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RenterE-BikeBookingFilter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen layout
+2. Show "Welcome Username" as heading of the RenterE-BikeFilter screen
+3. Show "Book an E-Bike" sub-heading under heading
+4. Activate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Rides</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Lister/Owner should be navigated to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OwnerE-BikeBooking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+2. Show "Welcome Username" as heading of the OwnerE-BikeListing screen
+3. Show "Your E-Bikes" as subheading under heading
+4. Activate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>My Bikes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottomNavTab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. T&amp;C checkbox pressing calls a mockFunction()
+2. Govt. ID &amp; Selfie buttons pressing calls a mockFunction()
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Continue </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">&amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pressing calls a mockFunction()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sign Up screen renders
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Full Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> input field is visible
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date of Birth</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> input field and calendar control is visible
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Email</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> input is visible
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Create Password</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> input is visible
+5. I accept the T&amp;C </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkbox</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is visible
+6. Upload Government ID &amp; Selfie buttons are visible
+7. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Continue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button is visible
+8. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hyperlink is visible</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Add ID upload button
 2. Integrate camera
 3. Preview uploaded ID
-4. Handle upload failure</t>
+4. Handle upload failure
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retake</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> buttons
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button closes the camera and navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retake</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button reopens the camera</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2601,127 +3005,152 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> button reopens the camera</t>
-    </r>
-  </si>
-  <si>
-    <t>1. Validate image against ID ~ 80%</t>
-  </si>
-  <si>
-    <t>1. Validate image is without hats or glasses
-2. Validate image clarity (no blur or shake)</t>
-  </si>
-  <si>
-    <t>AI verification</t>
-  </si>
-  <si>
-    <t>1. Show loading state
-2. Handle backend validation errors (existing email)
-3. Display field entry errors</t>
-  </si>
-  <si>
-    <t>1. Detect entryIntent (RENT/LIST)
-2. Detect tabIntent (RIDES/BIKES/PROFILE)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Renter should be navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RenterE-BikeBookingFilter</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen layout
-2. Show "Welcome Username" as heading of the RenterE-BikeFilter screen
-3. Show "Book an E-Bike" sub-heading under heading
-4. Activate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Rides</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Lister/Owner should be navigated to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OwnerE-BikeBooking</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen
-2. Show "Welcome Username" as heading of the OwnerE-BikeListing screen
-3. Show "Your E-Bikes" as subheading under heading
-4. Activate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>My Bikes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottomNavTab</t>
-    </r>
+      <t xml:space="preserve"> button reopens the camera
+7. Handle upload failure</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. T&amp;C screen navigation and reverse navigation to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button works
+2. Camera open, close, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retake</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> navigations work
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>Sign In screen renders without crashing
+1. Email input is visible
+2. Password input is visible
+3. Sign In button is visible
+4. Sign Up hyperlink is visible</t>
+  </si>
+  <si>
+    <t>ID and Selfie matching accuracy ~ 80%</t>
   </si>
 </sst>
 </file>
@@ -2804,7 +3233,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2901,6 +3330,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -2966,16 +3407,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3081,33 +3519,6 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3126,11 +3537,38 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3434,2870 +3872,2986 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="88.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="80.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:13" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="5">
+        <f>SUM(J2:J79)</f>
+        <v>159</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="19">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="J1" s="6">
-        <f>SUM(J2:J76)</f>
-        <v>156</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="20">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20" t="s">
+      <c r="F2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="20" cm="1">
+      <c r="G2" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="19" cm="1">
         <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="J2" s="20">
+      <c r="J2" s="19">
         <f>I2</f>
         <v>8</v>
       </c>
-      <c r="K2" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20" t="s">
+      <c r="K2" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="20">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="20" cm="1">
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="19" cm="1">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J3" s="20">
-        <f t="shared" ref="J3:J65" si="0">I3</f>
+      <c r="J3" s="19">
+        <f t="shared" ref="J3:J68" si="0">I3</f>
         <v>5</v>
       </c>
-      <c r="K3" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20" t="s">
+      <c r="K3" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="20">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="20" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4" s="20" cm="1">
+      <c r="G4" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="19" cm="1">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="19">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K4" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20" t="s">
+      <c r="K4" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="12" cm="1">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="11" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12" t="s">
+      <c r="K5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="12" cm="1">
+      <c r="G6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="11" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K6" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12" t="s">
+      <c r="K6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>6</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="12" cm="1">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="11" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12" t="s">
+      <c r="K7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="12" cm="1">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="11" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="11">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12" t="s">
+      <c r="K8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>8</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="12" cm="1">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="11" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" s="12">
+      <c r="K9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="11">
         <v>32</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="22">
+      <c r="A10" s="21">
         <v>10</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="22" cm="1">
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="21" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="21">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K10" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22" t="s">
+      <c r="K10" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
-        <v>9</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="22" cm="1">
+      <c r="A11" s="21">
+        <v>9</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="21" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="21">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K11" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22" t="s">
+      <c r="K11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="22">
+      <c r="A12" s="21">
         <v>11</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="22" t="s">
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="22" cm="1">
+      <c r="H12" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="21" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="21">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K12" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22" t="s">
+      <c r="K12" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="7" cm="1">
+      <c r="G13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="6" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7" t="s">
+      <c r="K13" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I14" s="7" cm="1">
+      <c r="E14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" s="6" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7" t="s">
+      <c r="K14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="7" cm="1">
+      <c r="E15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="6" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7" t="s">
+      <c r="K15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="7">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="9" t="s">
+      <c r="E16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="7" cm="1">
+      <c r="H16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="6" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7" t="s">
+      <c r="K16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" s="7" cm="1">
+      <c r="E17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="6" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
+      <c r="K17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I18" s="7" cm="1">
+      <c r="E18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="6" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
+      <c r="K18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
     </row>
     <row r="19" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
+      <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="9">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="10" t="s">
+      <c r="E19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="10" cm="1">
+      <c r="H19" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="9" cm="1">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K19" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10" t="s">
+      <c r="K19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
+      <c r="A20" s="9">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="9">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="10" t="s">
+      <c r="E20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="10" cm="1">
+      <c r="H20" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="9" cm="1">
         <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="9">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10" t="s">
+      <c r="K20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="14">
+      <c r="A21" s="13">
         <v>20</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14">
+      <c r="B21" s="13"/>
+      <c r="C21" s="13">
         <v>1.2</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I21" s="14" cm="1">
+      <c r="E21" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="13" cm="1">
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J21" s="20">
+      <c r="J21" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K21" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14" t="s">
+      <c r="K21" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="14">
+      <c r="A22" s="13">
         <v>21</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14">
+      <c r="B22" s="13"/>
+      <c r="C22" s="13">
         <v>1.2</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="14" cm="1">
+      <c r="E22" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="13" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K22" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14" t="s">
+      <c r="K22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="14">
+      <c r="A23" s="13">
         <v>22</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14">
+      <c r="B23" s="13"/>
+      <c r="C23" s="13">
         <v>1.2</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="14" cm="1">
+      <c r="E23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23" s="13" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J23" s="20">
+      <c r="J23" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K23" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14" t="s">
+      <c r="K23" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="14">
+      <c r="A24" s="13">
         <v>23</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14">
+      <c r="B24" s="13"/>
+      <c r="C24" s="13">
         <v>1.2</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E24" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="14" cm="1">
+      <c r="E24" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" s="13" cm="1">
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K24" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="14">
+      <c r="K24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
         <v>24</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14">
+      <c r="B25" s="13"/>
+      <c r="C25" s="13">
         <v>1.2</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="G25" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="14" cm="1">
+      <c r="E25" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I25" s="13" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J25" s="20">
+      <c r="J25" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K25" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14" t="s">
+      <c r="K25" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="14">
+      <c r="A26" s="13">
         <v>25</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14">
+      <c r="B26" s="13"/>
+      <c r="C26" s="13">
         <v>1.2</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="G26" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="14" cm="1">
+      <c r="E26" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="13" cm="1">
         <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K26" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14" t="s">
+      <c r="K26" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="14">
+      <c r="A27" s="13">
         <v>26</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14">
+      <c r="B27" s="13"/>
+      <c r="C27" s="13">
         <v>1.2</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" s="14" cm="1">
+      <c r="E27" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="13" cm="1">
         <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K27" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14" t="s">
+      <c r="K27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
+      <c r="A28" s="13">
         <v>29</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14">
+      <c r="B28" s="13"/>
+      <c r="C28" s="13">
         <v>1.2</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="14" cm="1">
+      <c r="E28" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" s="13" cm="1">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K28" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="19" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A29" s="15">
+      <c r="K28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="18" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A29" s="14">
         <v>30</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="14">
         <v>1.2</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E29" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G29" s="15" t="s">
+      <c r="E29" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H29" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="I29" s="15" cm="1">
+      <c r="H29" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29" s="14" cm="1">
         <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J29" s="20">
+      <c r="J29" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K29" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15" t="s">
+      <c r="K29" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="15">
+      <c r="A30" s="14">
         <v>31</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="14">
         <v>1.2</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="G30" s="15" t="s">
+      <c r="E30" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="I30" s="15" cm="1">
+      <c r="H30" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30" s="14" cm="1">
         <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K30" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15" t="s">
+      <c r="K30" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="15">
+      <c r="A31" s="14">
         <v>32</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="14">
         <v>1.2</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E31" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="15" t="s">
+      <c r="E31" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="I31" s="15" cm="1">
+      <c r="H31" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I31" s="14" cm="1">
         <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J31" s="20">
+      <c r="J31" s="14">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K31" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="24">
+      <c r="K31" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A32" s="23">
         <v>33</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="23">
         <v>1.3</v>
       </c>
-      <c r="D32" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="G32" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="H32" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" s="24" cm="1">
+      <c r="D32" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="23" cm="1">
         <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="23">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K32" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="24">
+      <c r="K32" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" s="23"/>
+      <c r="M32" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="38" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="36">
         <v>34</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="36">
         <v>1.3</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="E33" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F33" s="25" t="s">
+      <c r="G33" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36" t="str" cm="1">
+        <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K33" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" s="36"/>
+      <c r="M33" s="36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="23">
+        <v>35</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="23">
+        <v>1.3</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="G33" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="H33" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="I33" s="24" cm="1">
-        <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="G34" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I34" s="23" cm="1">
+        <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J34" s="23">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K34" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" s="23"/>
+      <c r="M34" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="38" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="36">
+        <v>36</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="36">
+        <v>1.3</v>
+      </c>
+      <c r="D35" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="G35" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="H35" s="36"/>
+      <c r="I35" s="36" t="str" cm="1">
+        <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="36" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K35" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="L35" s="36"/>
+      <c r="M35" s="36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="23">
+        <v>37</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="23">
+        <v>1.3</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I36" s="23" cm="1">
+        <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J33" s="20">
+      <c r="J36" s="23">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K33" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" s="39" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="37">
+      <c r="K36" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="23">
+        <v>38</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="23">
+        <v>1.3</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="G37" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H37" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="37">
-        <v>1.3</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F34" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="G34" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37" t="str" cm="1">
-        <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="37" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K34" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="L34" s="37"/>
-      <c r="M34" s="37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="24">
-        <v>36</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="24">
-        <v>1.3</v>
-      </c>
-      <c r="D35" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F35" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="G35" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="H35" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" s="24" cm="1">
-        <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I37" s="23" cm="1">
+        <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J35" s="20">
+      <c r="J37" s="23">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K35" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" s="39" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="37">
+      <c r="K37" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L37" s="23"/>
+      <c r="M37" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A38" s="25">
+        <v>39</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="H38" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="I38" s="48" cm="1">
+        <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J38" s="48">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="K38" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="25">
+        <v>40</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39" s="49"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="49"/>
+      <c r="J39" s="49"/>
+      <c r="K39" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L39" s="25"/>
+      <c r="M39" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" s="38" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="36">
+        <v>41</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="36">
+        <v>1.3</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="49"/>
+      <c r="K40" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="25">
+        <v>42</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
+      <c r="K41" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41" s="25"/>
+      <c r="M41" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="25">
+        <v>43</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L42" s="25"/>
+      <c r="M42" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="25">
+        <v>44</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L43" s="25"/>
+      <c r="M43" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="25">
+        <v>45</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="G44" s="49"/>
+      <c r="H44" s="49"/>
+      <c r="I44" s="49"/>
+      <c r="J44" s="49"/>
+      <c r="K44" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L44" s="25"/>
+      <c r="M44" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="25">
+        <v>46</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F45" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="G45" s="49"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="49"/>
+      <c r="J45" s="49"/>
+      <c r="K45" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L45" s="25"/>
+      <c r="M45" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="25">
+        <v>47</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="G46" s="50"/>
+      <c r="H46" s="50"/>
+      <c r="I46" s="50"/>
+      <c r="J46" s="50"/>
+      <c r="K46" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L46" s="25"/>
+      <c r="M46" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="27">
+        <v>48</v>
+      </c>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="G47" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="H47" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47" s="45" cm="1">
+        <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J47" s="45">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K47" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L47" s="27"/>
+      <c r="M47" s="27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="27">
+        <v>49</v>
+      </c>
+      <c r="B48" s="27"/>
+      <c r="C48" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G48" s="46"/>
+      <c r="H48" s="46"/>
+      <c r="I48" s="46"/>
+      <c r="J48" s="46"/>
+      <c r="K48" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L48" s="27"/>
+      <c r="M48" s="27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="27">
+        <v>50</v>
+      </c>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E49" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L49" s="27"/>
+      <c r="M49" s="27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="27">
+        <v>51</v>
+      </c>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+      <c r="I50" s="47"/>
+      <c r="J50" s="47"/>
+      <c r="K50" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L50" s="27"/>
+      <c r="M50" s="27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A51" s="29">
+        <v>52</v>
+      </c>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E51" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F51" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G51" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="37" t="s">
+      <c r="I51" s="39" cm="1">
+        <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J51" s="39">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K51" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A52" s="29">
+        <v>53</v>
+      </c>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E52" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F52" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="29">
+        <v>54</v>
+      </c>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E53" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F53" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="L53" s="29"/>
+      <c r="M53" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="29">
+        <v>55</v>
+      </c>
+      <c r="B54" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="37">
-        <v>1.3</v>
-      </c>
-      <c r="D36" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="E36" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" s="38" t="s">
+      <c r="C54" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="E54" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="L54" s="29"/>
+      <c r="M54" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="34">
+        <v>56</v>
+      </c>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F55" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="G36" s="37" t="s">
+      <c r="G55" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="H55" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="I55" s="42" cm="1">
+        <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J55" s="42">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K55" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="L55" s="34"/>
+      <c r="M55" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A56" s="34">
         <v>57</v>
       </c>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37" t="str" cm="1">
-        <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="37" t="str">
+      <c r="B56" s="34"/>
+      <c r="C56" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E56" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F56" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="43"/>
+      <c r="J56" s="43"/>
+      <c r="K56" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="L56" s="34"/>
+      <c r="M56" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="34">
+        <v>58</v>
+      </c>
+      <c r="B57" s="34"/>
+      <c r="C57" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F57" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="G57" s="43"/>
+      <c r="H57" s="43"/>
+      <c r="I57" s="43"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="L57" s="34"/>
+      <c r="M57" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="34">
+        <v>59</v>
+      </c>
+      <c r="B58" s="34"/>
+      <c r="C58" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F58" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
+      <c r="I58" s="44"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="L58" s="34"/>
+      <c r="M58" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A59" s="32">
+        <v>60</v>
+      </c>
+      <c r="B59" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D59" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="G59" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I59" s="32" cm="1">
+        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J59" s="32">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="L36" s="37"/>
-      <c r="M36" s="37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="24">
-        <v>38</v>
-      </c>
-      <c r="B37" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L59" s="32"/>
+      <c r="M59" s="32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="32">
+        <v>61</v>
+      </c>
+      <c r="B60" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="24">
-        <v>1.3</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E37" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F37" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="G37" s="24" t="s">
+      <c r="C60" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="H37" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="I37" s="24" cm="1">
-        <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="F60" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="G60" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="I60" s="32" cm="1">
+        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J60" s="32">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K60" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L60" s="32"/>
+      <c r="M60" s="32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="32">
+        <v>62</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D61" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="E61" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="G61" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61" s="32" cm="1">
+        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J61" s="32">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K61" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L61" s="32"/>
+      <c r="M61" s="32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" s="18" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="51">
+        <v>63</v>
+      </c>
+      <c r="B62" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="51">
+        <v>1.6</v>
+      </c>
+      <c r="D62" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E62" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F62" s="52" t="s">
+        <v>124</v>
+      </c>
+      <c r="G62" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="H62" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="I62" s="51" cm="1">
+        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J37" s="20">
+      <c r="J62" s="51">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K37" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="24">
-        <v>39</v>
-      </c>
-      <c r="B38" s="24" t="s">
+      <c r="K62" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="L62" s="51"/>
+      <c r="M62" s="51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="51">
+        <v>64</v>
+      </c>
+      <c r="B63" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="24">
-        <v>1.3</v>
-      </c>
-      <c r="D38" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E38" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="F38" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="G38" s="24" t="s">
+      <c r="C63" s="51">
+        <v>1.6</v>
+      </c>
+      <c r="D63" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E63" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F63" s="52" t="s">
+        <v>123</v>
+      </c>
+      <c r="G63" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="H63" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="I63" s="51" cm="1">
+        <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J63" s="51">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K63" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="L63" s="51"/>
+      <c r="M63" s="51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="51">
+        <v>65</v>
+      </c>
+      <c r="B64" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="51">
+        <v>1.6</v>
+      </c>
+      <c r="D64" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E64" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F64" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="G64" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="H64" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="I64" s="51" cm="1">
+        <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J64" s="51">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K64" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="L64" s="51"/>
+      <c r="M64" s="51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="51">
+        <v>66</v>
+      </c>
+      <c r="B65" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="51">
+        <v>2.6</v>
+      </c>
+      <c r="D65" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="E65" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="F65" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="G65" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="H65" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="I65" s="51" cm="1">
+        <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J65" s="51">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K65" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="L65" s="51"/>
+      <c r="M65" s="51" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="54">
+        <v>67</v>
+      </c>
+      <c r="B66" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D66" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E66" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="H38" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="I38" s="24" cm="1">
-        <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J38" s="20">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K38" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A39" s="26">
-        <v>40</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="G39" s="40" t="s">
+      <c r="F66" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="G66" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H39" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" s="40" cm="1">
-        <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J39" s="43">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K39" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="L39" s="26"/>
-      <c r="M39" s="26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="26">
-        <v>41</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="44"/>
-      <c r="K40" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="L40" s="26"/>
-      <c r="M40" s="26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" s="39" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="37">
-        <v>42</v>
-      </c>
-      <c r="B41" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="37">
-        <v>1.3</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="44"/>
-      <c r="K41" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="L41" s="37"/>
-      <c r="M41" s="37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="26">
-        <v>43</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D42" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F42" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A43" s="26">
-        <v>44</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D43" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E43" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="44"/>
-      <c r="K43" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="L43" s="26"/>
-      <c r="M43" s="26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A44" s="26">
-        <v>45</v>
-      </c>
-      <c r="B44" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D44" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E44" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F44" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="L44" s="26"/>
-      <c r="M44" s="26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="26">
-        <v>46</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D45" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F45" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="44"/>
-      <c r="K45" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="L45" s="26"/>
-      <c r="M45" s="26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="26">
-        <v>47</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D46" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E46" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F46" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="44"/>
-      <c r="K46" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="L46" s="26"/>
-      <c r="M46" s="26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="26">
-        <v>48</v>
-      </c>
-      <c r="B47" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="26">
-        <v>1.3</v>
-      </c>
-      <c r="D47" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E47" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="F47" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="G47" s="42"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="42"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="28">
-        <v>49</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28">
-        <v>1.4</v>
-      </c>
-      <c r="D48" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E48" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F48" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="G48" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="H48" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="I48" s="46" cm="1">
-        <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J48" s="43">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K48" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="L48" s="28"/>
-      <c r="M48" s="28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="28">
-        <v>50</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28">
-        <v>1.4</v>
-      </c>
-      <c r="D49" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E49" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="44"/>
-      <c r="K49" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="28">
-        <v>51</v>
-      </c>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28">
-        <v>1.4</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F50" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="48"/>
-      <c r="J50" s="44"/>
-      <c r="K50" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="L50" s="28"/>
-      <c r="M50" s="28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="28">
-        <v>52</v>
-      </c>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28">
-        <v>1.4</v>
-      </c>
-      <c r="D51" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E51" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F51" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="47"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A52" s="30">
-        <v>53</v>
-      </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30">
-        <v>1.4</v>
-      </c>
-      <c r="D52" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E52" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F52" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G52" s="49" t="s">
-        <v>10</v>
-      </c>
-      <c r="H52" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="I52" s="49" cm="1">
-        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H66" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="I66" s="54" cm="1">
+        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J52" s="43">
+      <c r="J66" s="54">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K52" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A53" s="30">
-        <v>54</v>
-      </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30">
-        <v>1.4</v>
-      </c>
-      <c r="D53" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E53" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F53" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="G53" s="50"/>
-      <c r="H53" s="50"/>
-      <c r="I53" s="50"/>
-      <c r="J53" s="44"/>
-      <c r="K53" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="L53" s="30"/>
-      <c r="M53" s="30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A54" s="30">
-        <v>55</v>
-      </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30">
-        <v>1.4</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E54" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F54" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="G54" s="50"/>
-      <c r="H54" s="50"/>
-      <c r="I54" s="50"/>
-      <c r="J54" s="44"/>
-      <c r="K54" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="L54" s="30"/>
-      <c r="M54" s="30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="30">
-        <v>56</v>
-      </c>
-      <c r="B55" s="30" t="s">
+      <c r="K66" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L66" s="54"/>
+      <c r="M66" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="54">
+        <v>68</v>
+      </c>
+      <c r="B67" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C55" s="30">
-        <v>1.4</v>
-      </c>
-      <c r="D55" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E55" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F55" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="G55" s="51"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="51"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="35">
+      <c r="C67" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D67" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E67" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="35"/>
-      <c r="C56" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="D56" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E56" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="F56" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="G56" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="H56" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="I56" s="52" cm="1">
-        <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="F67" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G67" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="H67" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="I67" s="54" cm="1">
+        <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J56" s="43">
+      <c r="J67" s="54">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K56" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="L56" s="35"/>
-      <c r="M56" s="35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A57" s="35">
-        <v>58</v>
-      </c>
-      <c r="B57" s="35"/>
-      <c r="C57" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="D57" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E57" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="F57" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="G57" s="53"/>
-      <c r="H57" s="53"/>
-      <c r="I57" s="53"/>
-      <c r="J57" s="44"/>
-      <c r="K57" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="L57" s="35"/>
-      <c r="M57" s="35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="35">
-        <v>59</v>
-      </c>
-      <c r="B58" s="35"/>
-      <c r="C58" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="D58" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E58" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="F58" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="G58" s="53"/>
-      <c r="H58" s="53"/>
-      <c r="I58" s="53"/>
-      <c r="J58" s="44"/>
-      <c r="K58" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="L58" s="35"/>
-      <c r="M58" s="35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A59" s="35">
-        <v>60</v>
-      </c>
-      <c r="B59" s="35"/>
-      <c r="C59" s="35">
-        <v>1.5</v>
-      </c>
-      <c r="D59" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E59" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="F59" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="G59" s="54"/>
-      <c r="H59" s="54"/>
-      <c r="I59" s="54"/>
-      <c r="J59" s="45"/>
-      <c r="K59" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="L59" s="35"/>
-      <c r="M59" s="35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A60" s="33">
-        <v>61</v>
-      </c>
-      <c r="B60" s="33" t="s">
+      <c r="K67" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L67" s="54"/>
+      <c r="M67" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A68" s="54">
+        <v>69</v>
+      </c>
+      <c r="B68" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="33">
-        <v>1.5</v>
-      </c>
-      <c r="D60" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="E60" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="F60" s="34" t="s">
-        <v>109</v>
-      </c>
-      <c r="G60" s="33" t="s">
+      <c r="C68" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D68" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F68" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H60" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="I60" s="33" cm="1">
-        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J60" s="20">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K60" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="L60" s="33"/>
-      <c r="M60" s="33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="33">
-        <v>62</v>
-      </c>
-      <c r="B61" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="33">
-        <v>1.5</v>
-      </c>
-      <c r="D61" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="E61" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="F61" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="G61" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="H61" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="I61" s="33" cm="1">
-        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J61" s="20">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K61" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="L61" s="33"/>
-      <c r="M61" s="33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A62" s="33">
-        <v>63</v>
-      </c>
-      <c r="B62" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="33">
-        <v>1.5</v>
-      </c>
-      <c r="D62" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="E62" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="F62" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="G62" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="H62" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="I62" s="33" cm="1">
-        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J62" s="20">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K62" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="L62" s="33"/>
-      <c r="M62" s="33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="2">
-        <v>64</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I63" s="2" cm="1">
-        <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J63" s="20">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
-        <v>65</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I64" s="2" cm="1">
-        <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J64" s="20">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A65" s="2">
-        <v>66</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I65" s="2" cm="1">
-        <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H68" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="I68" s="54" cm="1">
+        <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J65" s="20">
+      <c r="J68" s="54">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K65" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
-        <v>67</v>
-      </c>
-      <c r="B66" s="2" t="s">
+      <c r="K68" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L68" s="54"/>
+      <c r="M68" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="54">
+        <v>70</v>
+      </c>
+      <c r="B69" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="3" t="s">
+      <c r="C69" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D69" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E69" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F69" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="G69" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="H69" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69" s="54" cm="1">
+        <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J69" s="54">
+        <f t="shared" ref="J69:J88" si="1">I69</f>
+        <v>2</v>
+      </c>
+      <c r="K69" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L69" s="54"/>
+      <c r="M69" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A70" s="54">
+        <v>71</v>
+      </c>
+      <c r="B70" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D70" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E70" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F70" s="55" t="s">
         <v>125</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G70" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H66" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I66" s="2" cm="1">
-        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J66" s="20">
-        <f t="shared" ref="J66:J85" si="1">I66</f>
-        <v>2</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
-        <v>71</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I67" s="2" cm="1">
-        <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H70" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="I70" s="54" cm="1">
+        <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="J67" s="20">
+      <c r="J70" s="54">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K67" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
-        <v>76</v>
-      </c>
-      <c r="B68" s="2" t="s">
+      <c r="K70" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L70" s="54"/>
+      <c r="M70" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="54">
+        <v>72</v>
+      </c>
+      <c r="B71" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G68" s="2" t="s">
+      <c r="C71" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D71" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E71" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F71" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="G71" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I68" s="2" cm="1">
-        <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H71" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="I71" s="54" cm="1">
+        <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J68" s="20">
+      <c r="J71" s="54">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K68" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
-        <v>81</v>
-      </c>
-      <c r="B69" s="2" t="s">
+      <c r="K71" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L71" s="54"/>
+      <c r="M71" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A72" s="54">
+        <v>73</v>
+      </c>
+      <c r="B72" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="2"/>
-      <c r="D69" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="E69" s="55" t="s">
-        <v>130</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H69" s="2" t="s">
+      <c r="C72" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D72" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E72" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F72" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="G72" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="I69" s="2" cm="1">
-        <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H72" s="54" t="s">
+        <v>38</v>
+      </c>
+      <c r="I72" s="54" cm="1">
+        <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="J69" s="20">
+      <c r="J72" s="54">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K69" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="56"/>
-      <c r="E70" s="56"/>
-      <c r="F70" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I70" s="2" cm="1">
-        <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="K72" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L72" s="54"/>
+      <c r="M72" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="54">
+        <v>74</v>
+      </c>
+      <c r="B73" s="54"/>
+      <c r="C73" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D73" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E73" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F73" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="G73" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H73" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="I73" s="54" cm="1">
+        <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J70" s="20">
+      <c r="J73" s="54">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
-        <v>83</v>
-      </c>
-      <c r="B71" s="2" t="s">
+      <c r="K73" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L73" s="54"/>
+      <c r="M73" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="54">
+        <v>75</v>
+      </c>
+      <c r="B74" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G71" s="2" t="s">
+      <c r="C74" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D74" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E74" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F74" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="G74" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H71" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I71" s="2" cm="1">
-        <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H74" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="I74" s="54" cm="1">
+        <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J71" s="20">
+      <c r="J74" s="54">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
-        <v>86</v>
-      </c>
-      <c r="B72" s="2" t="s">
+      <c r="K74" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L74" s="54"/>
+      <c r="M74" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="54">
+        <v>76</v>
+      </c>
+      <c r="B75" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G72" s="2" t="s">
+      <c r="C75" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D75" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E75" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F75" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="G75" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H72" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I72" s="2" cm="1">
-        <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H75" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="I75" s="54" cm="1">
+        <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J72" s="20">
+      <c r="J75" s="54">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K72" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
-        <v>89</v>
-      </c>
-      <c r="B73" s="2" t="s">
+      <c r="K75" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L75" s="54"/>
+      <c r="M75" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A76" s="54">
+        <v>77</v>
+      </c>
+      <c r="B76" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G73" s="2" t="s">
+      <c r="C76" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D76" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E76" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F76" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="G76" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H73" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I73" s="2" cm="1">
-        <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H76" s="54" t="s">
+        <v>45</v>
+      </c>
+      <c r="I76" s="54" cm="1">
+        <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J73" s="20">
+      <c r="J76" s="54">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K73" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
-        <v>90</v>
-      </c>
-      <c r="B74" s="2" t="s">
+      <c r="K76" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L76" s="54"/>
+      <c r="M76" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="54">
+        <v>78</v>
+      </c>
+      <c r="B77" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G74" s="2" t="s">
+      <c r="C77" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D77" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E77" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F77" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="G77" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H74" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I74" s="2" cm="1">
-        <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H77" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77" s="54" cm="1">
+        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J74" s="20">
+      <c r="J77" s="54">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K74" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
-        <v>91</v>
-      </c>
-      <c r="B75" s="2" t="s">
+      <c r="K77" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L77" s="54"/>
+      <c r="M77" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="54">
+        <v>79</v>
+      </c>
+      <c r="B78" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G75" s="2" t="s">
+      <c r="C78" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D78" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E78" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F78" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="G78" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H75" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I75" s="2" cm="1">
-        <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H78" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="I78" s="54" cm="1">
+        <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J75" s="20">
+      <c r="J78" s="54">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K75" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
-        <v>92</v>
-      </c>
-      <c r="B76" s="2" t="s">
+      <c r="K78" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L78" s="54"/>
+      <c r="M78" s="54" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="54">
+        <v>80</v>
+      </c>
+      <c r="B79" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G76" s="2" t="s">
+      <c r="C79" s="54">
+        <v>1.6</v>
+      </c>
+      <c r="D79" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E79" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="F79" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="G79" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H76" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I76" s="2" cm="1">
-        <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H79" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79" s="54" cm="1">
+        <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J76" s="20">
+      <c r="J79" s="54">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K76" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
-        <v>93</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2" t="str" cm="1">
-        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J77" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
-        <v>94</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2" t="str" cm="1">
-        <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
-        <v>95</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2" t="str" cm="1">
-        <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J79" s="20" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
+      <c r="K79" s="54" t="s">
+        <v>28</v>
+      </c>
+      <c r="L79" s="54"/>
+      <c r="M79" s="54" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>7</v>
@@ -6312,7 +6866,7 @@
         <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J80" s="20" t="str">
+      <c r="J80" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6322,7 +6876,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>7</v>
@@ -6337,7 +6891,7 @@
         <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J81" s="20" t="str">
+      <c r="J81" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6347,7 +6901,7 @@
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>7</v>
@@ -6362,7 +6916,7 @@
         <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J82" s="20" t="str">
+      <c r="J82" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6372,7 +6926,7 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>7</v>
@@ -6387,7 +6941,7 @@
         <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J83" s="20" t="str">
+      <c r="J83" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6397,7 +6951,7 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>7</v>
@@ -6412,7 +6966,7 @@
         <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J84" s="20" t="str">
+      <c r="J84" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6422,7 +6976,7 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>7</v>
@@ -6437,7 +6991,7 @@
         <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J85" s="20" t="str">
+      <c r="J85" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6445,26 +6999,99 @@
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
     </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>84</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2" t="str" cm="1">
+        <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J86" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>85</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2" t="str" cm="1">
+        <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J87" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>86</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2" t="str" cm="1">
+        <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J88" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2"/>
+      <c r="M88" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="G52:G55"/>
-    <mergeCell ref="H52:H55"/>
-    <mergeCell ref="I52:I55"/>
-    <mergeCell ref="J52:J55"/>
-    <mergeCell ref="G56:G59"/>
-    <mergeCell ref="H56:H59"/>
-    <mergeCell ref="I56:I59"/>
-    <mergeCell ref="J56:J59"/>
-    <mergeCell ref="H48:H51"/>
-    <mergeCell ref="I48:I51"/>
-    <mergeCell ref="G48:G51"/>
-    <mergeCell ref="J48:J51"/>
-    <mergeCell ref="G39:G47"/>
-    <mergeCell ref="H39:H47"/>
-    <mergeCell ref="I39:I47"/>
-    <mergeCell ref="J39:J47"/>
+  <mergeCells count="16">
+    <mergeCell ref="H47:H50"/>
+    <mergeCell ref="I47:I50"/>
+    <mergeCell ref="G47:G50"/>
+    <mergeCell ref="J47:J50"/>
+    <mergeCell ref="G38:G46"/>
+    <mergeCell ref="H38:H46"/>
+    <mergeCell ref="I38:I46"/>
+    <mergeCell ref="J38:J46"/>
+    <mergeCell ref="J51:J54"/>
+    <mergeCell ref="G55:G58"/>
+    <mergeCell ref="H55:H58"/>
+    <mergeCell ref="I55:I58"/>
+    <mergeCell ref="J55:J58"/>
+    <mergeCell ref="G51:G54"/>
+    <mergeCell ref="H51:H54"/>
+    <mergeCell ref="I51:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6517,7 +7144,7 @@
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="13.44140625" style="1"/>
-    <col min="3" max="16384" width="13.44140625" style="4"/>
+    <col min="3" max="16384" width="13.44140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -6525,7 +7152,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">

--- a/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8173FFF-3AAF-4444-9860-6EA7DE17E68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42DD1EA-E5F1-488A-A452-5DFBF6334E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,9 +159,6 @@
     <t>Show inline errors</t>
   </si>
   <si>
-    <t>Auto-login user upon successful sign up</t>
-  </si>
-  <si>
     <t>S</t>
   </si>
   <si>
@@ -3010,139 +3007,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. T&amp;C screen navigation and reverse navigation to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign Up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen via </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ok</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button works
-2. Camera open, close, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Retake</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ok</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> navigations work
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign In</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> navigates to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sign In</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
     <t>Sign In screen renders without crashing
 1. Email input is visible
 2. Password input is visible
@@ -3150,7 +3014,194 @@
 4. Sign Up hyperlink is visible</t>
   </si>
   <si>
-    <t>ID and Selfie matching accuracy ~ 80%</t>
+    <r>
+      <t xml:space="preserve">1. T&amp;C screen navigation and reverse navigation to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign Up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button works
+2. Camera open, close, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retake</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ok</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> navigations work
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> navigates to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sign In</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen
+(MANUAL/e2e TESTING)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Auto-login user upon successful sign up
+2. Do not let the user to continue until all details are filled and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">T&amp;C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>is checked</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. ID and Selfie matching accuracy ~ 80% (MANUAL/e2e TESTING)
+2. Sign up attempt with duplicate email does NOT work
+3. Sign up attempt with password length less than 6 characters does NOT work
+4. Sign up attempt without checking in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">T&amp;C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkbox does not work</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3519,23 +3570,20 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3555,20 +3603,23 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3893,7 +3944,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -3905,7 +3956,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>3</v>
@@ -3921,7 +3972,7 @@
       </c>
       <c r="J1" s="5">
         <f>SUM(J2:J79)</f>
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>5</v>
@@ -3941,16 +3992,16 @@
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>48</v>
-      </c>
       <c r="G2" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I2" s="19" cm="1">
         <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3976,16 +4027,16 @@
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I3" s="19" cm="1">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4011,16 +4062,16 @@
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
       <c r="E4" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I4" s="19" cm="1">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4046,16 +4097,16 @@
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I5" s="11" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4081,16 +4132,16 @@
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>62</v>
-      </c>
       <c r="G6" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="11" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4116,16 +4167,16 @@
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" s="11" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4151,16 +4202,16 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I8" s="11" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4186,16 +4237,16 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I9" s="11" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4223,16 +4274,16 @@
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
       <c r="E10" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I10" s="21" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4258,16 +4309,16 @@
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
       <c r="E11" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I11" s="21" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4293,16 +4344,16 @@
       <c r="C12" s="21"/>
       <c r="D12" s="21"/>
       <c r="E12" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="21" t="s">
         <v>10</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I12" s="21" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4334,16 +4385,16 @@
         <v>8</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="G13" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I13" s="6" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4375,16 +4426,16 @@
         <v>8</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I14" s="6" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4416,16 +4467,16 @@
         <v>8</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I15" s="6" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4457,16 +4508,16 @@
         <v>8</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="H16" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I16" s="6" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4498,16 +4549,16 @@
         <v>8</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I17" s="6" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4537,16 +4588,16 @@
         <v>8</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I18" s="6" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4576,16 +4627,16 @@
         <v>8</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I19" s="9" cm="1">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4617,16 +4668,16 @@
         <v>8</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I20" s="9" cm="1">
         <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4656,16 +4707,16 @@
         <v>31</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I21" s="13" cm="1">
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4695,16 +4746,16 @@
         <v>31</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I22" s="13" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4734,16 +4785,16 @@
         <v>31</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I23" s="13" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4773,16 +4824,16 @@
         <v>31</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I24" s="13" cm="1">
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4812,16 +4863,16 @@
         <v>31</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I25" s="13" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4851,16 +4902,16 @@
         <v>31</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I26" s="13" cm="1">
         <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4890,16 +4941,16 @@
         <v>31</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I27" s="13" cm="1">
         <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4929,16 +4980,16 @@
         <v>31</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I28" s="13" cm="1">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4970,16 +5021,16 @@
         <v>31</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I29" s="14" cm="1">
         <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5011,16 +5062,16 @@
         <v>31</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I30" s="14" cm="1">
         <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5052,16 +5103,16 @@
         <v>31</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I31" s="14" cm="1">
         <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5090,19 +5141,19 @@
         <v>1.3</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I32" s="23" cm="1">
         <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5131,16 +5182,16 @@
         <v>1.3</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H33" s="36"/>
       <c r="I33" s="36" t="str" cm="1">
@@ -5170,19 +5221,19 @@
         <v>1.3</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I34" s="23" cm="1">
         <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5211,16 +5262,16 @@
         <v>1.3</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F35" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H35" s="36"/>
       <c r="I35" s="36" t="str" cm="1">
@@ -5250,19 +5301,19 @@
         <v>1.3</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F36" s="24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G36" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I36" s="23" cm="1">
         <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5291,19 +5342,19 @@
         <v>1.3</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F37" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I37" s="23" cm="1">
         <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5332,25 +5383,25 @@
         <v>1.3</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="G38" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="G38" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="H38" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="I38" s="48" cm="1">
+      <c r="H38" s="47" t="s">
+        <v>41</v>
+      </c>
+      <c r="I38" s="47" cm="1">
         <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J38" s="48">
+      <c r="J38" s="47">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -5373,18 +5424,18 @@
         <v>1.3</v>
       </c>
       <c r="D39" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F39" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="F39" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
       <c r="K39" s="25" t="s">
         <v>28</v>
       </c>
@@ -5404,18 +5455,18 @@
         <v>1.3</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
+        <v>76</v>
+      </c>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
       <c r="K40" s="36" t="s">
         <v>28</v>
       </c>
@@ -5435,18 +5486,18 @@
         <v>1.3</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
+        <v>77</v>
+      </c>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
       <c r="K41" s="25" t="s">
         <v>28</v>
       </c>
@@ -5466,18 +5517,18 @@
         <v>1.3</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="G42" s="49"/>
-      <c r="H42" s="49"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
+        <v>74</v>
+      </c>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48"/>
+      <c r="J42" s="48"/>
       <c r="K42" s="25" t="s">
         <v>28</v>
       </c>
@@ -5497,18 +5548,18 @@
         <v>1.3</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
+        <v>75</v>
+      </c>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
       <c r="K43" s="25" t="s">
         <v>28</v>
       </c>
@@ -5528,18 +5579,18 @@
         <v>1.3</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E44" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="G44" s="49"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
+        <v>81</v>
+      </c>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
       <c r="K44" s="25" t="s">
         <v>28</v>
       </c>
@@ -5559,18 +5610,18 @@
         <v>1.3</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E45" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="G45" s="49"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
+        <v>78</v>
+      </c>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="48"/>
       <c r="K45" s="25" t="s">
         <v>28</v>
       </c>
@@ -5590,18 +5641,18 @@
         <v>1.3</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="G46" s="50"/>
-      <c r="H46" s="50"/>
-      <c r="I46" s="50"/>
-      <c r="J46" s="50"/>
+        <v>82</v>
+      </c>
+      <c r="G46" s="49"/>
+      <c r="H46" s="49"/>
+      <c r="I46" s="49"/>
+      <c r="J46" s="49"/>
       <c r="K46" s="25" t="s">
         <v>28</v>
       </c>
@@ -5619,25 +5670,25 @@
         <v>1.4</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="G47" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="H47" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="I47" s="45" cm="1">
+        <v>102</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" s="44" t="s">
+        <v>34</v>
+      </c>
+      <c r="I47" s="44" cm="1">
         <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J47" s="45">
+      <c r="J47" s="44">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -5658,18 +5709,18 @@
         <v>1.4</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E48" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F48" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="G48" s="46"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
+        <v>103</v>
+      </c>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
       <c r="K48" s="27" t="s">
         <v>28</v>
       </c>
@@ -5687,18 +5738,18 @@
         <v>1.4</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E49" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F49" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="G49" s="46"/>
-      <c r="H49" s="46"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
+        <v>93</v>
+      </c>
+      <c r="G49" s="45"/>
+      <c r="H49" s="45"/>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
       <c r="K49" s="27" t="s">
         <v>28</v>
       </c>
@@ -5716,18 +5767,18 @@
         <v>1.4</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E50" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F50" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="G50" s="47"/>
-      <c r="H50" s="47"/>
-      <c r="I50" s="47"/>
-      <c r="J50" s="47"/>
+        <v>94</v>
+      </c>
+      <c r="G50" s="46"/>
+      <c r="H50" s="46"/>
+      <c r="I50" s="46"/>
+      <c r="J50" s="46"/>
       <c r="K50" s="27" t="s">
         <v>28</v>
       </c>
@@ -5745,25 +5796,25 @@
         <v>1.4</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="G51" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="G51" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="I51" s="39" cm="1">
+      <c r="H51" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="I51" s="50" cm="1">
         <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J51" s="39">
+      <c r="J51" s="50">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -5784,18 +5835,18 @@
         <v>1.4</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="G52" s="40"/>
-      <c r="H52" s="40"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="40"/>
+        <v>109</v>
+      </c>
+      <c r="G52" s="51"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
+      <c r="J52" s="51"/>
       <c r="K52" s="29" t="s">
         <v>28</v>
       </c>
@@ -5813,18 +5864,18 @@
         <v>1.4</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E53" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="G53" s="40"/>
-      <c r="H53" s="40"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="40"/>
+        <v>92</v>
+      </c>
+      <c r="G53" s="51"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="51"/>
       <c r="K53" s="29" t="s">
         <v>28</v>
       </c>
@@ -5844,18 +5895,18 @@
         <v>1.4</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F54" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
+        <v>97</v>
+      </c>
+      <c r="G54" s="52"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="52"/>
       <c r="K54" s="29" t="s">
         <v>28</v>
       </c>
@@ -5873,25 +5924,25 @@
         <v>1.5</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="G55" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="H55" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="I55" s="42" cm="1">
+        <v>100</v>
+      </c>
+      <c r="G55" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="H55" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="I55" s="53" cm="1">
         <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J55" s="42">
+      <c r="J55" s="53">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -5912,18 +5963,18 @@
         <v>1.5</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="G56" s="43"/>
-      <c r="H56" s="43"/>
-      <c r="I56" s="43"/>
-      <c r="J56" s="43"/>
+        <v>101</v>
+      </c>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54"/>
+      <c r="I56" s="54"/>
+      <c r="J56" s="54"/>
       <c r="K56" s="34" t="s">
         <v>28</v>
       </c>
@@ -5941,18 +5992,18 @@
         <v>1.5</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E57" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="G57" s="43"/>
-      <c r="H57" s="43"/>
-      <c r="I57" s="43"/>
-      <c r="J57" s="43"/>
+        <v>110</v>
+      </c>
+      <c r="G57" s="54"/>
+      <c r="H57" s="54"/>
+      <c r="I57" s="54"/>
+      <c r="J57" s="54"/>
       <c r="K57" s="34" t="s">
         <v>28</v>
       </c>
@@ -5970,18 +6021,18 @@
         <v>1.5</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F58" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="G58" s="44"/>
-      <c r="H58" s="44"/>
-      <c r="I58" s="44"/>
-      <c r="J58" s="44"/>
+        <v>111</v>
+      </c>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
+      <c r="J58" s="55"/>
       <c r="K58" s="34" t="s">
         <v>28</v>
       </c>
@@ -6001,19 +6052,19 @@
         <v>1.5</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E59" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F59" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G59" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H59" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I59" s="32" cm="1">
         <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6042,19 +6093,19 @@
         <v>1.5</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E60" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F60" s="33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G60" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H60" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I60" s="32" cm="1">
         <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6083,19 +6134,19 @@
         <v>1.5</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E61" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F61" s="33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H61" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I61" s="32" cm="1">
         <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6114,738 +6165,738 @@
       </c>
     </row>
     <row r="62" spans="1:13" s="18" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="51">
+      <c r="A62" s="39">
         <v>63</v>
       </c>
-      <c r="B62" s="51" t="s">
+      <c r="B62" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="51">
+      <c r="C62" s="39">
         <v>1.6</v>
       </c>
-      <c r="D62" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="E62" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="F62" s="52" t="s">
-        <v>124</v>
-      </c>
-      <c r="G62" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="H62" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="I62" s="51" cm="1">
+      <c r="D62" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E62" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F62" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="G62" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="H62" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I62" s="39" cm="1">
         <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J62" s="51">
+      <c r="J62" s="39">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K62" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="L62" s="51"/>
-      <c r="M62" s="51" t="s">
+      <c r="K62" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="L62" s="39"/>
+      <c r="M62" s="39" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:13" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="51">
+      <c r="A63" s="39">
         <v>64</v>
       </c>
-      <c r="B63" s="51" t="s">
+      <c r="B63" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C63" s="51">
+      <c r="C63" s="39">
         <v>1.6</v>
       </c>
-      <c r="D63" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="E63" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="F63" s="52" t="s">
-        <v>123</v>
-      </c>
-      <c r="G63" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="H63" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="I63" s="51" cm="1">
+      <c r="D63" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E63" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F63" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="G63" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="H63" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I63" s="39" cm="1">
         <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J63" s="51">
+      <c r="J63" s="39">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K63" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="L63" s="51"/>
-      <c r="M63" s="51" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="51">
+      <c r="K63" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="L63" s="39"/>
+      <c r="M63" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A64" s="39">
         <v>65</v>
       </c>
-      <c r="B64" s="51" t="s">
+      <c r="B64" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C64" s="51">
+      <c r="C64" s="39">
         <v>1.6</v>
       </c>
-      <c r="D64" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="E64" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="F64" s="52" t="s">
+      <c r="D64" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E64" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F64" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="G64" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="H64" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="I64" s="51" cm="1">
+      <c r="G64" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="H64" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I64" s="39" cm="1">
         <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J64" s="51">
+      <c r="J64" s="39">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K64" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="L64" s="51"/>
-      <c r="M64" s="51" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="51">
+      <c r="K64" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="L64" s="39"/>
+      <c r="M64" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="39">
         <v>66</v>
       </c>
-      <c r="B65" s="51" t="s">
+      <c r="B65" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="51">
+      <c r="C65" s="39">
         <v>2.6</v>
       </c>
-      <c r="D65" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="E65" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="F65" s="52" t="s">
+      <c r="D65" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E65" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="F65" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="G65" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="H65" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="I65" s="51" cm="1">
+      <c r="G65" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="H65" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I65" s="39" cm="1">
         <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J65" s="51">
+      <c r="J65" s="39">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K65" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="L65" s="51"/>
-      <c r="M65" s="51" t="s">
+      <c r="K65" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="L65" s="39"/>
+      <c r="M65" s="39" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="54">
+      <c r="A66" s="42">
         <v>67</v>
       </c>
-      <c r="B66" s="54" t="s">
+      <c r="B66" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="54">
+      <c r="C66" s="42">
         <v>1.6</v>
       </c>
-      <c r="D66" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E66" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F66" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="G66" s="54" t="s">
+      <c r="D66" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E66" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F66" s="43" t="s">
+        <v>113</v>
+      </c>
+      <c r="G66" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H66" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="I66" s="54" cm="1">
+      <c r="H66" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I66" s="42" cm="1">
         <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J66" s="54">
+      <c r="J66" s="42">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K66" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L66" s="54"/>
-      <c r="M66" s="54" t="s">
+      <c r="K66" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L66" s="42"/>
+      <c r="M66" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="54">
+      <c r="A67" s="42">
         <v>68</v>
       </c>
-      <c r="B67" s="54" t="s">
+      <c r="B67" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C67" s="54">
+      <c r="C67" s="42">
         <v>1.6</v>
       </c>
-      <c r="D67" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E67" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F67" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="G67" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="H67" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="I67" s="54" cm="1">
+      <c r="D67" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E67" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F67" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="G67" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="H67" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I67" s="42" cm="1">
         <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J67" s="54">
+      <c r="J67" s="42">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K67" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L67" s="54"/>
-      <c r="M67" s="54" t="s">
+      <c r="K67" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L67" s="42"/>
+      <c r="M67" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A68" s="54">
+      <c r="A68" s="42">
         <v>69</v>
       </c>
-      <c r="B68" s="54" t="s">
+      <c r="B68" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="54">
+      <c r="C68" s="42">
         <v>1.6</v>
       </c>
-      <c r="D68" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E68" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F68" s="55" t="s">
+      <c r="D68" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E68" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F68" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="G68" s="54" t="s">
+      <c r="G68" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H68" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="I68" s="54" cm="1">
+      <c r="H68" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="I68" s="42" cm="1">
         <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J68" s="54">
+      <c r="J68" s="42">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K68" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L68" s="54"/>
-      <c r="M68" s="54" t="s">
+      <c r="K68" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L68" s="42"/>
+      <c r="M68" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="54">
+      <c r="A69" s="42">
         <v>70</v>
       </c>
-      <c r="B69" s="54" t="s">
+      <c r="B69" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="54">
+      <c r="C69" s="42">
         <v>1.6</v>
       </c>
-      <c r="D69" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E69" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F69" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="G69" s="54" t="s">
+      <c r="D69" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E69" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F69" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="G69" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H69" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="I69" s="54" cm="1">
+      <c r="H69" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="I69" s="42" cm="1">
         <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J69" s="54">
+      <c r="J69" s="42">
         <f t="shared" ref="J69:J88" si="1">I69</f>
         <v>2</v>
       </c>
-      <c r="K69" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L69" s="54"/>
-      <c r="M69" s="54" t="s">
+      <c r="K69" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L69" s="42"/>
+      <c r="M69" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="54">
+      <c r="A70" s="42">
         <v>71</v>
       </c>
-      <c r="B70" s="54" t="s">
+      <c r="B70" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="54">
+      <c r="C70" s="42">
         <v>1.6</v>
       </c>
-      <c r="D70" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E70" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F70" s="55" t="s">
-        <v>125</v>
-      </c>
-      <c r="G70" s="54" t="s">
+      <c r="D70" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E70" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F70" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="G70" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H70" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="I70" s="54" cm="1">
+      <c r="H70" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="I70" s="42" cm="1">
         <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="J70" s="54">
+      <c r="J70" s="42">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K70" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L70" s="54"/>
-      <c r="M70" s="54" t="s">
+      <c r="K70" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L70" s="42"/>
+      <c r="M70" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="54">
+      <c r="A71" s="42">
         <v>72</v>
       </c>
-      <c r="B71" s="54" t="s">
+      <c r="B71" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="54">
+      <c r="C71" s="42">
         <v>1.6</v>
       </c>
-      <c r="D71" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E71" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F71" s="55" t="s">
-        <v>126</v>
-      </c>
-      <c r="G71" s="54" t="s">
+      <c r="D71" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E71" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F71" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="G71" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H71" s="54" t="s">
-        <v>42</v>
-      </c>
-      <c r="I71" s="54" cm="1">
+      <c r="H71" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="I71" s="42" cm="1">
         <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J71" s="54">
+      <c r="J71" s="42">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K71" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L71" s="54"/>
-      <c r="M71" s="54" t="s">
+      <c r="K71" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L71" s="42"/>
+      <c r="M71" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A72" s="54">
+      <c r="A72" s="42">
         <v>73</v>
       </c>
-      <c r="B72" s="54" t="s">
+      <c r="B72" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C72" s="54">
+      <c r="C72" s="42">
         <v>1.6</v>
       </c>
-      <c r="D72" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E72" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F72" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="G72" s="54" t="s">
-        <v>39</v>
-      </c>
-      <c r="H72" s="54" t="s">
+      <c r="D72" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E72" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F72" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="G72" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="I72" s="54" cm="1">
+      <c r="H72" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="I72" s="42" cm="1">
         <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="J72" s="54">
+      <c r="J72" s="42">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="K72" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L72" s="54"/>
-      <c r="M72" s="54" t="s">
+      <c r="K72" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L72" s="42"/>
+      <c r="M72" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="54">
+      <c r="A73" s="42">
         <v>74</v>
       </c>
-      <c r="B73" s="54"/>
-      <c r="C73" s="54">
+      <c r="B73" s="42"/>
+      <c r="C73" s="42">
         <v>1.6</v>
       </c>
-      <c r="D73" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E73" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F73" s="55" t="s">
-        <v>118</v>
-      </c>
-      <c r="G73" s="54" t="s">
-        <v>39</v>
-      </c>
-      <c r="H73" s="54" t="s">
-        <v>42</v>
-      </c>
-      <c r="I73" s="54" cm="1">
+      <c r="D73" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E73" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F73" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="G73" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="H73" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="I73" s="42" cm="1">
         <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J73" s="54">
+      <c r="J73" s="42">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K73" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L73" s="54"/>
-      <c r="M73" s="54" t="s">
+      <c r="K73" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L73" s="42"/>
+      <c r="M73" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="54">
+      <c r="A74" s="42">
         <v>75</v>
       </c>
-      <c r="B74" s="54" t="s">
+      <c r="B74" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C74" s="54">
+      <c r="C74" s="42">
         <v>1.6</v>
       </c>
-      <c r="D74" s="54" t="s">
+      <c r="D74" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E74" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F74" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="E74" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F74" s="55" t="s">
-        <v>67</v>
-      </c>
-      <c r="G74" s="54" t="s">
+      <c r="G74" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H74" s="54" t="s">
-        <v>42</v>
-      </c>
-      <c r="I74" s="54" cm="1">
+      <c r="H74" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="I74" s="42" cm="1">
         <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J74" s="54">
+      <c r="J74" s="42">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K74" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L74" s="54"/>
-      <c r="M74" s="54" t="s">
+      <c r="K74" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L74" s="42"/>
+      <c r="M74" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="54">
+      <c r="A75" s="42">
         <v>76</v>
       </c>
-      <c r="B75" s="54" t="s">
+      <c r="B75" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="54">
+      <c r="C75" s="42">
         <v>1.6</v>
       </c>
-      <c r="D75" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E75" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F75" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="G75" s="54" t="s">
+      <c r="D75" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E75" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F75" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="G75" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H75" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="I75" s="54" cm="1">
+      <c r="H75" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75" s="42" cm="1">
         <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J75" s="54">
+      <c r="J75" s="42">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K75" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L75" s="54"/>
-      <c r="M75" s="54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A76" s="54">
+      <c r="K75" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L75" s="42"/>
+      <c r="M75" s="42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="42">
         <v>77</v>
       </c>
-      <c r="B76" s="54" t="s">
+      <c r="B76" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="54">
+      <c r="C76" s="42">
         <v>1.6</v>
       </c>
-      <c r="D76" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E76" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F76" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="G76" s="54" t="s">
+      <c r="D76" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E76" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F76" s="43" t="s">
+        <v>128</v>
+      </c>
+      <c r="G76" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H76" s="54" t="s">
-        <v>45</v>
-      </c>
-      <c r="I76" s="54" cm="1">
+      <c r="H76" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="I76" s="42" cm="1">
         <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J76" s="54">
+      <c r="J76" s="42">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K76" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L76" s="54"/>
-      <c r="M76" s="54" t="s">
+      <c r="K76" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L76" s="42"/>
+      <c r="M76" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="54">
+      <c r="A77" s="42">
         <v>78</v>
       </c>
-      <c r="B77" s="54" t="s">
+      <c r="B77" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C77" s="54">
+      <c r="C77" s="42">
         <v>1.6</v>
       </c>
-      <c r="D77" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E77" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F77" s="55" t="s">
+      <c r="D77" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E77" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F77" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="G77" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="H77" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="I77" s="42" cm="1">
+        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J77" s="42">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K77" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L77" s="42"/>
+      <c r="M77" s="42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="42">
+        <v>79</v>
+      </c>
+      <c r="B78" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="42">
+        <v>1.6</v>
+      </c>
+      <c r="D78" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E78" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F78" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="G77" s="54" t="s">
+      <c r="G78" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H77" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="I77" s="54" cm="1">
-        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H78" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="I78" s="42" cm="1">
+        <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J78" s="42">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K78" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L78" s="42"/>
+      <c r="M78" s="42" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="42">
+        <v>80</v>
+      </c>
+      <c r="B79" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="42">
+        <v>1.6</v>
+      </c>
+      <c r="D79" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="E79" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="F79" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="G79" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="H79" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="I79" s="42" cm="1">
+        <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J77" s="54">
+      <c r="J79" s="42">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K77" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L77" s="54"/>
-      <c r="M77" s="54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="54">
-        <v>79</v>
-      </c>
-      <c r="B78" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="54">
-        <v>1.6</v>
-      </c>
-      <c r="D78" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E78" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F78" s="55" t="s">
-        <v>121</v>
-      </c>
-      <c r="G78" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="H78" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="I78" s="54" cm="1">
-        <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J78" s="54">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K78" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L78" s="54"/>
-      <c r="M78" s="54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="54">
-        <v>80</v>
-      </c>
-      <c r="B79" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="54">
-        <v>1.6</v>
-      </c>
-      <c r="D79" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="E79" s="54" t="s">
-        <v>57</v>
-      </c>
-      <c r="F79" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="G79" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="H79" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="I79" s="54" cm="1">
-        <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J79" s="54">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="K79" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="L79" s="54"/>
-      <c r="M79" s="54" t="s">
+      <c r="K79" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L79" s="42"/>
+      <c r="M79" s="42" t="s">
         <v>9</v>
       </c>
     </row>
@@ -6866,7 +6917,7 @@
         <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J80" s="53" t="str">
+      <c r="J80" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6891,7 +6942,7 @@
         <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J81" s="53" t="str">
+      <c r="J81" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6916,7 +6967,7 @@
         <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J82" s="53" t="str">
+      <c r="J82" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6941,7 +6992,7 @@
         <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J83" s="53" t="str">
+      <c r="J83" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6966,7 +7017,7 @@
         <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J84" s="53" t="str">
+      <c r="J84" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6991,7 +7042,7 @@
         <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J85" s="53" t="str">
+      <c r="J85" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7016,7 +7067,7 @@
         <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J86" s="53" t="str">
+      <c r="J86" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7041,7 +7092,7 @@
         <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J87" s="53" t="str">
+      <c r="J87" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7066,7 +7117,7 @@
         <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J88" s="53" t="str">
+      <c r="J88" s="41" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -7076,6 +7127,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="J51:J54"/>
+    <mergeCell ref="G55:G58"/>
+    <mergeCell ref="H55:H58"/>
+    <mergeCell ref="I55:I58"/>
+    <mergeCell ref="J55:J58"/>
+    <mergeCell ref="G51:G54"/>
+    <mergeCell ref="H51:H54"/>
+    <mergeCell ref="I51:I54"/>
     <mergeCell ref="H47:H50"/>
     <mergeCell ref="I47:I50"/>
     <mergeCell ref="G47:G50"/>
@@ -7084,14 +7143,6 @@
     <mergeCell ref="H38:H46"/>
     <mergeCell ref="I38:I46"/>
     <mergeCell ref="J38:J46"/>
-    <mergeCell ref="J51:J54"/>
-    <mergeCell ref="G55:G58"/>
-    <mergeCell ref="H55:H58"/>
-    <mergeCell ref="I55:I58"/>
-    <mergeCell ref="J55:J58"/>
-    <mergeCell ref="G51:G54"/>
-    <mergeCell ref="H51:H54"/>
-    <mergeCell ref="I51:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7152,7 +7203,7 @@
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">

--- a/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42DD1EA-E5F1-488A-A452-5DFBF6334E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A3B0E1-C312-49D8-83B4-6FC31937EBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Board" sheetId="1" r:id="rId1"/>
-    <sheet name="Daily Standup Guide" sheetId="2" r:id="rId2"/>
-    <sheet name="Burndown" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="Daily Standup Guide" sheetId="2" r:id="rId3"/>
+    <sheet name="Burndown" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="133">
   <si>
     <t>Epic</t>
   </si>
@@ -709,206 +710,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. Create AuthContext to manage authentication state globally
-2. Define </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>authStatus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> enum: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>UNKNOWN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AUTHENTICATED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>UNAUTHENTICATED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-3. On app startup, check for stored auth token for the user
-4. Set authStatus to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AUTHENTICATED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> if token </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>exists</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-5. Set authStatus to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>UNAUTHENTICATED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> if token does not </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>exist</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-6. Ensure Splash screen </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>waits</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> until authStatus is resolved
-7. Expose authStatus globally</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Add entryResolve logic for separating renter, lister(owner) based on </t>
     </r>
     <r>
@@ -946,29 +747,6 @@
   <si>
     <t>1. Prevent multiple submissions
 2. Implement loading state while login is underway</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Disable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Sign In button when both or any one inputs (Email, Password)are empty</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1004,11 +782,6 @@
 1. Button- testID = "SignInButton"</t>
   </si>
   <si>
-    <t>1. Sign In button is disabled when email is empty
-2. Sign In button is disabled when password is empty
-3. Sign In button is enabled when both fields are filled</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">1. Create </t>
     </r>
@@ -1388,10 +1161,6 @@
 1. Calls a mockFunction()
 2. navigates to Sign Up screen layout (MANUAL/e2e TESTING)</t>
     </r>
-  </si>
-  <si>
-    <t>1. Multiple rapid presses do not trigger multiple signin calls (MANUAL/e2e TESTING)
-2. Loading indicator is shown during login attempt (MANUAL/e2e TESTING)</t>
   </si>
   <si>
     <r>
@@ -3202,6 +2971,33 @@
       </rPr>
       <t>checkbox does not work</t>
     </r>
+  </si>
+  <si>
+    <t>1. Create AuthContext to manage authentication state globally
+2. Define authStatus enum: UNKNOWN / AUTHENTICATED / UNAUTHENTICATED
+3. On app startup, check for stored auth token for the user
+4. Set authStatus to AUTHENTICATED if token exists
+5. Set authStatus to UNAUTHENTICATED if token does not exist
+6. Ensure Splash screen waits until authStatus is resolved
+7. Expose authStatus globally</t>
+  </si>
+  <si>
+    <t>KYC</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>Actual Story Points Left</t>
+  </si>
+  <si>
+    <t>Expected Story Points Left</t>
+  </si>
+  <si>
+    <t>Story Points Done</t>
   </si>
 </sst>
 </file>
@@ -3284,7 +3080,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3377,12 +3173,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3390,6 +3180,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3458,7 +3260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3567,7 +3369,7 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3576,14 +3378,23 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3603,23 +3414,71 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3636,6 +3495,1004 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual Story Points Left</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>148</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-93A3-4D70-A15D-11D521EE13C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Expected Story Points Left</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>140.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>124.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>109.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>93.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>62.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15.599999999999994</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-93A3-4D70-A15D-11D521EE13C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="228576623"/>
+        <c:axId val="228581423"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="228576623"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228581423"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="228581423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="228576623"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4606402-996D-6CA4-C8E9-5276D0F88F29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3923,7 +4780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="1" customWidth="1"/>
@@ -3936,13 +4793,14 @@
     <col min="8" max="8" width="13.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="4.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>48</v>
       </c>
@@ -3971,20 +4829,24 @@
         <v>32</v>
       </c>
       <c r="J1" s="5">
-        <f>SUM(J2:J79)</f>
-        <v>158</v>
-      </c>
-      <c r="K1" s="5" t="s">
+        <f>SUM(J2:J76)</f>
+        <v>156</v>
+      </c>
+      <c r="K1" s="5">
+        <f>SUM(K2:K76)</f>
+        <v>156</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="19">
         <v>1</v>
       </c>
@@ -4011,15 +4873,19 @@
         <f>I2</f>
         <v>8</v>
       </c>
-      <c r="K2" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19" t="s">
+      <c r="K2" s="19">
+        <f>J2</f>
+        <v>8</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="19">
         <v>2</v>
       </c>
@@ -4043,18 +4909,22 @@
         <v>5</v>
       </c>
       <c r="J3" s="19">
-        <f t="shared" ref="J3:J68" si="0">I3</f>
+        <f t="shared" ref="J3:K64" si="0">I3</f>
         <v>5</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="19">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L3" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="19"/>
+      <c r="N3" s="19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>3</v>
       </c>
@@ -4081,15 +4951,19 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L4" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19" t="s">
+      <c r="M4" s="19"/>
+      <c r="N4" s="19" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>4</v>
       </c>
@@ -4100,7 +4974,7 @@
         <v>60</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>39</v>
@@ -4116,15 +4990,19 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="11"/>
+      <c r="N5" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>5</v>
       </c>
@@ -4151,15 +5029,19 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="11">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="11"/>
+      <c r="N6" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>6</v>
       </c>
@@ -4186,15 +5068,19 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="11">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="11"/>
+      <c r="N7" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>7</v>
       </c>
@@ -4221,15 +5107,19 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="11">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="L8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="11"/>
+      <c r="N8" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>8</v>
       </c>
@@ -4240,7 +5130,7 @@
         <v>56</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>39</v>
@@ -4256,17 +5146,21 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="11">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="11">
+      <c r="M9" s="11">
         <v>32</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="N9" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A10" s="21">
         <v>10</v>
       </c>
@@ -4277,7 +5171,7 @@
         <v>56</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G10" s="21" t="s">
         <v>39</v>
@@ -4293,15 +5187,19 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K10" s="21" t="s">
+      <c r="K10" s="21">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L10" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21" t="s">
+      <c r="M10" s="21"/>
+      <c r="N10" s="21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="21">
         <v>9</v>
       </c>
@@ -4328,52 +5226,65 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K11" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="21">
-        <v>11</v>
-      </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" s="21" cm="1">
-        <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J12" s="21">
+      <c r="K11" s="21">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="L11" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21" t="s">
+      <c r="M11" s="21"/>
+      <c r="N11" s="21" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>12</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="6" cm="1">
+        <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="53">
+        <v>9</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>7</v>
@@ -4388,7 +5299,7 @@
         <v>49</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>55</v>
@@ -4404,17 +5315,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="54"/>
+      <c r="L13" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="6"/>
+      <c r="N13" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>7</v>
@@ -4428,8 +5340,8 @@
       <c r="E14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>51</v>
+      <c r="F14" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>55</v>
@@ -4445,17 +5357,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="54"/>
+      <c r="L14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="6"/>
+      <c r="N14" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>7</v>
@@ -4470,7 +5383,7 @@
         <v>49</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>55</v>
@@ -4486,17 +5399,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="54"/>
+      <c r="L15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="6"/>
+      <c r="N15" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>7</v>
@@ -4510,8 +5424,8 @@
       <c r="E16" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>54</v>
+      <c r="F16" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>55</v>
@@ -4527,17 +5441,16 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="54"/>
+      <c r="L16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>7</v>
@@ -4552,7 +5465,7 @@
         <v>49</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>55</v>
@@ -4568,54 +5481,58 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="54"/>
+      <c r="L17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="6"/>
       <c r="M17" s="6"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="6">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
+        <v>18</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="9">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H18" s="6" t="s">
+      <c r="E18" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="6" cm="1">
+      <c r="I18" s="9" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="54"/>
+      <c r="L18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-    </row>
-    <row r="19" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="M18" s="9"/>
+      <c r="N18" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>7</v>
@@ -4630,74 +5547,76 @@
         <v>56</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I19" s="9" cm="1">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="9">
         <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K19" s="55"/>
+      <c r="L19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="13">
+        <v>20</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="13" cm="1">
+        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="J20" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K20" s="56">
+        <v>18</v>
+      </c>
+      <c r="L20" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9" t="s">
+      <c r="M20" s="13"/>
+      <c r="N20" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
-        <v>19</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="9">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="9" cm="1">
-        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J20" s="9">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K20" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13">
@@ -4710,7 +5629,7 @@
         <v>49</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>55</v>
@@ -4726,17 +5645,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="K21" s="57"/>
+      <c r="L21" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13" t="s">
+      <c r="M21" s="13"/>
+      <c r="N21" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13">
@@ -4749,7 +5669,7 @@
         <v>49</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>55</v>
@@ -4765,17 +5685,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K22" s="13" t="s">
+      <c r="K22" s="57"/>
+      <c r="L22" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13" t="s">
+      <c r="M22" s="13"/>
+      <c r="N22" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13">
@@ -4788,7 +5709,7 @@
         <v>49</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>55</v>
@@ -4804,17 +5725,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K23" s="13" t="s">
+      <c r="K23" s="57"/>
+      <c r="L23" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13" t="s">
+      <c r="M23" s="13"/>
+      <c r="N23" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13">
@@ -4826,8 +5748,8 @@
       <c r="E24" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="16" t="s">
-        <v>105</v>
+      <c r="F24" s="17" t="s">
+        <v>102</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>55</v>
@@ -4843,17 +5765,18 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="K24" s="57"/>
+      <c r="L24" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13" t="s">
+      <c r="M24" s="13"/>
+      <c r="N24" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="13">
@@ -4866,33 +5789,34 @@
         <v>49</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>55</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I25" s="13" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="13">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K25" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" s="57"/>
+      <c r="L25" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13" t="s">
+      <c r="M25" s="13"/>
+      <c r="N25" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13">
@@ -4905,7 +5829,7 @@
         <v>49</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>55</v>
@@ -4921,17 +5845,18 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K26" s="13" t="s">
+      <c r="K26" s="57"/>
+      <c r="L26" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13" t="s">
+      <c r="M26" s="13"/>
+      <c r="N26" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13">
@@ -4944,7 +5869,7 @@
         <v>49</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>55</v>
@@ -4960,56 +5885,60 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K27" s="13" t="s">
+      <c r="K27" s="57"/>
+      <c r="L27" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13" t="s">
+      <c r="M27" s="13"/>
+      <c r="N27" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
-        <v>29</v>
-      </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13">
+    <row r="28" spans="1:14" s="18" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="14">
+        <v>30</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="14">
         <v>1.2</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="H28" s="13" t="s">
+      <c r="E28" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="I28" s="13" cm="1">
+      <c r="I28" s="14" cm="1">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="14">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K28" s="13" t="s">
+      <c r="K28" s="57"/>
+      <c r="L28" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13" t="s">
+      <c r="M28" s="14"/>
+      <c r="N28" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="18" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>7</v>
@@ -5024,7 +5953,7 @@
         <v>56</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>10</v>
@@ -5040,17 +5969,18 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K29" s="14" t="s">
+      <c r="K29" s="57"/>
+      <c r="L29" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14" t="s">
+      <c r="M29" s="14"/>
+      <c r="N29" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>7</v>
@@ -5065,74 +5995,78 @@
         <v>56</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I30" s="14" cm="1">
         <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K30" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="K30" s="58"/>
+      <c r="L30" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14" t="s">
+      <c r="M30" s="14"/>
+      <c r="N30" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="14">
-        <v>32</v>
-      </c>
-      <c r="B31" s="14" t="s">
+    <row r="31" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="23">
+        <v>33</v>
+      </c>
+      <c r="B31" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G31" s="14" t="s">
+      <c r="C31" s="23">
+        <v>1.3</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="H31" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="14" cm="1">
+      <c r="I31" s="23" cm="1">
         <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J31" s="14">
+      <c r="J31" s="23">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K31" s="14" t="s">
+      <c r="K31" s="59">
+        <v>14</v>
+      </c>
+      <c r="L31" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14" t="s">
+      <c r="M31" s="23"/>
+      <c r="N31" s="23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A32" s="23">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" s="23" t="s">
         <v>7</v>
@@ -5141,13 +6075,13 @@
         <v>1.3</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E32" s="23" t="s">
         <v>49</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G32" s="23" t="s">
         <v>55</v>
@@ -5163,56 +6097,60 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K32" s="23" t="s">
+      <c r="K32" s="60"/>
+      <c r="L32" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="L32" s="23"/>
-      <c r="M32" s="23" t="s">
+      <c r="M32" s="23"/>
+      <c r="N32" s="23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="38" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="36">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="23">
+        <v>36</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="23">
+        <v>1.3</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="36">
-        <v>1.3</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="F33" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="G33" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36" t="str" cm="1">
+      <c r="I33" s="23" cm="1">
         <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="36" t="str">
+        <v>2</v>
+      </c>
+      <c r="J33" s="23">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K33" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="K33" s="60"/>
+      <c r="L33" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="L33" s="36"/>
-      <c r="M33" s="36" t="s">
+      <c r="M33" s="23"/>
+      <c r="N33" s="23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="23">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>7</v>
@@ -5221,160 +6159,156 @@
         <v>1.3</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E34" s="23" t="s">
         <v>49</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G34" s="23" t="s">
         <v>55</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I34" s="23" cm="1">
         <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" s="23">
         <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K34" s="60"/>
+      <c r="L34" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="M34" s="23"/>
+      <c r="N34" s="23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="23">
+        <v>39</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="23">
+        <v>1.3</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="G35" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="I35" s="23" cm="1">
+        <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="K34" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="L34" s="23"/>
-      <c r="M34" s="23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" s="38" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="36">
-        <v>36</v>
-      </c>
-      <c r="B35" s="36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="36">
-        <v>1.3</v>
-      </c>
-      <c r="D35" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="G35" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36" t="str" cm="1">
-        <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="36" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K35" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="23">
-        <v>37</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="23">
-        <v>1.3</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="G36" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="I36" s="23" cm="1">
-        <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J36" s="23">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K36" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="23">
-        <v>38</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="23">
-        <v>1.3</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F37" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="G37" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="H37" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I37" s="23" cm="1">
-        <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J37" s="23">
+      <c r="J35" s="23">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K37" s="23" t="s">
+      <c r="K35" s="60"/>
+      <c r="L35" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23" t="s">
+      <c r="M35" s="23"/>
+      <c r="N35" s="23" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A36" s="25">
+        <v>40</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="I36" s="50" cm="1">
+        <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J36" s="50">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="K36" s="60"/>
+      <c r="L36" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="25">
+        <v>41</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="25">
+        <v>1.3</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="25">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B38" s="25" t="s">
         <v>7</v>
@@ -5383,39 +6317,30 @@
         <v>1.3</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E38" s="25" t="s">
         <v>56</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="G38" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="H38" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="I38" s="47" cm="1">
-        <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J38" s="47">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K38" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L38" s="25"/>
-      <c r="M38" s="25" t="s">
+      <c r="M38" s="25"/>
+      <c r="N38" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="25">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B39" s="25" t="s">
         <v>7</v>
@@ -5424,7 +6349,7 @@
         <v>1.3</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E39" s="25" t="s">
         <v>56</v>
@@ -5432,52 +6357,54 @@
       <c r="F39" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="25" t="s">
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
+      <c r="K39" s="60"/>
+      <c r="L39" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L39" s="25"/>
-      <c r="M39" s="25" t="s">
+      <c r="M39" s="25"/>
+      <c r="N39" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="38" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="36">
-        <v>41</v>
-      </c>
-      <c r="B40" s="36" t="s">
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="25">
+        <v>45</v>
+      </c>
+      <c r="B40" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="36">
+      <c r="C40" s="25">
         <v>1.3</v>
       </c>
-      <c r="D40" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E40" s="36" t="s">
+      <c r="D40" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="F40" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="36" t="s">
+      <c r="F40" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L40" s="36"/>
-      <c r="M40" s="36" t="s">
+      <c r="M40" s="25"/>
+      <c r="N40" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="25">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B41" s="25" t="s">
         <v>7</v>
@@ -5486,29 +6413,30 @@
         <v>1.3</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E41" s="25" t="s">
         <v>56</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L41" s="25"/>
-      <c r="M41" s="25" t="s">
+      <c r="M41" s="25"/>
+      <c r="N41" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="25">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B42" s="25" t="s">
         <v>7</v>
@@ -5517,29 +6445,30 @@
         <v>1.3</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E42" s="25" t="s">
         <v>56</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="60"/>
+      <c r="L42" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L42" s="25"/>
-      <c r="M42" s="25" t="s">
+      <c r="M42" s="25"/>
+      <c r="N42" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="25">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B43" s="25" t="s">
         <v>7</v>
@@ -5548,666 +6477,722 @@
         <v>1.3</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E43" s="25" t="s">
         <v>56</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="G43" s="52"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="61"/>
+      <c r="L43" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="L43" s="25"/>
-      <c r="M43" s="25" t="s">
+      <c r="M43" s="25"/>
+      <c r="N43" s="25" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="25">
-        <v>45</v>
-      </c>
-      <c r="B44" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="25">
-        <v>1.3</v>
-      </c>
-      <c r="D44" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E44" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="F44" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="25" t="s">
+    <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="27">
+        <v>49</v>
+      </c>
+      <c r="B44" s="27"/>
+      <c r="C44" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E44" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="G44" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="H44" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="I44" s="47" cm="1">
+        <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J44" s="47">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K44" s="47">
+        <v>5</v>
+      </c>
+      <c r="L44" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="L44" s="25"/>
-      <c r="M44" s="25" t="s">
+      <c r="M44" s="27"/>
+      <c r="N44" s="27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="25">
-        <v>46</v>
-      </c>
-      <c r="B45" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="25">
-        <v>1.3</v>
-      </c>
-      <c r="D45" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E45" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="F45" s="26" t="s">
-        <v>78</v>
+    <row r="45" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="27">
+        <v>50</v>
+      </c>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>99</v>
       </c>
       <c r="G45" s="48"/>
       <c r="H45" s="48"/>
       <c r="I45" s="48"/>
       <c r="J45" s="48"/>
-      <c r="K45" s="25" t="s">
+      <c r="K45" s="48"/>
+      <c r="L45" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="L45" s="25"/>
-      <c r="M45" s="25" t="s">
+      <c r="M45" s="27"/>
+      <c r="N45" s="27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A46" s="25">
-        <v>47</v>
-      </c>
-      <c r="B46" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="25">
-        <v>1.3</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E46" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="F46" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="G46" s="49"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="49"/>
-      <c r="K46" s="25" t="s">
+    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="27">
+        <v>51</v>
+      </c>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27">
+        <v>1.4</v>
+      </c>
+      <c r="D46" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="48"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
+      <c r="L46" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="25"/>
-      <c r="M46" s="25" t="s">
+      <c r="M46" s="27"/>
+      <c r="N46" s="27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="27">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B47" s="27"/>
       <c r="C47" s="27">
         <v>1.4</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E47" s="27" t="s">
         <v>49</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="G47" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="G47" s="49"/>
+      <c r="H47" s="49"/>
+      <c r="I47" s="49"/>
+      <c r="J47" s="49"/>
+      <c r="K47" s="48"/>
+      <c r="L47" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="M47" s="27"/>
+      <c r="N47" s="27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A48" s="29">
+        <v>53</v>
+      </c>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E48" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F48" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="G48" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="H48" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" s="41" cm="1">
+        <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J48" s="41">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="K48" s="48"/>
+      <c r="L48" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A49" s="29">
+        <v>54</v>
+      </c>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E49" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F49" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="48"/>
+      <c r="L49" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="29">
         <v>55</v>
       </c>
-      <c r="H47" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="I47" s="44" cm="1">
-        <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J47" s="44">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K47" s="27" t="s">
+      <c r="B50" s="29"/>
+      <c r="C50" s="29">
+        <v>1.4</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F50" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="48"/>
+      <c r="L50" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27" t="s">
+      <c r="M50" s="29"/>
+      <c r="N50" s="29" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="27">
-        <v>49</v>
-      </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27">
-        <v>1.4</v>
-      </c>
-      <c r="D48" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="E48" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="F48" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="L48" s="27"/>
-      <c r="M48" s="27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="27">
-        <v>50</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27">
-        <v>1.4</v>
-      </c>
-      <c r="D49" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="E49" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="F49" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
-      <c r="K49" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="27">
-        <v>51</v>
-      </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27">
-        <v>1.4</v>
-      </c>
-      <c r="D50" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="E50" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="F50" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="L50" s="27"/>
-      <c r="M50" s="27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="29">
-        <v>52</v>
-      </c>
-      <c r="B51" s="29"/>
+        <v>56</v>
+      </c>
+      <c r="B51" s="29" t="s">
+        <v>7</v>
+      </c>
       <c r="C51" s="29">
         <v>1.4</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E51" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="F51" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="G51" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="H51" s="50" t="s">
+      <c r="F51" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43"/>
+      <c r="I51" s="43"/>
+      <c r="J51" s="43"/>
+      <c r="K51" s="49"/>
+      <c r="L51" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="34">
+        <v>57</v>
+      </c>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F52" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="G52" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="H52" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="I51" s="50" cm="1">
-        <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I52" s="44" cm="1">
+        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J51" s="50">
+      <c r="J52" s="44">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K51" s="29" t="s">
+      <c r="K52" s="44">
+        <v>11</v>
+      </c>
+      <c r="L52" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29" t="s">
+      <c r="M52" s="34"/>
+      <c r="N52" s="34" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A52" s="29">
-        <v>53</v>
-      </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29">
-        <v>1.4</v>
-      </c>
-      <c r="D52" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="E52" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="G52" s="51"/>
-      <c r="H52" s="51"/>
-      <c r="I52" s="51"/>
-      <c r="J52" s="51"/>
-      <c r="K52" s="29" t="s">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="34">
+        <v>58</v>
+      </c>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E53" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F53" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="G53" s="45"/>
+      <c r="H53" s="45"/>
+      <c r="I53" s="45"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29" t="s">
+      <c r="M53" s="34"/>
+      <c r="N53" s="34" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="29">
-        <v>54</v>
-      </c>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29">
-        <v>1.4</v>
-      </c>
-      <c r="D53" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="E53" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="F53" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="G53" s="51"/>
-      <c r="H53" s="51"/>
-      <c r="I53" s="51"/>
-      <c r="J53" s="51"/>
-      <c r="K53" s="29" t="s">
+    <row r="54" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="34">
+        <v>59</v>
+      </c>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34">
+        <v>1.5</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" s="34" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="G54" s="45"/>
+      <c r="H54" s="45"/>
+      <c r="I54" s="45"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="45"/>
+      <c r="L54" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="L53" s="29"/>
-      <c r="M53" s="29" t="s">
+      <c r="M54" s="34"/>
+      <c r="N54" s="34" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="29">
-        <v>55</v>
-      </c>
-      <c r="B54" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="29">
-        <v>1.4</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="E54" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="F54" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="G54" s="52"/>
-      <c r="H54" s="52"/>
-      <c r="I54" s="52"/>
-      <c r="J54" s="52"/>
-      <c r="K54" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A55" s="34">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B55" s="34"/>
       <c r="C55" s="34">
         <v>1.5</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E55" s="34" t="s">
         <v>49</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="G55" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="H55" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="G55" s="46"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="46"/>
+      <c r="J55" s="46"/>
+      <c r="K55" s="45"/>
+      <c r="L55" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="M55" s="34"/>
+      <c r="N55" s="34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A56" s="32">
+        <v>61</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E56" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="G56" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="H56" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="I55" s="53" cm="1">
-        <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I56" s="32" cm="1">
+        <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J55" s="53">
+      <c r="J56" s="32">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K55" s="34" t="s">
+      <c r="K56" s="45"/>
+      <c r="L56" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="L55" s="34"/>
-      <c r="M55" s="34" t="s">
+      <c r="M56" s="32"/>
+      <c r="N56" s="32" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A56" s="34">
-        <v>57</v>
-      </c>
-      <c r="B56" s="34"/>
-      <c r="C56" s="34">
+    <row r="57" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="32">
+        <v>62</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="32">
         <v>1.5</v>
       </c>
-      <c r="D56" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E56" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F56" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="G56" s="54"/>
-      <c r="H56" s="54"/>
-      <c r="I56" s="54"/>
-      <c r="J56" s="54"/>
-      <c r="K56" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="L56" s="34"/>
-      <c r="M56" s="34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="34">
-        <v>58</v>
-      </c>
-      <c r="B57" s="34"/>
-      <c r="C57" s="34">
-        <v>1.5</v>
-      </c>
-      <c r="D57" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E57" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F57" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="G57" s="54"/>
-      <c r="H57" s="54"/>
-      <c r="I57" s="54"/>
-      <c r="J57" s="54"/>
-      <c r="K57" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="L57" s="34"/>
-      <c r="M57" s="34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A58" s="34">
-        <v>59</v>
-      </c>
-      <c r="B58" s="34"/>
-      <c r="C58" s="34">
-        <v>1.5</v>
-      </c>
-      <c r="D58" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E58" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="F58" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="G58" s="55"/>
-      <c r="H58" s="55"/>
-      <c r="I58" s="55"/>
-      <c r="J58" s="55"/>
-      <c r="K58" s="34" t="s">
-        <v>28</v>
-      </c>
-      <c r="L58" s="34"/>
-      <c r="M58" s="34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A59" s="32">
-        <v>60</v>
-      </c>
-      <c r="B59" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="32">
-        <v>1.5</v>
-      </c>
-      <c r="D59" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="E59" s="32" t="s">
+      <c r="D57" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F59" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="G59" s="32" t="s">
+      <c r="F57" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="G57" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="H59" s="32" t="s">
+      <c r="H57" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="I59" s="32" cm="1">
-        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I57" s="32" cm="1">
+        <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J59" s="32">
+      <c r="J57" s="32">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K59" s="32" t="s">
+      <c r="K57" s="45"/>
+      <c r="L57" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="L59" s="32"/>
-      <c r="M59" s="32" t="s">
+      <c r="M57" s="32"/>
+      <c r="N57" s="32" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="32">
-        <v>61</v>
-      </c>
-      <c r="B60" s="32" t="s">
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="32">
+        <v>63</v>
+      </c>
+      <c r="B58" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C58" s="32">
         <v>1.5</v>
       </c>
-      <c r="D60" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="E60" s="32" t="s">
+      <c r="D58" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E58" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="F60" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="G60" s="32" t="s">
+      <c r="F58" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="G58" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="H60" s="32" t="s">
+      <c r="H58" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="I58" s="32" cm="1">
+        <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J58" s="32">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K58" s="46"/>
+      <c r="L58" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="M58" s="32"/>
+      <c r="N58" s="32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" s="18" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A59" s="36">
+        <v>64</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="36">
+        <v>1.6</v>
+      </c>
+      <c r="D59" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E59" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="G59" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="H59" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="I59" s="36" cm="1">
+        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J59" s="36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K59" s="66">
+        <v>27</v>
+      </c>
+      <c r="L59" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="M59" s="36"/>
+      <c r="N59" s="36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="36">
+        <v>65</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="36">
+        <v>1.6</v>
+      </c>
+      <c r="D60" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="F60" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="G60" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="H60" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="I60" s="36" cm="1">
+        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J60" s="36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K60" s="67"/>
+      <c r="L60" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="M60" s="36"/>
+      <c r="N60" s="36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A61" s="36">
+        <v>66</v>
+      </c>
+      <c r="B61" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="36">
+        <v>1.6</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="G61" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="H61" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="I61" s="36" cm="1">
+        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J61" s="36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K61" s="67"/>
+      <c r="L61" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="M61" s="36"/>
+      <c r="N61" s="36" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="39">
+        <v>68</v>
+      </c>
+      <c r="B62" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="39">
+        <v>1.6</v>
+      </c>
+      <c r="D62" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E62" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="F62" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="G62" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="I60" s="32" cm="1">
-        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I62" s="39" cm="1">
+        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J60" s="32">
+      <c r="J62" s="39">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K60" s="32" t="s">
+      <c r="K62" s="67"/>
+      <c r="L62" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L60" s="32"/>
-      <c r="M60" s="32" t="s">
+      <c r="M62" s="39"/>
+      <c r="N62" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A61" s="32">
-        <v>62</v>
-      </c>
-      <c r="B61" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="32">
-        <v>1.5</v>
-      </c>
-      <c r="D61" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="E61" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="F61" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="G61" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="H61" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="I61" s="32" cm="1">
-        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J61" s="32">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K61" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="L61" s="32"/>
-      <c r="M61" s="32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" s="18" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="39">
-        <v>63</v>
-      </c>
-      <c r="B62" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="39">
-        <v>1.6</v>
-      </c>
-      <c r="D62" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="E62" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="F62" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="G62" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="H62" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I62" s="39" cm="1">
-        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J62" s="39">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K62" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="L62" s="39"/>
-      <c r="M62" s="39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" s="18" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" s="39">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B63" s="39" t="s">
         <v>7</v>
@@ -6219,36 +7204,37 @@
         <v>65</v>
       </c>
       <c r="E63" s="39" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F63" s="40" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G63" s="39" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H63" s="39" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="I63" s="39" cm="1">
         <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J63" s="39">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K63" s="39" t="s">
+        <v>3</v>
+      </c>
+      <c r="K63" s="67"/>
+      <c r="L63" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L63" s="39"/>
-      <c r="M63" s="39" t="s">
+      <c r="M63" s="39"/>
+      <c r="N63" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:13" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="39">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B64" s="39" t="s">
         <v>7</v>
@@ -6260,13 +7246,13 @@
         <v>65</v>
       </c>
       <c r="E64" s="39" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F64" s="40" t="s">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="G64" s="39" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H64" s="39" t="s">
         <v>44</v>
@@ -6279,630 +7265,600 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K64" s="39" t="s">
+      <c r="K64" s="67"/>
+      <c r="L64" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L64" s="39"/>
-      <c r="M64" s="39" t="s">
+      <c r="M64" s="39"/>
+      <c r="N64" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:13" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A65" s="39">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B65" s="39" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="39">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="D65" s="39" t="s">
         <v>65</v>
       </c>
       <c r="E65" s="39" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F65" s="40" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="G65" s="39" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H65" s="39" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="I65" s="39" cm="1">
         <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" s="39">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K65" s="39" t="s">
+        <f t="shared" ref="J65:J81" si="1">I65</f>
+        <v>2</v>
+      </c>
+      <c r="K65" s="67"/>
+      <c r="L65" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L65" s="39"/>
-      <c r="M65" s="39" t="s">
+      <c r="M65" s="39"/>
+      <c r="N65" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="42">
-        <v>67</v>
-      </c>
-      <c r="B66" s="42" t="s">
+    <row r="66" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="39">
+        <v>76</v>
+      </c>
+      <c r="B66" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="42">
+      <c r="C66" s="39">
         <v>1.6</v>
       </c>
-      <c r="D66" s="42" t="s">
+      <c r="D66" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="E66" s="42" t="s">
+      <c r="E66" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="F66" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="G66" s="42" t="s">
+      <c r="F66" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="G66" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H66" s="42" t="s">
+      <c r="H66" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="I66" s="39" cm="1">
+        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J66" s="39">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="K66" s="67"/>
+      <c r="L66" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="M66" s="39"/>
+      <c r="N66" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="39">
+        <v>77</v>
+      </c>
+      <c r="B67" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="39">
+        <v>1.6</v>
+      </c>
+      <c r="D67" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E67" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="F67" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="G67" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H67" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="I66" s="42" cm="1">
-        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J66" s="42">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="K66" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L66" s="42"/>
-      <c r="M66" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="42">
-        <v>68</v>
-      </c>
-      <c r="B67" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D67" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E67" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F67" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="G67" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="H67" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="I67" s="42" cm="1">
+      <c r="I67" s="39" cm="1">
         <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J67" s="42">
-        <f t="shared" si="0"/>
+      <c r="J67" s="39">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K67" s="42" t="s">
+      <c r="K67" s="67"/>
+      <c r="L67" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L67" s="42"/>
-      <c r="M67" s="42" t="s">
+      <c r="M67" s="39"/>
+      <c r="N67" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A68" s="42">
-        <v>69</v>
-      </c>
-      <c r="B68" s="42" t="s">
+    <row r="68" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="39">
+        <v>78</v>
+      </c>
+      <c r="B68" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="42">
+      <c r="C68" s="39">
         <v>1.6</v>
       </c>
-      <c r="D68" s="42" t="s">
+      <c r="D68" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="E68" s="42" t="s">
+      <c r="E68" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="F68" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="G68" s="42" t="s">
+      <c r="F68" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="G68" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H68" s="42" t="s">
+      <c r="H68" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="I68" s="42" cm="1">
+      <c r="I68" s="39" cm="1">
         <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J68" s="42">
-        <f t="shared" si="0"/>
+      <c r="J68" s="39">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K68" s="42" t="s">
+      <c r="K68" s="67"/>
+      <c r="L68" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L68" s="42"/>
-      <c r="M68" s="42" t="s">
+      <c r="M68" s="39"/>
+      <c r="N68" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="42">
-        <v>70</v>
-      </c>
-      <c r="B69" s="42" t="s">
+    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="39">
+        <v>79</v>
+      </c>
+      <c r="B69" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C69" s="42">
+      <c r="C69" s="39">
         <v>1.6</v>
       </c>
-      <c r="D69" s="42" t="s">
+      <c r="D69" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="E69" s="42" t="s">
+      <c r="E69" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="F69" s="43" t="s">
+      <c r="F69" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="G69" s="42" t="s">
+      <c r="G69" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H69" s="42" t="s">
+      <c r="H69" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I69" s="39" cm="1">
+        <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J69" s="39">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K69" s="67"/>
+      <c r="L69" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="M69" s="39"/>
+      <c r="N69" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="39">
+        <v>80</v>
+      </c>
+      <c r="B70" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="39">
+        <v>1.6</v>
+      </c>
+      <c r="D70" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E70" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="F70" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="G70" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H70" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="I70" s="39" cm="1">
+        <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J70" s="39">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="K70" s="67"/>
+      <c r="L70" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="M70" s="39"/>
+      <c r="N70" s="39" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="39">
+        <v>81</v>
+      </c>
+      <c r="B71" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="39">
+        <v>1.6</v>
+      </c>
+      <c r="D71" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E71" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="F71" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="G71" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="H71" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="I69" s="42" cm="1">
-        <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I71" s="39" cm="1">
+        <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J69" s="42">
-        <f t="shared" ref="J69:J88" si="1">I69</f>
+      <c r="J71" s="39">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K69" s="42" t="s">
+      <c r="K71" s="68"/>
+      <c r="L71" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="L69" s="42"/>
-      <c r="M69" s="42" t="s">
+      <c r="M71" s="39"/>
+      <c r="N71" s="39" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A70" s="42">
-        <v>71</v>
-      </c>
-      <c r="B70" s="42" t="s">
+    <row r="72" spans="1:14" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="36">
+        <v>67</v>
+      </c>
+      <c r="B72" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D70" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E70" s="42" t="s">
+      <c r="C72" s="64">
+        <v>1.7</v>
+      </c>
+      <c r="D72" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="E72" s="64" t="s">
+        <v>49</v>
+      </c>
+      <c r="F72" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="G72" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="H72" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="I72" s="64" cm="1">
+        <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J72" s="64">
+        <f>I72</f>
+        <v>1</v>
+      </c>
+      <c r="K72" s="69">
+        <v>27</v>
+      </c>
+      <c r="L72" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="M72" s="64"/>
+      <c r="N72" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="39">
+        <v>72</v>
+      </c>
+      <c r="B73" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="62">
+        <v>1.7</v>
+      </c>
+      <c r="D73" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="E73" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F70" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="G70" s="42" t="s">
+      <c r="F73" s="63" t="s">
+        <v>120</v>
+      </c>
+      <c r="G73" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="H70" s="42" t="s">
+      <c r="H73" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="I70" s="42" cm="1">
-        <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I73" s="62" cm="1">
+        <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="J70" s="42">
-        <f t="shared" si="1"/>
+      <c r="J73" s="62">
+        <f>I73</f>
         <v>8</v>
       </c>
-      <c r="K70" s="42" t="s">
+      <c r="K73" s="70"/>
+      <c r="L73" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="L70" s="42"/>
-      <c r="M70" s="42" t="s">
+      <c r="M73" s="62"/>
+      <c r="N73" s="62" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="42">
-        <v>72</v>
-      </c>
-      <c r="B71" s="42" t="s">
+    <row r="74" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="39">
+        <v>73</v>
+      </c>
+      <c r="B74" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C71" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D71" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E71" s="42" t="s">
+      <c r="C74" s="62">
+        <v>1.7</v>
+      </c>
+      <c r="D74" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="E74" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="F71" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="G71" s="42" t="s">
+      <c r="F74" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="G74" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="H71" s="42" t="s">
+      <c r="H74" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="I71" s="42" cm="1">
-        <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J71" s="42">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K71" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L71" s="42"/>
-      <c r="M71" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A72" s="42">
-        <v>73</v>
-      </c>
-      <c r="B72" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D72" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E72" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F72" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="G72" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="H72" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="I72" s="42" cm="1">
-        <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>8</v>
-      </c>
-      <c r="J72" s="42">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="K72" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L72" s="42"/>
-      <c r="M72" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="42">
-        <v>74</v>
-      </c>
-      <c r="B73" s="42"/>
-      <c r="C73" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D73" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E73" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F73" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="G73" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="H73" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="I73" s="42" cm="1">
-        <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J73" s="42">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K73" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L73" s="42"/>
-      <c r="M73" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="42">
-        <v>75</v>
-      </c>
-      <c r="B74" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D74" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E74" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F74" s="43" t="s">
-        <v>66</v>
-      </c>
-      <c r="G74" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="H74" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="I74" s="42" cm="1">
+      <c r="I74" s="62" cm="1">
         <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J74" s="42">
+      <c r="J74" s="62">
+        <f>I74</f>
+        <v>5</v>
+      </c>
+      <c r="K74" s="70"/>
+      <c r="L74" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="M74" s="62"/>
+      <c r="N74" s="62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A75" s="39">
+        <v>74</v>
+      </c>
+      <c r="B75" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="62">
+        <v>1.7</v>
+      </c>
+      <c r="D75" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="E75" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="F75" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="G75" s="62" t="s">
+        <v>38</v>
+      </c>
+      <c r="H75" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="I75" s="62" cm="1">
+        <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>8</v>
+      </c>
+      <c r="J75" s="62">
+        <f>I75</f>
+        <v>8</v>
+      </c>
+      <c r="K75" s="70"/>
+      <c r="L75" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="M75" s="62"/>
+      <c r="N75" s="62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A76" s="39">
+        <v>75</v>
+      </c>
+      <c r="B76" s="39"/>
+      <c r="C76" s="62">
+        <v>1.7</v>
+      </c>
+      <c r="D76" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="E76" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="F76" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="G76" s="62" t="s">
+        <v>38</v>
+      </c>
+      <c r="H76" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="I76" s="62" cm="1">
+        <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J76" s="62">
+        <f>I76</f>
+        <v>5</v>
+      </c>
+      <c r="K76" s="71"/>
+      <c r="L76" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="M76" s="62"/>
+      <c r="N76" s="62" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>82</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2" t="str" cm="1">
+        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="38" t="str">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="K74" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L74" s="42"/>
-      <c r="M74" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="42">
-        <v>76</v>
-      </c>
-      <c r="B75" s="42" t="s">
+        <v/>
+      </c>
+      <c r="K77" s="38"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>83</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D75" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E75" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F75" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="G75" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="H75" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="I75" s="42" cm="1">
-        <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J75" s="42">
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2" t="str" cm="1">
+        <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J78" s="38" t="str">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K75" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L75" s="42"/>
-      <c r="M75" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A76" s="42">
-        <v>77</v>
-      </c>
-      <c r="B76" s="42" t="s">
+        <v/>
+      </c>
+      <c r="K78" s="38"/>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>84</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C76" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D76" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E76" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F76" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="G76" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="H76" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="I76" s="42" cm="1">
-        <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J76" s="42">
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2" t="str" cm="1">
+        <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J79" s="38" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K76" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L76" s="42"/>
-      <c r="M76" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="42">
-        <v>78</v>
-      </c>
-      <c r="B77" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D77" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E77" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F77" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="G77" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="H77" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="I77" s="42" cm="1">
-        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J77" s="42">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K77" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L77" s="42"/>
-      <c r="M77" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="42">
-        <v>79</v>
-      </c>
-      <c r="B78" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D78" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E78" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F78" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="G78" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="H78" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="I78" s="42" cm="1">
-        <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J78" s="42">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="K78" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L78" s="42"/>
-      <c r="M78" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A79" s="42">
-        <v>80</v>
-      </c>
-      <c r="B79" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="42">
-        <v>1.6</v>
-      </c>
-      <c r="D79" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E79" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="F79" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="G79" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="H79" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="I79" s="42" cm="1">
-        <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J79" s="42">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="K79" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L79" s="42"/>
-      <c r="M79" s="42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+        <v/>
+      </c>
+      <c r="K79" s="38"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>7</v>
@@ -6917,17 +7873,18 @@
         <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J80" s="41" t="str">
+      <c r="J80" s="38" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K80" s="2"/>
+      <c r="K80" s="38"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>7</v>
@@ -6942,207 +7899,40 @@
         <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J81" s="41" t="str">
+      <c r="J81" s="38" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K81" s="2"/>
+      <c r="K81" s="38"/>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
-        <v>80</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2" t="str" cm="1">
-        <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J82" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
-        <v>81</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2" t="str" cm="1">
-        <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J83" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K83" s="2"/>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
-        <v>82</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2" t="str" cm="1">
-        <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J84" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
-        <v>83</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2" t="str" cm="1">
-        <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J85" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K85" s="2"/>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
-        <v>84</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2" t="str" cm="1">
-        <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J86" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K86" s="2"/>
-      <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
-        <v>85</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2" t="str" cm="1">
-        <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J87" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
-        <v>86</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2" t="str" cm="1">
-        <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J88" s="41" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
+      <c r="N81" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="J51:J54"/>
-    <mergeCell ref="G55:G58"/>
-    <mergeCell ref="H55:H58"/>
-    <mergeCell ref="I55:I58"/>
-    <mergeCell ref="J55:J58"/>
-    <mergeCell ref="G51:G54"/>
-    <mergeCell ref="H51:H54"/>
-    <mergeCell ref="I51:I54"/>
-    <mergeCell ref="H47:H50"/>
-    <mergeCell ref="I47:I50"/>
-    <mergeCell ref="G47:G50"/>
-    <mergeCell ref="J47:J50"/>
-    <mergeCell ref="G38:G46"/>
-    <mergeCell ref="H38:H46"/>
-    <mergeCell ref="I38:I46"/>
-    <mergeCell ref="J38:J46"/>
+  <mergeCells count="23">
+    <mergeCell ref="K59:K71"/>
+    <mergeCell ref="K72:K76"/>
+    <mergeCell ref="K12:K19"/>
+    <mergeCell ref="K20:K30"/>
+    <mergeCell ref="K31:K43"/>
+    <mergeCell ref="K44:K51"/>
+    <mergeCell ref="K52:K58"/>
+    <mergeCell ref="H44:H47"/>
+    <mergeCell ref="I44:I47"/>
+    <mergeCell ref="G44:G47"/>
+    <mergeCell ref="J44:J47"/>
+    <mergeCell ref="G36:G43"/>
+    <mergeCell ref="H36:H43"/>
+    <mergeCell ref="I36:I43"/>
+    <mergeCell ref="J36:J43"/>
+    <mergeCell ref="J48:J51"/>
+    <mergeCell ref="G52:G55"/>
+    <mergeCell ref="H52:H55"/>
+    <mergeCell ref="I52:I55"/>
+    <mergeCell ref="J52:J55"/>
+    <mergeCell ref="G48:G51"/>
+    <mergeCell ref="H48:H51"/>
+    <mergeCell ref="I48:I51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7150,6 +7940,197 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D389B43-8ACA-4B5D-A185-0146C384427F}">
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" style="74" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
+      <c r="B2" s="73">
+        <v>156</v>
+      </c>
+      <c r="C2" s="1">
+        <v>156</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="74">
+        <f>156-SUM(D$3:D3)</f>
+        <v>156</v>
+      </c>
+      <c r="C3" s="3">
+        <f>156-A3*15.6</f>
+        <v>140.4</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="74">
+        <f>156-SUM(D$3:D4)</f>
+        <v>156</v>
+      </c>
+      <c r="C4" s="3">
+        <f t="shared" ref="C4:C12" si="0">156-A4*15.6</f>
+        <v>124.8</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="K4" s="72"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="74">
+        <f>156-SUM(D$3:D5)</f>
+        <v>156</v>
+      </c>
+      <c r="C5" s="3">
+        <f t="shared" si="0"/>
+        <v>109.2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="74">
+        <f>156-SUM(D$3:D6)</f>
+        <v>156</v>
+      </c>
+      <c r="C6" s="3">
+        <f t="shared" si="0"/>
+        <v>93.6</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="74">
+        <f>156-SUM(D$3:D7)</f>
+        <v>148</v>
+      </c>
+      <c r="C7" s="3">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="D7" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="74">
+        <f>156-SUM(D$3:D8)</f>
+        <v>148</v>
+      </c>
+      <c r="C8" s="3">
+        <f t="shared" si="0"/>
+        <v>62.400000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="74">
+        <f>156-SUM(D$3:D9)</f>
+        <v>148</v>
+      </c>
+      <c r="C9" s="3">
+        <f t="shared" si="0"/>
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="74">
+        <f>156-SUM(D$3:D10)</f>
+        <v>148</v>
+      </c>
+      <c r="C10" s="3">
+        <f t="shared" si="0"/>
+        <v>31.200000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="74">
+        <f>156-SUM(D$3:D11)</f>
+        <v>148</v>
+      </c>
+      <c r="C11" s="3">
+        <f t="shared" si="0"/>
+        <v>15.599999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>10</v>
+      </c>
+      <c r="B12" s="74">
+        <f>156-SUM(D$3:D12)</f>
+        <v>148</v>
+      </c>
+      <c r="C12" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7189,7 +8170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
+++ b/BusinessAnalysis/01SprintPlanJanuary2026.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A3B0E1-C312-49D8-83B4-6FC31937EBB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D25F64-9906-4B73-ACC0-5F7BC6227F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint Board" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
+    <sheet name="Burndown" sheetId="4" r:id="rId2"/>
     <sheet name="Daily Standup Guide" sheetId="2" r:id="rId3"/>
-    <sheet name="Burndown" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="123">
   <si>
     <t>Epic</t>
   </si>
@@ -107,39 +106,6 @@
   </si>
   <si>
     <t>Any help needed today?</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Day 1</t>
-  </si>
-  <si>
-    <t>Day 2</t>
-  </si>
-  <si>
-    <t>Day 3</t>
-  </si>
-  <si>
-    <t>Day 4</t>
-  </si>
-  <si>
-    <t>Day 5</t>
-  </si>
-  <si>
-    <t>Day 6</t>
-  </si>
-  <si>
-    <t>Day 7</t>
-  </si>
-  <si>
-    <t>Day 8</t>
-  </si>
-  <si>
-    <t>Day 9</t>
-  </si>
-  <si>
-    <t>Day 10</t>
   </si>
   <si>
     <t>ToDo</t>
@@ -184,9 +150,6 @@
   </si>
   <si>
     <t>L</t>
-  </si>
-  <si>
-    <t>Remaining Story Points</t>
   </si>
   <si>
     <t>Create reusable color palate</t>
@@ -2998,6 +2961,12 @@
   </si>
   <si>
     <t>Story Points Done</t>
+  </si>
+  <si>
+    <t>WIP</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -3378,40 +3347,43 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3441,44 +3413,41 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3552,7 +3521,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>Burndown!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3575,7 +3544,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$12</c:f>
+              <c:f>Burndown!$B$2:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -3598,19 +3567,19 @@
                   <c:v>148</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>148</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>148</c:v>
+                  <c:v>116</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>148</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>148</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>148</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3627,7 +3596,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
+              <c:f>Burndown!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3650,7 +3619,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$12</c:f>
+              <c:f>Burndown!$C$2:$C$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
@@ -4802,7 +4771,7 @@
   <sheetData>
     <row r="1" spans="1:14" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>0</v>
@@ -4814,7 +4783,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>3</v>
@@ -4823,10 +4792,10 @@
         <v>4</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J1" s="5">
         <f>SUM(J2:J76)</f>
@@ -4843,7 +4812,7 @@
         <v>6</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -4854,16 +4823,16 @@
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
       <c r="E2" s="19" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I2" s="19" cm="1">
         <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4878,11 +4847,11 @@
         <v>8</v>
       </c>
       <c r="L2" s="19" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="M2" s="19"/>
       <c r="N2" s="19" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -4893,16 +4862,16 @@
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I3" s="19" cm="1">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4917,11 +4886,11 @@
         <v>5</v>
       </c>
       <c r="L3" s="19" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M3" s="19"/>
       <c r="N3" s="19" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -4932,16 +4901,16 @@
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
       <c r="E4" s="19" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G4" s="19" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I4" s="19" cm="1">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4956,11 +4925,11 @@
         <v>3</v>
       </c>
       <c r="L4" s="19" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M4" s="19"/>
       <c r="N4" s="19" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -4971,16 +4940,16 @@
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I5" s="11" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -4995,11 +4964,11 @@
         <v>5</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M5" s="11"/>
       <c r="N5" s="11" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -5010,16 +4979,16 @@
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I6" s="11" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5034,11 +5003,11 @@
         <v>3</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -5049,16 +5018,16 @@
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I7" s="11" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5073,11 +5042,11 @@
         <v>3</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="11" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -5088,16 +5057,16 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I8" s="11" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5112,11 +5081,11 @@
         <v>3</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M8" s="11"/>
       <c r="N8" s="11" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -5127,16 +5096,16 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I9" s="11" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5151,13 +5120,13 @@
         <v>5</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M9" s="11">
         <v>32</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="374.4" x14ac:dyDescent="0.3">
@@ -5168,16 +5137,16 @@
       <c r="C10" s="21"/>
       <c r="D10" s="21"/>
       <c r="E10" s="21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I10" s="21" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5192,11 +5161,11 @@
         <v>5</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M10" s="21"/>
       <c r="N10" s="21" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -5207,16 +5176,16 @@
       <c r="C11" s="21"/>
       <c r="D11" s="21"/>
       <c r="E11" s="21" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I11" s="21" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5231,11 +5200,11 @@
         <v>5</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M11" s="21"/>
       <c r="N11" s="21" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -5252,16 +5221,16 @@
         <v>8</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I12" s="6" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5271,11 +5240,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K12" s="53">
+      <c r="K12" s="54">
         <v>9</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M12" s="6"/>
       <c r="N12" s="6" t="s">
@@ -5296,16 +5265,16 @@
         <v>8</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I13" s="6" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5315,9 +5284,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K13" s="54"/>
+      <c r="K13" s="55"/>
       <c r="L13" s="6" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6" t="s">
@@ -5338,16 +5307,16 @@
         <v>8</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I14" s="6" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5357,9 +5326,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K14" s="54"/>
+      <c r="K14" s="55"/>
       <c r="L14" s="6" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6" t="s">
@@ -5380,16 +5349,16 @@
         <v>8</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I15" s="6" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5399,9 +5368,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K15" s="54"/>
+      <c r="K15" s="55"/>
       <c r="L15" s="6" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M15" s="6"/>
       <c r="N15" s="6" t="s">
@@ -5422,16 +5391,16 @@
         <v>8</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I16" s="6" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5441,12 +5410,14 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K16" s="54"/>
+      <c r="K16" s="55"/>
       <c r="L16" s="6" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="6" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
@@ -5462,16 +5433,16 @@
         <v>8</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I17" s="6" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5481,161 +5452,163 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K17" s="54"/>
+      <c r="K17" s="55"/>
       <c r="L17" s="6" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="N17" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="9">
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>10</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="I18" s="9" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J18" s="9">
+        <f>I18</f>
+        <v>3</v>
+      </c>
+      <c r="K18" s="55"/>
+      <c r="L18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="9" cm="1">
+        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J19" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K18" s="54"/>
-      <c r="L18" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="9">
+      <c r="K19" s="55"/>
+      <c r="L19" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
         <v>19</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C20" s="9">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D20" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G19" s="9" t="s">
+      <c r="E20" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="9" cm="1">
-        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="H20" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="9" cm="1">
+        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J20" s="9">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K19" s="55"/>
-      <c r="L19" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13">
-        <v>20</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13">
-        <v>1.2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="13" cm="1">
-        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J20" s="13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K20" s="56">
-        <v>18</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13" t="s">
-        <v>9</v>
+      <c r="K20" s="56"/>
+      <c r="L20" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13">
         <v>1.2</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I21" s="13" cm="1">
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5645,9 +5618,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K21" s="57"/>
+      <c r="K21" s="57">
+        <v>18</v>
+      </c>
       <c r="L21" s="13" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M21" s="13"/>
       <c r="N21" s="13" t="s">
@@ -5656,26 +5631,26 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="13"/>
       <c r="C22" s="13">
         <v>1.2</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I22" s="13" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5685,9 +5660,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K22" s="57"/>
+      <c r="K22" s="58"/>
       <c r="L22" s="13" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M22" s="13"/>
       <c r="N22" s="13" t="s">
@@ -5696,26 +5671,26 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13">
         <v>1.2</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I23" s="13" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5725,37 +5700,37 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K23" s="57"/>
+      <c r="K23" s="58"/>
       <c r="L23" s="13" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M23" s="13"/>
       <c r="N23" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13">
         <v>1.2</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>102</v>
+        <v>37</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I24" s="13" cm="1">
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5765,49 +5740,49 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K24" s="57"/>
+      <c r="K24" s="58"/>
       <c r="L24" s="13" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M24" s="13"/>
       <c r="N24" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="13">
         <v>1.2</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I25" s="13" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="K25" s="57"/>
+        <v>1</v>
+      </c>
+      <c r="K25" s="58"/>
       <c r="L25" s="13" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M25" s="13"/>
       <c r="N25" s="13" t="s">
@@ -5816,26 +5791,26 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13">
         <v>1.2</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I26" s="13" cm="1">
         <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5845,9 +5820,9 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K26" s="57"/>
+      <c r="K26" s="58"/>
       <c r="L26" s="13" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M26" s="13"/>
       <c r="N26" s="13" t="s">
@@ -5856,26 +5831,26 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="13">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13">
         <v>1.2</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I27" s="13" cm="1">
         <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5885,60 +5860,58 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K27" s="57"/>
+      <c r="K27" s="58"/>
       <c r="L27" s="13" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:14" s="18" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
-        <v>30</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="13">
+        <v>29</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13">
         <v>1.2</v>
       </c>
-      <c r="D28" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="14" cm="1">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="13" cm="1">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J28" s="14">
+      <c r="J28" s="13">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K28" s="57"/>
-      <c r="L28" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14" t="s">
+      <c r="K28" s="58"/>
+      <c r="L28" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" s="18" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>7</v>
@@ -5947,19 +5920,19 @@
         <v>1.2</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I29" s="14" cm="1">
         <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -5969,18 +5942,18 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K29" s="57"/>
+      <c r="K29" s="58"/>
       <c r="L29" s="14" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M29" s="14"/>
       <c r="N29" s="14" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>7</v>
@@ -5989,79 +5962,77 @@
         <v>1.2</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>10</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I30" s="14" cm="1">
         <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K30" s="58"/>
       <c r="L30" s="14" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M30" s="14"/>
       <c r="N30" s="14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="23">
-        <v>33</v>
-      </c>
-      <c r="B31" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="14">
+        <v>32</v>
+      </c>
+      <c r="B31" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="23">
-        <v>1.3</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F31" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="G31" s="23" t="s">
+      <c r="C31" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="I31" s="23" cm="1">
+      <c r="H31" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" s="14" cm="1">
         <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J31" s="23">
+      <c r="J31" s="14">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K31" s="59">
-        <v>14</v>
-      </c>
-      <c r="L31" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23" t="s">
-        <v>9</v>
+      <c r="K31" s="59"/>
+      <c r="L31" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -6075,19 +6046,19 @@
         <v>1.3</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F32" s="24" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I32" s="23" cm="1">
         <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6097,9 +6068,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K32" s="60"/>
+      <c r="K32" s="60">
+        <v>14</v>
+      </c>
       <c r="L32" s="23" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M32" s="23"/>
       <c r="N32" s="23" t="s">
@@ -6117,19 +6090,19 @@
         <v>1.3</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I33" s="23" cm="1">
         <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6139,9 +6112,9 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K33" s="60"/>
+      <c r="K33" s="61"/>
       <c r="L33" s="23" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M33" s="23"/>
       <c r="N33" s="23" t="s">
@@ -6159,19 +6132,19 @@
         <v>1.3</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F34" s="24" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I34" s="23" cm="1">
         <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6181,9 +6154,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K34" s="60"/>
+      <c r="K34" s="61"/>
       <c r="L34" s="23" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M34" s="23"/>
       <c r="N34" s="23" t="s">
@@ -6201,19 +6174,19 @@
         <v>1.3</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F35" s="24" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G35" s="23" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I35" s="23" cm="1">
         <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6223,9 +6196,9 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K35" s="60"/>
+      <c r="K35" s="61"/>
       <c r="L35" s="23" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M35" s="23"/>
       <c r="N35" s="23" t="s">
@@ -6243,35 +6216,35 @@
         <v>1.3</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="G36" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="G36" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="H36" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="I36" s="50" cm="1">
+      <c r="H36" s="69" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="69" cm="1">
         <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J36" s="50">
+      <c r="J36" s="69">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K36" s="60"/>
+      <c r="K36" s="61"/>
       <c r="L36" s="25" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M36" s="25"/>
       <c r="N36" s="25" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -6285,25 +6258,25 @@
         <v>1.3</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="60"/>
+        <v>60</v>
+      </c>
+      <c r="G37" s="70"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="61"/>
       <c r="L37" s="25" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M37" s="25"/>
       <c r="N37" s="25" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -6317,25 +6290,25 @@
         <v>1.3</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="G38" s="51"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="51"/>
-      <c r="J38" s="51"/>
-      <c r="K38" s="60"/>
+        <v>63</v>
+      </c>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="61"/>
       <c r="L38" s="25" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M38" s="25"/>
       <c r="N38" s="25" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -6349,25 +6322,25 @@
         <v>1.3</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="60"/>
+        <v>61</v>
+      </c>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="61"/>
       <c r="L39" s="25" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M39" s="25"/>
       <c r="N39" s="25" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -6381,25 +6354,25 @@
         <v>1.3</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="51"/>
-      <c r="K40" s="60"/>
+        <v>62</v>
+      </c>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="61"/>
       <c r="L40" s="25" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M40" s="25"/>
       <c r="N40" s="25" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -6413,25 +6386,25 @@
         <v>1.3</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E41" s="25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="60"/>
+        <v>66</v>
+      </c>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="61"/>
       <c r="L41" s="25" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M41" s="25"/>
       <c r="N41" s="25" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -6445,25 +6418,25 @@
         <v>1.3</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E42" s="25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G42" s="51"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="60"/>
+        <v>64</v>
+      </c>
+      <c r="G42" s="70"/>
+      <c r="H42" s="70"/>
+      <c r="I42" s="70"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="61"/>
       <c r="L42" s="25" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M42" s="25"/>
       <c r="N42" s="25" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -6477,25 +6450,25 @@
         <v>1.3</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E43" s="25" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="G43" s="52"/>
-      <c r="H43" s="52"/>
-      <c r="I43" s="52"/>
-      <c r="J43" s="52"/>
-      <c r="K43" s="61"/>
+        <v>67</v>
+      </c>
+      <c r="G43" s="71"/>
+      <c r="H43" s="71"/>
+      <c r="I43" s="71"/>
+      <c r="J43" s="71"/>
+      <c r="K43" s="62"/>
       <c r="L43" s="25" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M43" s="25"/>
       <c r="N43" s="25" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -6507,33 +6480,33 @@
         <v>1.4</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E44" s="27" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="G44" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="H44" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="47" cm="1">
+        <v>86</v>
+      </c>
+      <c r="G44" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="H44" s="63" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="63" cm="1">
         <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J44" s="47">
+      <c r="J44" s="63">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K44" s="47">
+      <c r="K44" s="63">
         <v>5</v>
       </c>
       <c r="L44" s="27" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M44" s="27"/>
       <c r="N44" s="27" t="s">
@@ -6549,21 +6522,21 @@
         <v>1.4</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E45" s="27" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
+        <v>87</v>
+      </c>
+      <c r="G45" s="64"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="64"/>
+      <c r="J45" s="64"/>
+      <c r="K45" s="64"/>
       <c r="L45" s="27" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M45" s="27"/>
       <c r="N45" s="27" t="s">
@@ -6579,21 +6552,21 @@
         <v>1.4</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E46" s="27" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
+        <v>77</v>
+      </c>
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="64"/>
+      <c r="J46" s="64"/>
+      <c r="K46" s="64"/>
       <c r="L46" s="27" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M46" s="27"/>
       <c r="N46" s="27" t="s">
@@ -6609,21 +6582,21 @@
         <v>1.4</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E47" s="27" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F47" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="G47" s="49"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-      <c r="K47" s="48"/>
+        <v>78</v>
+      </c>
+      <c r="G47" s="65"/>
+      <c r="H47" s="65"/>
+      <c r="I47" s="65"/>
+      <c r="J47" s="65"/>
+      <c r="K47" s="64"/>
       <c r="L47" s="27" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M47" s="27"/>
       <c r="N47" s="27" t="s">
@@ -6639,35 +6612,35 @@
         <v>1.4</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="G48" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="G48" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="H48" s="41" t="s">
-        <v>36</v>
-      </c>
-      <c r="I48" s="41" cm="1">
+      <c r="H48" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="I48" s="72" cm="1">
         <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J48" s="41">
+      <c r="J48" s="72">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K48" s="48"/>
+      <c r="K48" s="64"/>
       <c r="L48" s="29" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M48" s="29"/>
       <c r="N48" s="29" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -6679,25 +6652,25 @@
         <v>1.4</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="G49" s="42"/>
-      <c r="H49" s="42"/>
-      <c r="I49" s="42"/>
-      <c r="J49" s="42"/>
-      <c r="K49" s="48"/>
+        <v>93</v>
+      </c>
+      <c r="G49" s="73"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73"/>
+      <c r="J49" s="73"/>
+      <c r="K49" s="64"/>
       <c r="L49" s="29" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M49" s="29"/>
       <c r="N49" s="29" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -6709,25 +6682,25 @@
         <v>1.4</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E50" s="29" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="G50" s="42"/>
-      <c r="H50" s="42"/>
-      <c r="I50" s="42"/>
-      <c r="J50" s="42"/>
-      <c r="K50" s="48"/>
+        <v>76</v>
+      </c>
+      <c r="G50" s="73"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73"/>
+      <c r="J50" s="73"/>
+      <c r="K50" s="64"/>
       <c r="L50" s="29" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M50" s="29"/>
       <c r="N50" s="29" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -6741,25 +6714,25 @@
         <v>1.4</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E51" s="29" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F51" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="G51" s="43"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="43"/>
-      <c r="J51" s="43"/>
-      <c r="K51" s="49"/>
+        <v>81</v>
+      </c>
+      <c r="G51" s="74"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="74"/>
+      <c r="J51" s="74"/>
+      <c r="K51" s="65"/>
       <c r="L51" s="29" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M51" s="29"/>
       <c r="N51" s="29" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -6771,33 +6744,33 @@
         <v>1.5</v>
       </c>
       <c r="D52" s="34" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F52" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="G52" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="H52" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="I52" s="44" cm="1">
+        <v>84</v>
+      </c>
+      <c r="G52" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="H52" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" s="66" cm="1">
         <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J52" s="44">
+      <c r="J52" s="66">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K52" s="44">
+      <c r="K52" s="66">
         <v>11</v>
       </c>
       <c r="L52" s="34" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M52" s="34"/>
       <c r="N52" s="34" t="s">
@@ -6813,21 +6786,21 @@
         <v>1.5</v>
       </c>
       <c r="D53" s="34" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F53" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="45"/>
+        <v>85</v>
+      </c>
+      <c r="G53" s="67"/>
+      <c r="H53" s="67"/>
+      <c r="I53" s="67"/>
+      <c r="J53" s="67"/>
+      <c r="K53" s="67"/>
       <c r="L53" s="34" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M53" s="34"/>
       <c r="N53" s="34" t="s">
@@ -6843,21 +6816,21 @@
         <v>1.5</v>
       </c>
       <c r="D54" s="34" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F54" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="45"/>
+        <v>94</v>
+      </c>
+      <c r="G54" s="67"/>
+      <c r="H54" s="67"/>
+      <c r="I54" s="67"/>
+      <c r="J54" s="67"/>
+      <c r="K54" s="67"/>
       <c r="L54" s="34" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M54" s="34"/>
       <c r="N54" s="34" t="s">
@@ -6873,21 +6846,21 @@
         <v>1.5</v>
       </c>
       <c r="D55" s="34" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="G55" s="46"/>
-      <c r="H55" s="46"/>
-      <c r="I55" s="46"/>
-      <c r="J55" s="46"/>
-      <c r="K55" s="45"/>
+        <v>95</v>
+      </c>
+      <c r="G55" s="68"/>
+      <c r="H55" s="68"/>
+      <c r="I55" s="68"/>
+      <c r="J55" s="68"/>
+      <c r="K55" s="67"/>
       <c r="L55" s="34" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M55" s="34"/>
       <c r="N55" s="34" t="s">
@@ -6905,19 +6878,19 @@
         <v>1.5</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E56" s="32" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G56" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H56" s="32" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I56" s="32" cm="1">
         <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6927,13 +6900,13 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K56" s="45"/>
+      <c r="K56" s="67"/>
       <c r="L56" s="32" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M56" s="32"/>
       <c r="N56" s="32" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -6947,19 +6920,19 @@
         <v>1.5</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E57" s="32" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F57" s="33" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G57" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H57" s="32" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I57" s="32" cm="1">
         <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -6969,13 +6942,13 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K57" s="45"/>
+      <c r="K57" s="67"/>
       <c r="L57" s="32" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M57" s="32"/>
       <c r="N57" s="32" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -6989,19 +6962,19 @@
         <v>1.5</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E58" s="32" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G58" s="32" t="s">
         <v>10</v>
       </c>
       <c r="H58" s="32" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I58" s="32" cm="1">
         <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7011,13 +6984,13 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K58" s="46"/>
+      <c r="K58" s="68"/>
       <c r="L58" s="32" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M58" s="32"/>
       <c r="N58" s="32" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:14" s="18" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
@@ -7031,19 +7004,19 @@
         <v>1.6</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F59" s="37" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="G59" s="36" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H59" s="36" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I59" s="36" cm="1">
         <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7053,11 +7026,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K59" s="66">
+      <c r="K59" s="48">
         <v>27</v>
       </c>
       <c r="L59" s="36" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M59" s="36"/>
       <c r="N59" s="36" t="s">
@@ -7075,19 +7048,19 @@
         <v>1.6</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F60" s="37" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G60" s="36" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H60" s="36" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I60" s="36" cm="1">
         <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7097,9 +7070,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K60" s="67"/>
+      <c r="K60" s="49"/>
       <c r="L60" s="36" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M60" s="36"/>
       <c r="N60" s="36" t="s">
@@ -7117,19 +7090,19 @@
         <v>1.6</v>
       </c>
       <c r="D61" s="36" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E61" s="36" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G61" s="36" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H61" s="36" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I61" s="36" cm="1">
         <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7139,9 +7112,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K61" s="67"/>
+      <c r="K61" s="49"/>
       <c r="L61" s="36" t="s">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="M61" s="36"/>
       <c r="N61" s="36" t="s">
@@ -7159,19 +7132,19 @@
         <v>1.6</v>
       </c>
       <c r="D62" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E62" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F62" s="40" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="G62" s="39" t="s">
         <v>10</v>
       </c>
       <c r="H62" s="39" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I62" s="39" cm="1">
         <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7181,13 +7154,13 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K62" s="67"/>
+      <c r="K62" s="49"/>
       <c r="L62" s="39" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M62" s="39"/>
       <c r="N62" s="39" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -7201,19 +7174,19 @@
         <v>1.6</v>
       </c>
       <c r="D63" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E63" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F63" s="40" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="G63" s="39" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H63" s="39" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I63" s="39" cm="1">
         <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7223,13 +7196,13 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K63" s="67"/>
+      <c r="K63" s="49"/>
       <c r="L63" s="39" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M63" s="39"/>
       <c r="N63" s="39" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
@@ -7243,19 +7216,19 @@
         <v>1.6</v>
       </c>
       <c r="D64" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E64" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F64" s="40" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G64" s="39" t="s">
         <v>10</v>
       </c>
       <c r="H64" s="39" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I64" s="39" cm="1">
         <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7265,9 +7238,9 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K64" s="67"/>
+      <c r="K64" s="49"/>
       <c r="L64" s="39" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="M64" s="39"/>
       <c r="N64" s="39" t="s">
@@ -7285,19 +7258,19 @@
         <v>1.6</v>
       </c>
       <c r="D65" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E65" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F65" s="40" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="G65" s="39" t="s">
         <v>10</v>
       </c>
       <c r="H65" s="39" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I65" s="39" cm="1">
         <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7307,13 +7280,13 @@
         <f t="shared" ref="J65:J81" si="1">I65</f>
         <v>2</v>
       </c>
-      <c r="K65" s="67"/>
+      <c r="K65" s="49"/>
       <c r="L65" s="39" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M65" s="39"/>
       <c r="N65" s="39" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -7327,19 +7300,19 @@
         <v>1.6</v>
       </c>
       <c r="D66" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E66" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F66" s="40" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G66" s="39" t="s">
         <v>10</v>
       </c>
       <c r="H66" s="39" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I66" s="39" cm="1">
         <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7349,13 +7322,13 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="K66" s="67"/>
+      <c r="K66" s="49"/>
       <c r="L66" s="39" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M66" s="39"/>
       <c r="N66" s="39" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -7369,19 +7342,19 @@
         <v>1.6</v>
       </c>
       <c r="D67" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E67" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F67" s="40" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="G67" s="39" t="s">
         <v>10</v>
       </c>
       <c r="H67" s="39" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I67" s="39" cm="1">
         <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7391,13 +7364,13 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K67" s="67"/>
+      <c r="K67" s="49"/>
       <c r="L67" s="39" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M67" s="39"/>
       <c r="N67" s="39" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -7411,19 +7384,19 @@
         <v>1.6</v>
       </c>
       <c r="D68" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E68" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F68" s="40" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="G68" s="39" t="s">
         <v>10</v>
       </c>
       <c r="H68" s="39" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I68" s="39" cm="1">
         <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7433,13 +7406,13 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K68" s="67"/>
+      <c r="K68" s="49"/>
       <c r="L68" s="39" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M68" s="39"/>
       <c r="N68" s="39" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -7453,19 +7426,19 @@
         <v>1.6</v>
       </c>
       <c r="D69" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E69" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F69" s="40" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="G69" s="39" t="s">
         <v>10</v>
       </c>
       <c r="H69" s="39" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I69" s="39" cm="1">
         <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7475,13 +7448,13 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K69" s="67"/>
+      <c r="K69" s="49"/>
       <c r="L69" s="39" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M69" s="39"/>
       <c r="N69" s="39" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -7495,19 +7468,19 @@
         <v>1.6</v>
       </c>
       <c r="D70" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E70" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F70" s="40" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="G70" s="39" t="s">
         <v>10</v>
       </c>
       <c r="H70" s="39" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I70" s="39" cm="1">
         <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7517,13 +7490,13 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="K70" s="67"/>
+      <c r="K70" s="49"/>
       <c r="L70" s="39" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M70" s="39"/>
       <c r="N70" s="39" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -7537,19 +7510,19 @@
         <v>1.6</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E71" s="39" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F71" s="40" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G71" s="39" t="s">
         <v>10</v>
       </c>
       <c r="H71" s="39" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="I71" s="39" cm="1">
         <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -7559,13 +7532,13 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="K71" s="68"/>
+      <c r="K71" s="50"/>
       <c r="L71" s="39" t="s">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="M71" s="39"/>
       <c r="N71" s="39" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:14" s="18" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -7575,40 +7548,40 @@
       <c r="B72" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="C72" s="64">
+      <c r="C72" s="43">
         <v>1.7</v>
       </c>
-      <c r="D72" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="E72" s="64" t="s">
-        <v>49</v>
-      </c>
-      <c r="F72" s="65" t="s">
-        <v>125</v>
-      </c>
-      <c r="G72" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="H72" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="I72" s="64" cm="1">
+      <c r="D72" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="E72" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="F72" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="G72" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="H72" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="I72" s="43" cm="1">
         <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J72" s="64">
+      <c r="J72" s="43">
         <f>I72</f>
         <v>1</v>
       </c>
-      <c r="K72" s="69">
+      <c r="K72" s="51">
         <v>27</v>
       </c>
-      <c r="L72" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="M72" s="64"/>
-      <c r="N72" s="64" t="s">
+      <c r="L72" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="M72" s="43"/>
+      <c r="N72" s="43" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7619,38 +7592,38 @@
       <c r="B73" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C73" s="62">
+      <c r="C73" s="41">
         <v>1.7</v>
       </c>
-      <c r="D73" s="62" t="s">
-        <v>127</v>
-      </c>
-      <c r="E73" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="F73" s="63" t="s">
-        <v>120</v>
-      </c>
-      <c r="G73" s="62" t="s">
+      <c r="D73" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="E73" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F73" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="G73" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="H73" s="62" t="s">
-        <v>37</v>
-      </c>
-      <c r="I73" s="62" cm="1">
+      <c r="H73" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="I73" s="41" cm="1">
         <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="J73" s="62">
+      <c r="J73" s="41">
         <f>I73</f>
         <v>8</v>
       </c>
-      <c r="K73" s="70"/>
-      <c r="L73" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="M73" s="62"/>
-      <c r="N73" s="62" t="s">
+      <c r="K73" s="52"/>
+      <c r="L73" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="M73" s="41"/>
+      <c r="N73" s="41" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7661,38 +7634,38 @@
       <c r="B74" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C74" s="62">
+      <c r="C74" s="41">
         <v>1.7</v>
       </c>
-      <c r="D74" s="62" t="s">
-        <v>127</v>
-      </c>
-      <c r="E74" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="F74" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="G74" s="62" t="s">
+      <c r="D74" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="E74" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="G74" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="H74" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="I74" s="62" cm="1">
+      <c r="H74" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I74" s="41" cm="1">
         <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J74" s="62">
+      <c r="J74" s="41">
         <f>I74</f>
         <v>5</v>
       </c>
-      <c r="K74" s="70"/>
-      <c r="L74" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="M74" s="62"/>
-      <c r="N74" s="62" t="s">
+      <c r="K74" s="52"/>
+      <c r="L74" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="M74" s="41"/>
+      <c r="N74" s="41" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7703,38 +7676,38 @@
       <c r="B75" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="C75" s="62">
+      <c r="C75" s="41">
         <v>1.7</v>
       </c>
-      <c r="D75" s="62" t="s">
-        <v>127</v>
-      </c>
-      <c r="E75" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="F75" s="63" t="s">
-        <v>112</v>
-      </c>
-      <c r="G75" s="62" t="s">
-        <v>38</v>
-      </c>
-      <c r="H75" s="62" t="s">
-        <v>37</v>
-      </c>
-      <c r="I75" s="62" cm="1">
+      <c r="D75" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="E75" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F75" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G75" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="H75" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="I75" s="41" cm="1">
         <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>8</v>
       </c>
-      <c r="J75" s="62">
+      <c r="J75" s="41">
         <f>I75</f>
         <v>8</v>
       </c>
-      <c r="K75" s="70"/>
-      <c r="L75" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="M75" s="62"/>
-      <c r="N75" s="62" t="s">
+      <c r="K75" s="52"/>
+      <c r="L75" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="M75" s="41"/>
+      <c r="N75" s="41" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7743,38 +7716,38 @@
         <v>75</v>
       </c>
       <c r="B76" s="39"/>
-      <c r="C76" s="62">
+      <c r="C76" s="41">
         <v>1.7</v>
       </c>
-      <c r="D76" s="62" t="s">
-        <v>127</v>
-      </c>
-      <c r="E76" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="F76" s="63" t="s">
-        <v>113</v>
-      </c>
-      <c r="G76" s="62" t="s">
-        <v>38</v>
-      </c>
-      <c r="H76" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="I76" s="62" cm="1">
+      <c r="D76" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="E76" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="42" t="s">
+        <v>101</v>
+      </c>
+      <c r="G76" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="H76" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I76" s="41" cm="1">
         <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J76" s="62">
+      <c r="J76" s="41">
         <f>I76</f>
         <v>5</v>
       </c>
-      <c r="K76" s="71"/>
-      <c r="L76" s="62" t="s">
-        <v>28</v>
-      </c>
-      <c r="M76" s="62"/>
-      <c r="N76" s="62" t="s">
+      <c r="K76" s="53"/>
+      <c r="L76" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="M76" s="41"/>
+      <c r="N76" s="41" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7910,13 +7883,16 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="K59:K71"/>
-    <mergeCell ref="K72:K76"/>
-    <mergeCell ref="K12:K19"/>
-    <mergeCell ref="K20:K30"/>
-    <mergeCell ref="K31:K43"/>
-    <mergeCell ref="K44:K51"/>
-    <mergeCell ref="K52:K58"/>
+    <mergeCell ref="K12:K20"/>
+    <mergeCell ref="K32:K43"/>
+    <mergeCell ref="J48:J51"/>
+    <mergeCell ref="G52:G55"/>
+    <mergeCell ref="H52:H55"/>
+    <mergeCell ref="I52:I55"/>
+    <mergeCell ref="J52:J55"/>
+    <mergeCell ref="G48:G51"/>
+    <mergeCell ref="H48:H51"/>
+    <mergeCell ref="I48:I51"/>
     <mergeCell ref="H44:H47"/>
     <mergeCell ref="I44:I47"/>
     <mergeCell ref="G44:G47"/>
@@ -7925,14 +7901,11 @@
     <mergeCell ref="H36:H43"/>
     <mergeCell ref="I36:I43"/>
     <mergeCell ref="J36:J43"/>
-    <mergeCell ref="J48:J51"/>
-    <mergeCell ref="G52:G55"/>
-    <mergeCell ref="H52:H55"/>
-    <mergeCell ref="I52:I55"/>
-    <mergeCell ref="J52:J55"/>
-    <mergeCell ref="G48:G51"/>
-    <mergeCell ref="H48:H51"/>
-    <mergeCell ref="I48:I51"/>
+    <mergeCell ref="K59:K71"/>
+    <mergeCell ref="K72:K76"/>
+    <mergeCell ref="K21:K31"/>
+    <mergeCell ref="K44:K51"/>
+    <mergeCell ref="K52:K58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7945,30 +7918,30 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.109375" style="74" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.109375" style="47" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="73" t="s">
-        <v>130</v>
+        <v>117</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>118</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>0</v>
       </c>
-      <c r="B2" s="73">
+      <c r="B2" s="46">
         <v>156</v>
       </c>
       <c r="C2" s="1">
@@ -7982,7 +7955,7 @@
       <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="74">
+      <c r="B3" s="47">
         <f>156-SUM(D$3:D3)</f>
         <v>156</v>
       </c>
@@ -7998,7 +7971,7 @@
       <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="74">
+      <c r="B4" s="47">
         <f>156-SUM(D$3:D4)</f>
         <v>156</v>
       </c>
@@ -8009,13 +7982,13 @@
       <c r="D4" s="3">
         <v>0</v>
       </c>
-      <c r="K4" s="72"/>
+      <c r="K4" s="45"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="74">
+      <c r="B5" s="47">
         <f>156-SUM(D$3:D5)</f>
         <v>156</v>
       </c>
@@ -8031,7 +8004,7 @@
       <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="74">
+      <c r="B6" s="47">
         <f>156-SUM(D$3:D6)</f>
         <v>156</v>
       </c>
@@ -8047,7 +8020,7 @@
       <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="74">
+      <c r="B7" s="47">
         <f>156-SUM(D$3:D7)</f>
         <v>148</v>
       </c>
@@ -8063,65 +8036,80 @@
       <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="74">
+      <c r="B8" s="47">
         <f>156-SUM(D$3:D8)</f>
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
         <v>62.400000000000006</v>
       </c>
+      <c r="D8" s="3">
+        <v>8</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="74">
+      <c r="B9" s="47">
         <f>156-SUM(D$3:D9)</f>
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="0"/>
         <v>46.8</v>
       </c>
+      <c r="D9" s="3">
+        <v>24</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="74">
+      <c r="B10" s="47">
         <f>156-SUM(D$3:D10)</f>
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="0"/>
         <v>31.200000000000003</v>
       </c>
+      <c r="D10" s="3">
+        <v>14</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="74">
+      <c r="B11" s="47">
         <f>156-SUM(D$3:D11)</f>
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="0"/>
         <v>15.599999999999994</v>
       </c>
+      <c r="D11" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="74">
+      <c r="B12" s="47">
         <f>156-SUM(D$3:D12)</f>
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -8168,76 +8156,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="13.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="13.44140625" style="1"/>
-    <col min="3" max="16384" width="13.44140625" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>